--- a/data/rateBuildUp/File1/RPT_RPT9853920998378DH_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT9853920998378DH_rateBuildUp.xlsx
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="C11" s="369" t="n">
-        <v>27533.60019374257</v>
+        <v>27533.60019374256</v>
       </c>
       <c r="D11" s="368" t="n">
         <v>26315.66991086273</v>
@@ -2979,7 +2979,7 @@
         <v>490.3091753834818</v>
       </c>
       <c r="K11" s="372" t="n">
-        <v>513.4725451369675</v>
+        <v>513.4725451369674</v>
       </c>
       <c r="L11" s="373" t="n">
         <v>495.9814021904138</v>
@@ -2994,7 +2994,7 @@
         <v>490.3091753834818</v>
       </c>
       <c r="P11" s="372" t="n">
-        <v>513.4725451369675</v>
+        <v>513.4725451369674</v>
       </c>
       <c r="Q11" s="373" t="n">
         <v>495.9814021904138</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="T11" s="374" t="n">
-        <v>27533.60019374257</v>
+        <v>27533.60019374256</v>
       </c>
       <c r="U11" s="375" t="n">
         <v>26315.66991086273</v>
@@ -3029,7 +3029,7 @@
         <v>490.3091753834818</v>
       </c>
       <c r="AB11" s="372" t="n">
-        <v>513.4725451369675</v>
+        <v>513.4725451369674</v>
       </c>
       <c r="AC11" s="378" t="n">
         <v>495.9814021904138</v>
@@ -3044,7 +3044,7 @@
         <v>490.3091753834818</v>
       </c>
       <c r="AG11" s="372" t="n">
-        <v>513.4725451369675</v>
+        <v>513.4725451369674</v>
       </c>
       <c r="AH11" s="378" t="n">
         <v>495.9814021904138</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="AK11" s="379" t="n">
-        <v>27533.60019374257</v>
+        <v>27533.60019374256</v>
       </c>
       <c r="AL11" s="368" t="n">
         <v>26315.66991086273</v>
@@ -3079,7 +3079,7 @@
         <v>490.3091753834818</v>
       </c>
       <c r="AS11" s="372" t="n">
-        <v>513.4725451369675</v>
+        <v>513.4725451369674</v>
       </c>
       <c r="AT11" s="382" t="n">
         <v>495.9814021904138</v>
@@ -3094,7 +3094,7 @@
         <v>490.3091753834818</v>
       </c>
       <c r="AX11" s="372" t="n">
-        <v>513.4725451369675</v>
+        <v>513.4725451369674</v>
       </c>
       <c r="AY11" s="382" t="n">
         <v>495.9814021904138</v>
@@ -3129,7 +3129,7 @@
         <v>541.8775257478355</v>
       </c>
       <c r="BJ11" s="372" t="n">
-        <v>582.7679089778392</v>
+        <v>582.7679089778394</v>
       </c>
       <c r="BK11" s="387" t="n">
         <v>577.2373044476068</v>
@@ -3144,7 +3144,7 @@
         <v>541.8775257478355</v>
       </c>
       <c r="BO11" s="389" t="n">
-        <v>582.7679089778392</v>
+        <v>582.7679089778394</v>
       </c>
       <c r="BP11" s="390" t="n">
         <v>577.2373044476068</v>
@@ -3155,67 +3155,67 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>28322.20805009452</v>
+        <v>28322.2080500945</v>
       </c>
       <c r="BT11" s="375" t="n">
-        <v>28002.07171383925</v>
+        <v>28002.07171383924</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>28094.86551429901</v>
+        <v>28094.865514299</v>
       </c>
       <c r="BV11" s="375" t="n">
         <v>26054.0704913905</v>
       </c>
       <c r="BW11" s="392" t="n">
-        <v>26045.21236363478</v>
+        <v>26045.21236363477</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>405.8570401836623</v>
+        <v>405.857040183662</v>
       </c>
       <c r="BY11" s="372" t="n">
-        <v>490.9636863282959</v>
+        <v>490.9636863282958</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>543.4302890512532</v>
+        <v>543.4302890512531</v>
       </c>
       <c r="CA11" s="372" t="n">
-        <v>584.8282025319799</v>
+        <v>584.8282025319797</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>578.9790234911328</v>
+        <v>578.9790234911326</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>405.8570401836623</v>
+        <v>405.857040183662</v>
       </c>
       <c r="CD11" s="389" t="n">
-        <v>490.9636863282959</v>
+        <v>490.9636863282958</v>
       </c>
       <c r="CE11" s="389" t="n">
-        <v>543.4302890512532</v>
+        <v>543.4302890512531</v>
       </c>
       <c r="CF11" s="389" t="n">
-        <v>584.8282025319799</v>
+        <v>584.8282025319797</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>578.9790234911328</v>
+        <v>578.9790234911326</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>-0.6910442327008468</v>
+        <v>-0.6910442327006194</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>-1.132949106394676</v>
+        <v>-1.132949106394506</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>-1.552763303417692</v>
+        <v>-1.552763303417578</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>-2.060293554140685</v>
+        <v>-2.060293554140344</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>-1.741719043526018</v>
+        <v>-1.741719043525791</v>
       </c>
       <c r="DC11" s="393" t="n">
-        <v>0.006882681329726999</v>
+        <v>0.006882681329727002</v>
       </c>
       <c r="DD11" s="394" t="n">
         <v>0.007078910884978879</v>
@@ -3224,7 +3224,7 @@
         <v>0.007369697822890922</v>
       </c>
       <c r="DF11" s="394" t="n">
-        <v>0.008029147366660704</v>
+        <v>0.008029147366660706</v>
       </c>
       <c r="DG11" s="395" t="n">
         <v>0.008141014872206944</v>
@@ -3243,7 +3243,7 @@
         <v>26168.92896157521</v>
       </c>
       <c r="E12" s="368" t="n">
-        <v>27515.98656406561</v>
+        <v>27515.98656406562</v>
       </c>
       <c r="F12" s="368" t="n">
         <v>29115.49965002214</v>
@@ -3258,7 +3258,7 @@
         <v>1204.523752301448</v>
       </c>
       <c r="J12" s="372" t="n">
-        <v>1259.965877238419</v>
+        <v>1259.96587723842</v>
       </c>
       <c r="K12" s="372" t="n">
         <v>1384.522274306753</v>
@@ -3273,7 +3273,7 @@
         <v>1204.523752301448</v>
       </c>
       <c r="O12" s="372" t="n">
-        <v>1259.965877238419</v>
+        <v>1259.96587723842</v>
       </c>
       <c r="P12" s="372" t="n">
         <v>1384.522274306753</v>
@@ -3293,7 +3293,7 @@
         <v>26168.92896157521</v>
       </c>
       <c r="V12" s="375" t="n">
-        <v>27515.98656406561</v>
+        <v>27515.98656406562</v>
       </c>
       <c r="W12" s="375" t="n">
         <v>29115.49965002214</v>
@@ -3308,7 +3308,7 @@
         <v>1204.523752301448</v>
       </c>
       <c r="AA12" s="372" t="n">
-        <v>1259.965877238419</v>
+        <v>1259.96587723842</v>
       </c>
       <c r="AB12" s="372" t="n">
         <v>1384.522274306753</v>
@@ -3323,7 +3323,7 @@
         <v>1204.523752301448</v>
       </c>
       <c r="AF12" s="372" t="n">
-        <v>1259.965877238419</v>
+        <v>1259.96587723842</v>
       </c>
       <c r="AG12" s="372" t="n">
         <v>1384.522274306753</v>
@@ -3343,7 +3343,7 @@
         <v>26168.92896157521</v>
       </c>
       <c r="AM12" s="368" t="n">
-        <v>27515.98656406561</v>
+        <v>27515.98656406562</v>
       </c>
       <c r="AN12" s="368" t="n">
         <v>29115.49965002214</v>
@@ -3358,7 +3358,7 @@
         <v>1204.523752301448</v>
       </c>
       <c r="AR12" s="372" t="n">
-        <v>1259.965877238419</v>
+        <v>1259.96587723842</v>
       </c>
       <c r="AS12" s="372" t="n">
         <v>1384.522274306753</v>
@@ -3373,7 +3373,7 @@
         <v>1204.523752301448</v>
       </c>
       <c r="AW12" s="372" t="n">
-        <v>1259.965877238419</v>
+        <v>1259.96587723842</v>
       </c>
       <c r="AX12" s="372" t="n">
         <v>1384.522274306753</v>
@@ -3399,7 +3399,7 @@
         <v>32921.43236967759</v>
       </c>
       <c r="BF12" s="385" t="n">
-        <v>35412.91240490867</v>
+        <v>35412.91240490868</v>
       </c>
       <c r="BG12" s="386" t="n">
         <v>1087.317919203497</v>
@@ -3414,7 +3414,7 @@
         <v>1565.504867365974</v>
       </c>
       <c r="BK12" s="387" t="n">
-        <v>1656.811177512632</v>
+        <v>1656.811177512633</v>
       </c>
       <c r="BL12" s="386" t="n">
         <v>1087.317919203497</v>
@@ -3429,7 +3429,7 @@
         <v>1565.504867365974</v>
       </c>
       <c r="BP12" s="387" t="n">
-        <v>1656.811177512632</v>
+        <v>1656.811177512633</v>
       </c>
       <c r="BR12" s="101" t="inlineStr">
         <is>
@@ -3443,13 +3443,13 @@
         <v>27900.96826196151</v>
       </c>
       <c r="BU12" s="375" t="n">
-        <v>30211.60156327631</v>
+        <v>30211.6015632763</v>
       </c>
       <c r="BV12" s="375" t="n">
         <v>32821.07093582704</v>
       </c>
       <c r="BW12" s="392" t="n">
-        <v>35324.77891113863</v>
+        <v>35324.77891113864</v>
       </c>
       <c r="BX12" s="386" t="n">
         <v>1088.422091931164</v>
@@ -3464,7 +3464,7 @@
         <v>1567.225421588523</v>
       </c>
       <c r="CB12" s="387" t="n">
-        <v>1658.548376232081</v>
+        <v>1658.548376232082</v>
       </c>
       <c r="CC12" s="386" t="n">
         <v>1088.422091931164</v>
@@ -3479,13 +3479,13 @@
         <v>1567.225421588523</v>
       </c>
       <c r="CG12" s="387" t="n">
-        <v>1658.548376232081</v>
+        <v>1658.548376232082</v>
       </c>
       <c r="CW12" s="102" t="n">
         <v>-1.104172727667901</v>
       </c>
       <c r="CX12" s="103" t="n">
-        <v>-1.235658099259808</v>
+        <v>-1.235658099259581</v>
       </c>
       <c r="CY12" s="103" t="n">
         <v>-1.333344593036372</v>
@@ -3494,7 +3494,7 @@
         <v>-1.720554222548571</v>
       </c>
       <c r="DA12" s="104" t="n">
-        <v>-1.737198719449225</v>
+        <v>-1.737198719448998</v>
       </c>
       <c r="DC12" s="396" t="n">
         <v>0.001959277825132627</v>
@@ -3525,22 +3525,22 @@
         <v>61746.03410505551</v>
       </c>
       <c r="E13" s="368" t="n">
-        <v>71264.64074453349</v>
+        <v>71264.64074453348</v>
       </c>
       <c r="F13" s="368" t="n">
         <v>83503.56355590188</v>
       </c>
       <c r="G13" s="370" t="n">
-        <v>88133.91767512726</v>
+        <v>88133.91767512725</v>
       </c>
       <c r="H13" s="371" t="n">
-        <v>951.7410152923399</v>
+        <v>951.74101529234</v>
       </c>
       <c r="I13" s="372" t="n">
         <v>1001.882330944587</v>
       </c>
       <c r="J13" s="372" t="n">
-        <v>1045.435453010062</v>
+        <v>1045.435453010061</v>
       </c>
       <c r="K13" s="372" t="n">
         <v>1089.217103321932</v>
@@ -3549,13 +3549,13 @@
         <v>1093.754178960799</v>
       </c>
       <c r="M13" s="371" t="n">
-        <v>951.7410152923399</v>
+        <v>951.74101529234</v>
       </c>
       <c r="N13" s="372" t="n">
         <v>1001.882330944587</v>
       </c>
       <c r="O13" s="372" t="n">
-        <v>1045.435453010062</v>
+        <v>1045.435453010061</v>
       </c>
       <c r="P13" s="372" t="n">
         <v>1089.217103321932</v>
@@ -3575,22 +3575,22 @@
         <v>61746.03410505551</v>
       </c>
       <c r="V13" s="375" t="n">
-        <v>71264.64074453349</v>
+        <v>71264.64074453348</v>
       </c>
       <c r="W13" s="375" t="n">
         <v>83503.56355590188</v>
       </c>
       <c r="X13" s="376" t="n">
-        <v>88133.91767512726</v>
+        <v>88133.91767512725</v>
       </c>
       <c r="Y13" s="377" t="n">
-        <v>951.7410152923399</v>
+        <v>951.74101529234</v>
       </c>
       <c r="Z13" s="372" t="n">
         <v>1001.882330944587</v>
       </c>
       <c r="AA13" s="372" t="n">
-        <v>1045.435453010062</v>
+        <v>1045.435453010061</v>
       </c>
       <c r="AB13" s="372" t="n">
         <v>1089.217103321932</v>
@@ -3599,13 +3599,13 @@
         <v>1093.754178960799</v>
       </c>
       <c r="AD13" s="377" t="n">
-        <v>951.7410152923399</v>
+        <v>951.74101529234</v>
       </c>
       <c r="AE13" s="372" t="n">
         <v>1001.882330944587</v>
       </c>
       <c r="AF13" s="372" t="n">
-        <v>1045.435453010062</v>
+        <v>1045.435453010061</v>
       </c>
       <c r="AG13" s="372" t="n">
         <v>1089.217103321932</v>
@@ -3619,22 +3619,22 @@
         </is>
       </c>
       <c r="AK13" s="379" t="n">
-        <v>54637.73174188553</v>
+        <v>54637.73174188552</v>
       </c>
       <c r="AL13" s="368" t="n">
         <v>63910.91446389175</v>
       </c>
       <c r="AM13" s="368" t="n">
-        <v>73048.19109610903</v>
+        <v>73048.19109610902</v>
       </c>
       <c r="AN13" s="368" t="n">
-        <v>84676.65565561295</v>
+        <v>84676.65565561294</v>
       </c>
       <c r="AO13" s="380" t="n">
-        <v>88286.35871449432</v>
+        <v>88286.35871449429</v>
       </c>
       <c r="AP13" s="381" t="n">
-        <v>915.6021385004517</v>
+        <v>915.6021385004516</v>
       </c>
       <c r="AQ13" s="372" t="n">
         <v>969.0341900405748</v>
@@ -3646,10 +3646,10 @@
         <v>1066.207444713713</v>
       </c>
       <c r="AT13" s="382" t="n">
-        <v>1095.645993465942</v>
+        <v>1095.645993465941</v>
       </c>
       <c r="AU13" s="372" t="n">
-        <v>915.6021385004517</v>
+        <v>915.6021385004516</v>
       </c>
       <c r="AV13" s="372" t="n">
         <v>969.0341900405748</v>
@@ -3661,7 +3661,7 @@
         <v>1066.207444713713</v>
       </c>
       <c r="AY13" s="382" t="n">
-        <v>1095.645993465942</v>
+        <v>1095.645993465941</v>
       </c>
       <c r="BA13" s="111" t="inlineStr">
         <is>
@@ -3678,13 +3678,13 @@
         <v>80312.3850211127</v>
       </c>
       <c r="BE13" s="384" t="n">
-        <v>95718.50622591648</v>
+        <v>95718.5062259165</v>
       </c>
       <c r="BF13" s="385" t="n">
         <v>102321.5533311226</v>
       </c>
       <c r="BG13" s="386" t="n">
-        <v>945.4487346261551</v>
+        <v>945.448734626155</v>
       </c>
       <c r="BH13" s="372" t="n">
         <v>1031.972578942236</v>
@@ -3693,13 +3693,13 @@
         <v>1111.671683105557</v>
       </c>
       <c r="BJ13" s="372" t="n">
-        <v>1205.24108025732</v>
+        <v>1205.241080257321</v>
       </c>
       <c r="BK13" s="387" t="n">
         <v>1269.824711142503</v>
       </c>
       <c r="BL13" s="386" t="n">
-        <v>945.4487346261551</v>
+        <v>945.448734626155</v>
       </c>
       <c r="BM13" s="372" t="n">
         <v>1031.972578942236</v>
@@ -3708,7 +3708,7 @@
         <v>1111.671683105557</v>
       </c>
       <c r="BO13" s="372" t="n">
-        <v>1205.24108025732</v>
+        <v>1205.241080257321</v>
       </c>
       <c r="BP13" s="387" t="n">
         <v>1269.824711142503</v>
@@ -3728,13 +3728,13 @@
         <v>80275.37117388066</v>
       </c>
       <c r="BV13" s="375" t="n">
-        <v>95676.90735934766</v>
+        <v>95676.90735934769</v>
       </c>
       <c r="BW13" s="392" t="n">
         <v>102277.2793220108</v>
       </c>
       <c r="BX13" s="386" t="n">
-        <v>946.2000887448386</v>
+        <v>946.2000887448385</v>
       </c>
       <c r="BY13" s="372" t="n">
         <v>1032.705485420063</v>
@@ -3743,13 +3743,13 @@
         <v>1112.37738860219</v>
       </c>
       <c r="CA13" s="372" t="n">
-        <v>1205.922877818226</v>
+        <v>1205.922877818227</v>
       </c>
       <c r="CB13" s="387" t="n">
         <v>1270.521214318287</v>
       </c>
       <c r="CC13" s="386" t="n">
-        <v>946.2000887448386</v>
+        <v>946.2000887448385</v>
       </c>
       <c r="CD13" s="372" t="n">
         <v>1032.705485420063</v>
@@ -3758,7 +3758,7 @@
         <v>1112.37738860219</v>
       </c>
       <c r="CF13" s="372" t="n">
-        <v>1205.922877818226</v>
+        <v>1205.922877818227</v>
       </c>
       <c r="CG13" s="387" t="n">
         <v>1270.521214318287</v>
@@ -3773,7 +3773,7 @@
         <v>-0.7057054966328451</v>
       </c>
       <c r="CZ13" s="103" t="n">
-        <v>-0.6817975609060341</v>
+        <v>-0.6817975609062614</v>
       </c>
       <c r="DA13" s="104" t="n">
         <v>-0.696503175783846</v>
@@ -3954,10 +3954,10 @@
         <v>1396.713675262076</v>
       </c>
       <c r="BC14" s="414" t="n">
-        <v>1574.304239361769</v>
+        <v>1574.304239361768</v>
       </c>
       <c r="BD14" s="414" t="n">
-        <v>1783.009384712697</v>
+        <v>1783.009384712696</v>
       </c>
       <c r="BE14" s="414" t="n">
         <v>1972.040097159817</v>
@@ -4004,7 +4004,7 @@
         <v>1388.182490247327</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>1564.688323821328</v>
+        <v>1564.688323821327</v>
       </c>
       <c r="BU14" s="420" t="n">
         <v>1772.11868949475</v>
@@ -4013,52 +4013,52 @@
         <v>1959.99479451594</v>
       </c>
       <c r="BW14" s="421" t="n">
-        <v>2162.621084936832</v>
+        <v>2162.621084936831</v>
       </c>
       <c r="BX14" s="416" t="n">
         <v>320.6687990267246</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>352.2890007084519</v>
+        <v>352.2890007084518</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>387.2241012132338</v>
+        <v>387.2241012132337</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>419.7639390213697</v>
+        <v>419.7639390213696</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>453.9534616845576</v>
+        <v>453.9534616845573</v>
       </c>
       <c r="CC14" s="417" t="n">
         <v>320.6687990267246</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>352.2890007084519</v>
+        <v>352.2890007084518</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>387.2241012132338</v>
+        <v>387.2241012132337</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>419.7639390213697</v>
+        <v>419.7639390213696</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>453.9534616845576</v>
+        <v>453.9534616845573</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>1.044104503900144</v>
+        <v>1.044104503900257</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>1.14706057498438</v>
+        <v>1.147060574984494</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>1.26081009756507</v>
+        <v>1.260810097565184</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>1.366760496201437</v>
+        <v>1.36676049620155</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>1.478082130893881</v>
+        <v>1.478082130894109</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         <v>143085.1761998027</v>
       </c>
       <c r="H15" s="427" t="n">
-        <v>692.7742736631672</v>
+        <v>692.7742736631673</v>
       </c>
       <c r="I15" s="427" t="n">
         <v>795.5296329163514</v>
@@ -4107,13 +4107,13 @@
         <v>857.8725573863406</v>
       </c>
       <c r="K15" s="427" t="n">
-        <v>932.2104230851974</v>
+        <v>932.2104230851971</v>
       </c>
       <c r="L15" s="428" t="n">
-        <v>939.8101191136197</v>
+        <v>939.8101191136195</v>
       </c>
       <c r="M15" s="427" t="n">
-        <v>692.7742736631672</v>
+        <v>692.7742736631673</v>
       </c>
       <c r="N15" s="427" t="n">
         <v>795.5296329163514</v>
@@ -4122,10 +4122,10 @@
         <v>857.8725573863406</v>
       </c>
       <c r="P15" s="427" t="n">
-        <v>932.2104230851974</v>
+        <v>932.2104230851971</v>
       </c>
       <c r="Q15" s="428" t="n">
-        <v>939.8101191136197</v>
+        <v>939.8101191136195</v>
       </c>
       <c r="S15" s="143" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>143085.1761998027</v>
       </c>
       <c r="Y15" s="432" t="n">
-        <v>692.7742736631672</v>
+        <v>692.7742736631673</v>
       </c>
       <c r="Z15" s="433" t="n">
         <v>795.5296329163514</v>
@@ -4157,13 +4157,13 @@
         <v>857.8725573863406</v>
       </c>
       <c r="AB15" s="433" t="n">
-        <v>932.2104230851974</v>
+        <v>932.2104230851971</v>
       </c>
       <c r="AC15" s="434" t="n">
-        <v>939.8101191136197</v>
+        <v>939.8101191136195</v>
       </c>
       <c r="AD15" s="433" t="n">
-        <v>692.7742736631672</v>
+        <v>692.7742736631673</v>
       </c>
       <c r="AE15" s="433" t="n">
         <v>795.5296329163514</v>
@@ -4172,10 +4172,10 @@
         <v>857.8725573863406</v>
       </c>
       <c r="AG15" s="433" t="n">
-        <v>932.2104230851974</v>
+        <v>932.2104230851971</v>
       </c>
       <c r="AH15" s="434" t="n">
-        <v>939.8101191136197</v>
+        <v>939.8101191136195</v>
       </c>
       <c r="AJ15" s="150" t="inlineStr">
         <is>
@@ -4192,13 +4192,13 @@
         <v>127769.928318071</v>
       </c>
       <c r="AN15" s="408" t="n">
-        <v>138648.0583758753</v>
+        <v>138648.0583758752</v>
       </c>
       <c r="AO15" s="409" t="n">
-        <v>143237.6172391698</v>
+        <v>143237.6172391697</v>
       </c>
       <c r="AP15" s="436" t="n">
-        <v>686.7142670816485</v>
+        <v>686.7142670816484</v>
       </c>
       <c r="AQ15" s="437" t="n">
         <v>787.0193878002541</v>
@@ -4207,13 +4207,13 @@
         <v>846.5152354149191</v>
       </c>
       <c r="AS15" s="437" t="n">
-        <v>922.9252215735536</v>
+        <v>922.9252215735534</v>
       </c>
       <c r="AT15" s="438" t="n">
-        <v>940.8113802866521</v>
+        <v>940.8113802866519</v>
       </c>
       <c r="AU15" s="437" t="n">
-        <v>686.7142670816485</v>
+        <v>686.7142670816484</v>
       </c>
       <c r="AV15" s="437" t="n">
         <v>787.0193878002541</v>
@@ -4222,10 +4222,10 @@
         <v>846.5152354149191</v>
       </c>
       <c r="AX15" s="437" t="n">
-        <v>922.9252215735536</v>
+        <v>922.9252215735534</v>
       </c>
       <c r="AY15" s="438" t="n">
-        <v>940.8113802866521</v>
+        <v>940.8113802866519</v>
       </c>
       <c r="BA15" s="155" t="inlineStr">
         <is>
@@ -4292,16 +4292,16 @@
         <v>140353.9569409507</v>
       </c>
       <c r="BV15" s="440" t="n">
-        <v>156512.0435810811</v>
+        <v>156512.0435810812</v>
       </c>
       <c r="BW15" s="441" t="n">
         <v>165809.8916817211</v>
       </c>
       <c r="BX15" s="442" t="n">
-        <v>712.0337954935409</v>
+        <v>712.0337954935407</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>842.3216510005188</v>
+        <v>842.3216510005187</v>
       </c>
       <c r="BZ15" s="443" t="n">
         <v>934.4971416336789</v>
@@ -4313,10 +4313,10 @@
         <v>1094.111246718037</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>712.0337954935409</v>
+        <v>712.0337954935407</v>
       </c>
       <c r="CD15" s="443" t="n">
-        <v>842.3216510005188</v>
+        <v>842.3216510005187</v>
       </c>
       <c r="CE15" s="443" t="n">
         <v>934.4971416336789</v>
@@ -7289,7 +7289,7 @@
         <v>21.09561146293518</v>
       </c>
       <c r="BC29" s="375" t="n">
-        <v>2.577067939231929</v>
+        <v>2.57706793923193</v>
       </c>
       <c r="BD29" s="375" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0.2995295734807621</v>
       </c>
       <c r="BH29" s="372" t="n">
-        <v>0.04473398905172603</v>
+        <v>0.04473398905172606</v>
       </c>
       <c r="BI29" s="372" t="n">
         <v>0</v>
@@ -7319,7 +7319,7 @@
         <v>0.2995295734807621</v>
       </c>
       <c r="BM29" s="389" t="n">
-        <v>0.04473398905172603</v>
+        <v>0.04473398905172606</v>
       </c>
       <c r="BN29" s="389" t="n">
         <v>0</v>
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>21.08304189588392</v>
+        <v>21.08304189588391</v>
       </c>
       <c r="BT29" s="375" t="n">
-        <v>2.575532424211909</v>
+        <v>2.57553242421191</v>
       </c>
       <c r="BU29" s="375" t="n">
         <v>0</v>
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3021198406140171</v>
       </c>
       <c r="BY29" s="372" t="n">
-        <v>0.04515711930786145</v>
+        <v>0.04515711930786146</v>
       </c>
       <c r="BZ29" s="372" t="n">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         <v>0</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3021198406140171</v>
       </c>
       <c r="CD29" s="389" t="n">
-        <v>0.04515711930786145</v>
+        <v>0.04515711930786146</v>
       </c>
       <c r="CE29" s="389" t="n">
         <v>0</v>
@@ -7381,10 +7381,10 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>-0.002590267133255164</v>
+        <v>-0.002590267133254998</v>
       </c>
       <c r="CX29" s="92" t="n">
-        <v>-0.000423130256135412</v>
+        <v>-0.000423130256135398</v>
       </c>
       <c r="CY29" s="92" t="n">
         <v>0</v>
@@ -7571,7 +7571,7 @@
         <v>158.9298921825861</v>
       </c>
       <c r="BC30" s="375" t="n">
-        <v>22.90282108124559</v>
+        <v>22.9028210812456</v>
       </c>
       <c r="BD30" s="375" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
         <v>6.541805167456872</v>
       </c>
       <c r="BH30" s="372" t="n">
-        <v>1.054188806411513</v>
+        <v>1.054188806411514</v>
       </c>
       <c r="BI30" s="372" t="n">
         <v>0</v>
@@ -7601,7 +7601,7 @@
         <v>6.541805167456872</v>
       </c>
       <c r="BM30" s="372" t="n">
-        <v>1.054188806411513</v>
+        <v>1.054188806411514</v>
       </c>
       <c r="BN30" s="372" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>-0.01949862848592954</v>
       </c>
       <c r="CX30" s="103" t="n">
-        <v>-0.002888024539288159</v>
+        <v>-0.002888024539287937</v>
       </c>
       <c r="CY30" s="103" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
         <v>180.0255036455213</v>
       </c>
       <c r="BC33" s="440" t="n">
-        <v>25.47988902047752</v>
+        <v>25.47988902047753</v>
       </c>
       <c r="BD33" s="440" t="n">
         <v>0</v>
@@ -8432,7 +8432,7 @@
         <v>1.13409583194487</v>
       </c>
       <c r="BH33" s="443" t="n">
-        <v>0.1701588791358589</v>
+        <v>0.170158879135859</v>
       </c>
       <c r="BI33" s="443" t="n">
         <v>0</v>
@@ -8447,7 +8447,7 @@
         <v>1.13409583194487</v>
       </c>
       <c r="BM33" s="443" t="n">
-        <v>0.1701588791358589</v>
+        <v>0.170158879135859</v>
       </c>
       <c r="BN33" s="443" t="n">
         <v>0</v>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="BT33" s="440" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="BU33" s="440" t="n">
         <v>0</v>
@@ -9229,7 +9229,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="D38" s="368" t="n">
-        <v>76.38905038910423</v>
+        <v>76.38905038910424</v>
       </c>
       <c r="E38" s="368" t="n">
         <v>36.27632243820575</v>
@@ -9244,7 +9244,7 @@
         <v>1.895187911118208</v>
       </c>
       <c r="I38" s="372" t="n">
-        <v>1.325998004071401</v>
+        <v>1.325998004071402</v>
       </c>
       <c r="J38" s="372" t="n">
         <v>0.6941065098504091</v>
@@ -9259,7 +9259,7 @@
         <v>1.895187911118208</v>
       </c>
       <c r="N38" s="372" t="n">
-        <v>1.325998004071401</v>
+        <v>1.325998004071402</v>
       </c>
       <c r="O38" s="372" t="n">
         <v>0.6941065098504091</v>
@@ -9279,7 +9279,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="U38" s="375" t="n">
-        <v>76.38905038910423</v>
+        <v>76.38905038910424</v>
       </c>
       <c r="V38" s="375" t="n">
         <v>36.27632243820575</v>
@@ -9294,7 +9294,7 @@
         <v>1.895187911118208</v>
       </c>
       <c r="Z38" s="372" t="n">
-        <v>1.325998004071401</v>
+        <v>1.325998004071402</v>
       </c>
       <c r="AA38" s="372" t="n">
         <v>0.6941065098504091</v>
@@ -9309,7 +9309,7 @@
         <v>1.895187911118208</v>
       </c>
       <c r="AE38" s="372" t="n">
-        <v>1.325998004071401</v>
+        <v>1.325998004071402</v>
       </c>
       <c r="AF38" s="372" t="n">
         <v>0.6941065098504091</v>
@@ -9329,7 +9329,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="AL38" s="368" t="n">
-        <v>76.38905038910423</v>
+        <v>76.38905038910424</v>
       </c>
       <c r="AM38" s="368" t="n">
         <v>36.27632243820575</v>
@@ -9344,7 +9344,7 @@
         <v>1.895187911118208</v>
       </c>
       <c r="AQ38" s="372" t="n">
-        <v>1.325998004071401</v>
+        <v>1.325998004071402</v>
       </c>
       <c r="AR38" s="372" t="n">
         <v>0.6941065098504091</v>
@@ -9359,7 +9359,7 @@
         <v>1.895187911118208</v>
       </c>
       <c r="AV38" s="372" t="n">
-        <v>1.325998004071401</v>
+        <v>1.325998004071402</v>
       </c>
       <c r="AW38" s="372" t="n">
         <v>0.6941065098504091</v>
@@ -9379,7 +9379,7 @@
         <v>128.9348234157811</v>
       </c>
       <c r="BC38" s="375" t="n">
-        <v>71.00908550703849</v>
+        <v>71.00908550703855</v>
       </c>
       <c r="BD38" s="375" t="n">
         <v>32.88217324194801</v>
@@ -9394,13 +9394,13 @@
         <v>1.830702690576236</v>
       </c>
       <c r="BH38" s="372" t="n">
-        <v>1.232609977132256</v>
+        <v>1.232609977132257</v>
       </c>
       <c r="BI38" s="372" t="n">
         <v>0.6291632936095912</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.3266949022040899</v>
+        <v>0.3266949022040898</v>
       </c>
       <c r="BK38" s="387" t="n">
         <v>0.3521058758323221</v>
@@ -9409,13 +9409,13 @@
         <v>1.830702690576236</v>
       </c>
       <c r="BM38" s="389" t="n">
-        <v>1.232609977132256</v>
+        <v>1.232609977132257</v>
       </c>
       <c r="BN38" s="389" t="n">
         <v>0.6291632936095912</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.3266949022040899</v>
+        <v>0.3266949022040898</v>
       </c>
       <c r="BP38" s="390" t="n">
         <v>0.3521058758323221</v>
@@ -9426,70 +9426,70 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>128.4033868530686</v>
+        <v>128.4033868530685</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>70.71498798436704</v>
+        <v>70.71498798436707</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>32.62212940287412</v>
+        <v>32.62212940287411</v>
       </c>
       <c r="BV38" s="375" t="n">
-        <v>14.47832342928954</v>
+        <v>14.47832342928953</v>
       </c>
       <c r="BW38" s="392" t="n">
         <v>15.75040501531567</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>1.840019621548196</v>
+        <v>1.840019621548195</v>
       </c>
       <c r="BY38" s="372" t="n">
         <v>1.239854376999804</v>
       </c>
       <c r="BZ38" s="372" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6309997533837133</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3249907483602631</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3501278464555652</v>
       </c>
       <c r="CC38" s="388" t="n">
-        <v>1.840019621548196</v>
+        <v>1.840019621548195</v>
       </c>
       <c r="CD38" s="389" t="n">
         <v>1.239854376999804</v>
       </c>
       <c r="CE38" s="389" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6309997533837133</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3249907483602631</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3501278464555652</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-0.009316930971960291</v>
+        <v>-0.009316930971959625</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>-0.00724439986754799</v>
+        <v>-0.007244399867547546</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>-0.001836459774122279</v>
+        <v>-0.001836459774122057</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>0.00170415384382655</v>
+        <v>0.001704153843826661</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>0.001978029376756785</v>
+        <v>0.001978029376756896</v>
       </c>
       <c r="DC38" s="393" t="n">
         <v>0.003528009884850775</v>
       </c>
       <c r="DD38" s="394" t="n">
-        <v>0.003547964645490739</v>
+        <v>0.003547964645490738</v>
       </c>
       <c r="DE38" s="394" t="n">
         <v>0.00731687483938503</v>
@@ -9661,46 +9661,46 @@
         <v>126.1809430239881</v>
       </c>
       <c r="BC39" s="375" t="n">
-        <v>68.63775949785338</v>
+        <v>68.63775949785339</v>
       </c>
       <c r="BD39" s="375" t="n">
-        <v>77.47123527199037</v>
+        <v>77.47123527199035</v>
       </c>
       <c r="BE39" s="375" t="n">
-        <v>84.15760347840741</v>
+        <v>84.15760347840747</v>
       </c>
       <c r="BF39" s="392" t="n">
-        <v>92.18559925034108</v>
+        <v>92.18559925034106</v>
       </c>
       <c r="BG39" s="386" t="n">
         <v>5.193806739392924</v>
       </c>
       <c r="BH39" s="372" t="n">
-        <v>3.159312012398927</v>
+        <v>3.159312012398928</v>
       </c>
       <c r="BI39" s="372" t="n">
-        <v>3.547432787225305</v>
+        <v>3.547432787225304</v>
       </c>
       <c r="BJ39" s="372" t="n">
-        <v>4.001926052058733</v>
+        <v>4.001926052058736</v>
       </c>
       <c r="BK39" s="387" t="n">
-        <v>4.31295030178016</v>
+        <v>4.312950301780159</v>
       </c>
       <c r="BL39" s="386" t="n">
         <v>5.193806739392924</v>
       </c>
       <c r="BM39" s="372" t="n">
-        <v>3.159312012398927</v>
+        <v>3.159312012398928</v>
       </c>
       <c r="BN39" s="372" t="n">
-        <v>3.547432787225305</v>
+        <v>3.547432787225304</v>
       </c>
       <c r="BO39" s="372" t="n">
-        <v>4.001926052058733</v>
+        <v>4.001926052058736</v>
       </c>
       <c r="BP39" s="387" t="n">
-        <v>4.31295030178016</v>
+        <v>4.312950301780159</v>
       </c>
       <c r="BR39" s="101" t="inlineStr">
         <is>
@@ -9717,10 +9717,10 @@
         <v>75.5422104497019</v>
       </c>
       <c r="BV39" s="375" t="n">
-        <v>82.06208885902387</v>
+        <v>82.06208885902392</v>
       </c>
       <c r="BW39" s="392" t="n">
-        <v>89.89018846223225</v>
+        <v>89.89018846223222</v>
       </c>
       <c r="BX39" s="386" t="n">
         <v>5.14556700413425</v>
@@ -9732,10 +9732,10 @@
         <v>3.473079703178348</v>
       </c>
       <c r="CA39" s="372" t="n">
-        <v>3.918512959555192</v>
+        <v>3.918512959555193</v>
       </c>
       <c r="CB39" s="387" t="n">
-        <v>4.220471598372009</v>
+        <v>4.220471598372007</v>
       </c>
       <c r="CC39" s="386" t="n">
         <v>5.14556700413425</v>
@@ -9747,25 +9747,25 @@
         <v>3.473079703178348</v>
       </c>
       <c r="CF39" s="372" t="n">
-        <v>3.918512959555192</v>
+        <v>3.918512959555193</v>
       </c>
       <c r="CG39" s="387" t="n">
-        <v>4.220471598372009</v>
+        <v>4.220471598372007</v>
       </c>
       <c r="CW39" s="102" t="n">
         <v>0.04823973525867409</v>
       </c>
       <c r="CX39" s="103" t="n">
-        <v>0.06620390629417905</v>
+        <v>0.06620390629417949</v>
       </c>
       <c r="CY39" s="103" t="n">
-        <v>0.0743530840469564</v>
+        <v>0.07435308404695595</v>
       </c>
       <c r="CZ39" s="103" t="n">
-        <v>0.0834130925035419</v>
+        <v>0.08341309250354279</v>
       </c>
       <c r="DA39" s="104" t="n">
-        <v>0.09247870340815112</v>
+        <v>0.09247870340815201</v>
       </c>
       <c r="DC39" s="396" t="n">
         <v>0.01223209394752628</v>
@@ -9943,13 +9943,13 @@
         <v>51.96539694362117</v>
       </c>
       <c r="BC40" s="375" t="n">
-        <v>76.16858652246991</v>
+        <v>76.16858652246989</v>
       </c>
       <c r="BD40" s="375" t="n">
-        <v>111.1588074868</v>
+        <v>111.1588074867999</v>
       </c>
       <c r="BE40" s="375" t="n">
-        <v>190.917038595453</v>
+        <v>190.9170385954531</v>
       </c>
       <c r="BF40" s="392" t="n">
         <v>343.9608887271741</v>
@@ -9958,13 +9958,13 @@
         <v>0.8708199819563451</v>
       </c>
       <c r="BH40" s="372" t="n">
-        <v>1.15488825604331</v>
+        <v>1.154888256043309</v>
       </c>
       <c r="BI40" s="372" t="n">
-        <v>1.538643119344204</v>
+        <v>1.538643119344203</v>
       </c>
       <c r="BJ40" s="372" t="n">
-        <v>2.403934901504039</v>
+        <v>2.40393490150404</v>
       </c>
       <c r="BK40" s="387" t="n">
         <v>4.268602478686692</v>
@@ -9973,13 +9973,13 @@
         <v>0.8708199819563451</v>
       </c>
       <c r="BM40" s="372" t="n">
-        <v>1.15488825604331</v>
+        <v>1.154888256043309</v>
       </c>
       <c r="BN40" s="372" t="n">
-        <v>1.538643119344204</v>
+        <v>1.538643119344203</v>
       </c>
       <c r="BO40" s="372" t="n">
-        <v>2.403934901504039</v>
+        <v>2.40393490150404</v>
       </c>
       <c r="BP40" s="387" t="n">
         <v>4.268602478686692</v>
@@ -9993,10 +9993,10 @@
         <v>51.28127016427074</v>
       </c>
       <c r="BT40" s="375" t="n">
-        <v>75.3469277074357</v>
+        <v>75.34692770743568</v>
       </c>
       <c r="BU40" s="375" t="n">
-        <v>110.2409153392683</v>
+        <v>110.2409153392682</v>
       </c>
       <c r="BV40" s="375" t="n">
         <v>189.8957709512762</v>
@@ -10011,10 +10011,10 @@
         <v>1.143804330213192</v>
       </c>
       <c r="BZ40" s="372" t="n">
-        <v>1.527610520250208</v>
+        <v>1.527610520250206</v>
       </c>
       <c r="CA40" s="372" t="n">
-        <v>2.393468402265412</v>
+        <v>2.393468402265413</v>
       </c>
       <c r="CB40" s="387" t="n">
         <v>4.258292614547692</v>
@@ -10026,10 +10026,10 @@
         <v>1.143804330213192</v>
       </c>
       <c r="CE40" s="372" t="n">
-        <v>1.527610520250208</v>
+        <v>1.527610520250206</v>
       </c>
       <c r="CF40" s="372" t="n">
-        <v>2.393468402265412</v>
+        <v>2.393468402265413</v>
       </c>
       <c r="CG40" s="387" t="n">
         <v>4.258292614547692</v>
@@ -10178,7 +10178,7 @@
         <v>266.0105798954489</v>
       </c>
       <c r="AM41" s="408" t="n">
-        <v>329.1549782868616</v>
+        <v>329.1549782868615</v>
       </c>
       <c r="AN41" s="408" t="n">
         <v>392.313015246292</v>
@@ -10187,13 +10187,13 @@
         <v>463.4693476612733</v>
       </c>
       <c r="AP41" s="410" t="n">
-        <v>47.77250315590119</v>
+        <v>47.77250315590118</v>
       </c>
       <c r="AQ41" s="411" t="n">
         <v>59.72017940832428</v>
       </c>
       <c r="AR41" s="411" t="n">
-        <v>71.71680847203383</v>
+        <v>71.71680847203382</v>
       </c>
       <c r="AS41" s="411" t="n">
         <v>83.77875012707169</v>
@@ -10202,13 +10202,13 @@
         <v>97.00695391441586</v>
       </c>
       <c r="AU41" s="411" t="n">
-        <v>47.77250315590119</v>
+        <v>47.77250315590118</v>
       </c>
       <c r="AV41" s="411" t="n">
         <v>59.72017940832428</v>
       </c>
       <c r="AW41" s="411" t="n">
-        <v>71.71680847203383</v>
+        <v>71.71680847203382</v>
       </c>
       <c r="AX41" s="411" t="n">
         <v>83.77875012707169</v>
@@ -10222,13 +10222,13 @@
         </is>
       </c>
       <c r="BB41" s="419" t="n">
-        <v>205.9361072516243</v>
+        <v>205.9361072516242</v>
       </c>
       <c r="BC41" s="420" t="n">
         <v>262.1317542878902</v>
       </c>
       <c r="BD41" s="420" t="n">
-        <v>321.7147627279969</v>
+        <v>321.7147627279968</v>
       </c>
       <c r="BE41" s="420" t="n">
         <v>381.2459079147778</v>
@@ -10243,7 +10243,7 @@
         <v>58.8493713326904</v>
       </c>
       <c r="BI41" s="417" t="n">
-        <v>70.09572251124146</v>
+        <v>70.09572251124145</v>
       </c>
       <c r="BJ41" s="417" t="n">
         <v>81.41536073206443</v>
@@ -10258,7 +10258,7 @@
         <v>58.8493713326904</v>
       </c>
       <c r="BN41" s="417" t="n">
-        <v>70.09572251124146</v>
+        <v>70.09572251124145</v>
       </c>
       <c r="BO41" s="417" t="n">
         <v>81.41536073206443</v>
@@ -10272,64 +10272,64 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>204.6782409735905</v>
+        <v>204.6782409735904</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>260.5306426687525</v>
+        <v>260.5306426687524</v>
       </c>
       <c r="BU41" s="420" t="n">
-        <v>319.7497156239127</v>
+        <v>319.7497156239124</v>
       </c>
       <c r="BV41" s="420" t="n">
         <v>378.9172421086479</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>445.2245594222547</v>
+        <v>445.2245594222545</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>47.2804736992541</v>
+        <v>47.28047369925407</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>58.658378389092</v>
+        <v>58.65837838909199</v>
       </c>
       <c r="BZ41" s="417" t="n">
-        <v>69.86823003427473</v>
+        <v>69.86823003427469</v>
       </c>
       <c r="CA41" s="417" t="n">
-        <v>81.15113088855017</v>
+        <v>81.15113088855016</v>
       </c>
       <c r="CB41" s="418" t="n">
-        <v>93.4566075326219</v>
+        <v>93.45660753262186</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>47.2804736992541</v>
+        <v>47.28047369925407</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>58.658378389092</v>
+        <v>58.65837838909199</v>
       </c>
       <c r="CE41" s="417" t="n">
-        <v>69.86823003427473</v>
+        <v>69.86823003427469</v>
       </c>
       <c r="CF41" s="417" t="n">
-        <v>81.15113088855017</v>
+        <v>81.15113088855016</v>
       </c>
       <c r="CG41" s="418" t="n">
-        <v>93.4566075326219</v>
+        <v>93.45660753262186</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>0.1539462388787314</v>
+        <v>0.1539462388787527</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>0.1909929435984026</v>
+        <v>0.1909929435984168</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>0.2274924769667308</v>
+        <v>0.2274924769667592</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>0.2642298435142578</v>
+        <v>0.264229843514272</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>0.3042967027838728</v>
+        <v>0.3042967027839154</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0</v>
@@ -10357,7 +10357,7 @@
         <v>525.8330041851209</v>
       </c>
       <c r="D42" s="425" t="n">
-        <v>498.5622087236193</v>
+        <v>498.5622087236194</v>
       </c>
       <c r="E42" s="425" t="n">
         <v>576.0994171316643</v>
@@ -10407,7 +10407,7 @@
         <v>525.8330041851209</v>
       </c>
       <c r="U42" s="430" t="n">
-        <v>498.5622087236193</v>
+        <v>498.5622087236194</v>
       </c>
       <c r="V42" s="430" t="n">
         <v>576.0994171316643</v>
@@ -10472,7 +10472,7 @@
         <v>3.312558533482157</v>
       </c>
       <c r="AQ42" s="437" t="n">
-        <v>3.329480224491155</v>
+        <v>3.329480224491156</v>
       </c>
       <c r="AR42" s="437" t="n">
         <v>3.816836560333535</v>
@@ -10487,7 +10487,7 @@
         <v>3.312558533482157</v>
       </c>
       <c r="AV42" s="437" t="n">
-        <v>3.329480224491155</v>
+        <v>3.329480224491156</v>
       </c>
       <c r="AW42" s="437" t="n">
         <v>3.816836560333535</v>
@@ -10507,10 +10507,10 @@
         <v>513.0172706350147</v>
       </c>
       <c r="BC42" s="440" t="n">
-        <v>477.947185815252</v>
+        <v>477.9471858152521</v>
       </c>
       <c r="BD42" s="440" t="n">
-        <v>543.2269787287353</v>
+        <v>543.226978728735</v>
       </c>
       <c r="BE42" s="440" t="n">
         <v>671.0532466772449</v>
@@ -10525,7 +10525,7 @@
         <v>3.191809719386966</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>3.599046503630638</v>
+        <v>3.599046503630636</v>
       </c>
       <c r="BJ42" s="443" t="n">
         <v>4.466935733771606</v>
@@ -10540,7 +10540,7 @@
         <v>3.191809719386966</v>
       </c>
       <c r="BN42" s="443" t="n">
-        <v>3.599046503630638</v>
+        <v>3.599046503630636</v>
       </c>
       <c r="BO42" s="443" t="n">
         <v>4.466935733771606</v>
@@ -10554,49 +10554,49 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>508.8382780749861</v>
+        <v>508.8382780749859</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>473.5212455639916</v>
+        <v>473.5212455639915</v>
       </c>
       <c r="BU42" s="440" t="n">
-        <v>538.154970815757</v>
+        <v>538.1549708157565</v>
       </c>
       <c r="BV42" s="440" t="n">
         <v>665.3534253482376</v>
       </c>
       <c r="BW42" s="441" t="n">
-        <v>893.6587861463256</v>
+        <v>893.6587861463254</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>3.22255614955571</v>
+        <v>3.222556149555709</v>
       </c>
       <c r="BY42" s="443" t="n">
         <v>3.178242892004288</v>
       </c>
       <c r="BZ42" s="443" t="n">
-        <v>3.583114384120007</v>
+        <v>3.583114384120005</v>
       </c>
       <c r="CA42" s="443" t="n">
         <v>4.450508379994656</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>5.896886601481765</v>
+        <v>5.896886601481764</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>3.22255614955571</v>
+        <v>3.222556149555709</v>
       </c>
       <c r="CD42" s="443" t="n">
         <v>3.178242892004288</v>
       </c>
       <c r="CE42" s="443" t="n">
-        <v>3.583114384120007</v>
+        <v>3.583114384120005</v>
       </c>
       <c r="CF42" s="443" t="n">
         <v>4.450508379994656</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>5.896886601481765</v>
+        <v>5.896886601481764</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="C47" s="454" t="n">
-        <v>27688.91534564878</v>
+        <v>27688.91534564877</v>
       </c>
       <c r="D47" s="375" t="n">
         <v>26394.83127934691</v>
@@ -11243,13 +11243,13 @@
         <v>25661.46998969722</v>
       </c>
       <c r="F47" s="375" t="n">
-        <v>23172.33588802851</v>
+        <v>23172.3358880285</v>
       </c>
       <c r="G47" s="455" t="n">
         <v>22594.86520251621</v>
       </c>
       <c r="H47" s="371" t="n">
-        <v>393.1457032283224</v>
+        <v>393.1457032283222</v>
       </c>
       <c r="I47" s="372" t="n">
         <v>458.1742202048313</v>
@@ -11264,7 +11264,7 @@
         <v>496.3949189621663</v>
       </c>
       <c r="M47" s="371" t="n">
-        <v>393.1457032283224</v>
+        <v>393.1457032283222</v>
       </c>
       <c r="N47" s="372" t="n">
         <v>458.1742202048313</v>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="T47" s="374" t="n">
-        <v>27688.91534564878</v>
+        <v>27688.91534564877</v>
       </c>
       <c r="U47" s="375" t="n">
         <v>26394.83127934691</v>
@@ -11293,13 +11293,13 @@
         <v>25661.46998969722</v>
       </c>
       <c r="W47" s="375" t="n">
-        <v>23172.33588802851</v>
+        <v>23172.3358880285</v>
       </c>
       <c r="X47" s="376" t="n">
         <v>22594.86520251621</v>
       </c>
       <c r="Y47" s="377" t="n">
-        <v>393.1457032283224</v>
+        <v>393.1457032283222</v>
       </c>
       <c r="Z47" s="372" t="n">
         <v>458.1742202048313</v>
@@ -11314,7 +11314,7 @@
         <v>496.3949189621663</v>
       </c>
       <c r="AD47" s="377" t="n">
-        <v>393.1457032283224</v>
+        <v>393.1457032283222</v>
       </c>
       <c r="AE47" s="372" t="n">
         <v>458.1742202048313</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="AK47" s="379" t="n">
-        <v>27688.91534564878</v>
+        <v>27688.91534564877</v>
       </c>
       <c r="AL47" s="375" t="n">
         <v>26394.83127934691</v>
@@ -11343,13 +11343,13 @@
         <v>25661.46998969722</v>
       </c>
       <c r="AN47" s="375" t="n">
-        <v>23172.33588802851</v>
+        <v>23172.3358880285</v>
       </c>
       <c r="AO47" s="456" t="n">
         <v>22594.86520251621</v>
       </c>
       <c r="AP47" s="381" t="n">
-        <v>393.1457032283223</v>
+        <v>393.1457032283222</v>
       </c>
       <c r="AQ47" s="372" t="n">
         <v>458.1742202048313</v>
@@ -11358,13 +11358,13 @@
         <v>491.0032818933322</v>
       </c>
       <c r="AS47" s="372" t="n">
-        <v>513.8423851917196</v>
+        <v>513.8423851917195</v>
       </c>
       <c r="AT47" s="382" t="n">
         <v>496.3949189621664</v>
       </c>
       <c r="AU47" s="372" t="n">
-        <v>393.1457032283223</v>
+        <v>393.1457032283222</v>
       </c>
       <c r="AV47" s="372" t="n">
         <v>458.1742202048313</v>
@@ -11373,7 +11373,7 @@
         <v>491.0032818933322</v>
       </c>
       <c r="AX47" s="372" t="n">
-        <v>513.8423851917196</v>
+        <v>513.8423851917195</v>
       </c>
       <c r="AY47" s="382" t="n">
         <v>496.3949189621664</v>
@@ -11393,7 +11393,7 @@
         <v>28353.20991412725</v>
       </c>
       <c r="BE47" s="375" t="n">
-        <v>26295.34737692758</v>
+        <v>26295.34737692759</v>
       </c>
       <c r="BF47" s="392" t="n">
         <v>26290.66972712829</v>
@@ -11408,7 +11408,7 @@
         <v>542.5066890414452</v>
       </c>
       <c r="BJ47" s="372" t="n">
-        <v>583.0946038800432</v>
+        <v>583.0946038800435</v>
       </c>
       <c r="BK47" s="387" t="n">
         <v>577.5894103234391</v>
@@ -11423,7 +11423,7 @@
         <v>542.5066890414452</v>
       </c>
       <c r="BO47" s="389" t="n">
-        <v>583.0946038800432</v>
+        <v>583.0946038800435</v>
       </c>
       <c r="BP47" s="390" t="n">
         <v>577.5894103234391</v>
@@ -11434,10 +11434,10 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>28471.69447884347</v>
+        <v>28471.69447884346</v>
       </c>
       <c r="BT47" s="375" t="n">
-        <v>28075.36223424783</v>
+        <v>28075.36223424782</v>
       </c>
       <c r="BU47" s="375" t="n">
         <v>28127.48764370188</v>
@@ -11446,37 +11446,37 @@
         <v>26068.54881481979</v>
       </c>
       <c r="BW47" s="392" t="n">
-        <v>26060.96276865009</v>
+        <v>26060.96276865008</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>407.9991796458245</v>
+        <v>407.9991796458243</v>
       </c>
       <c r="BY47" s="372" t="n">
-        <v>492.2486978246035</v>
+        <v>492.2486978246034</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>544.0612888046369</v>
+        <v>544.0612888046368</v>
       </c>
       <c r="CA47" s="372" t="n">
-        <v>585.1531932803401</v>
+        <v>585.15319328034</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>579.3291513375884</v>
+        <v>579.3291513375882</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>407.9991796458245</v>
+        <v>407.9991796458243</v>
       </c>
       <c r="CD47" s="389" t="n">
-        <v>492.2486978246035</v>
+        <v>492.2486978246034</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>544.0612888046369</v>
+        <v>544.0612888046368</v>
       </c>
       <c r="CF47" s="389" t="n">
         <v>585.15319328034</v>
       </c>
       <c r="CG47" s="390" t="n">
-        <v>579.3291513375883</v>
+        <v>579.3291513375882</v>
       </c>
     </row>
     <row r="48">
@@ -11610,7 +11610,7 @@
         <v>1263.985654623993</v>
       </c>
       <c r="AS48" s="372" t="n">
-        <v>1389.280891669854</v>
+        <v>1389.280891669853</v>
       </c>
       <c r="AT48" s="382" t="n">
         <v>1434.400058350325</v>
@@ -11625,7 +11625,7 @@
         <v>1263.985654623993</v>
       </c>
       <c r="AX48" s="372" t="n">
-        <v>1389.280891669854</v>
+        <v>1389.280891669853</v>
       </c>
       <c r="AY48" s="382" t="n">
         <v>1434.400058350325</v>
@@ -11654,7 +11654,7 @@
         <v>1099.053531110346</v>
       </c>
       <c r="BH48" s="372" t="n">
-        <v>1292.420601949609</v>
+        <v>1292.42060194961</v>
       </c>
       <c r="BI48" s="372" t="n">
         <v>1391.203099308574</v>
@@ -11663,13 +11663,13 @@
         <v>1569.506793418033</v>
       </c>
       <c r="BK48" s="387" t="n">
-        <v>1661.124127814412</v>
+        <v>1661.124127814413</v>
       </c>
       <c r="BL48" s="386" t="n">
         <v>1099.053531110346</v>
       </c>
       <c r="BM48" s="372" t="n">
-        <v>1292.420601949609</v>
+        <v>1292.42060194961</v>
       </c>
       <c r="BN48" s="372" t="n">
         <v>1391.203099308574</v>
@@ -11678,7 +11678,7 @@
         <v>1569.506793418033</v>
       </c>
       <c r="BP48" s="387" t="n">
-        <v>1661.124127814412</v>
+        <v>1661.124127814413</v>
       </c>
       <c r="BR48" s="101" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>32903.13302468607</v>
       </c>
       <c r="BW48" s="392" t="n">
-        <v>35414.66909960086</v>
+        <v>35414.66909960087</v>
       </c>
       <c r="BX48" s="386" t="n">
         <v>1100.128962731242</v>
@@ -11707,7 +11707,7 @@
         <v>1293.592944167114</v>
       </c>
       <c r="BZ48" s="372" t="n">
-        <v>1392.462090817564</v>
+        <v>1392.462090817563</v>
       </c>
       <c r="CA48" s="372" t="n">
         <v>1571.143934548078</v>
@@ -11722,13 +11722,13 @@
         <v>1293.592944167114</v>
       </c>
       <c r="CE48" s="372" t="n">
-        <v>1392.462090817564</v>
+        <v>1392.462090817563</v>
       </c>
       <c r="CF48" s="372" t="n">
         <v>1571.143934548078</v>
       </c>
       <c r="CG48" s="387" t="n">
-        <v>1662.768847830453</v>
+        <v>1662.768847830454</v>
       </c>
     </row>
     <row r="49">
@@ -11738,25 +11738,25 @@
         </is>
       </c>
       <c r="C49" s="454" t="n">
-        <v>52457.69518490259</v>
+        <v>52457.6951849026</v>
       </c>
       <c r="D49" s="375" t="n">
         <v>61827.42112122307</v>
       </c>
       <c r="E49" s="375" t="n">
-        <v>71387.52224502443</v>
+        <v>71387.52224502442</v>
       </c>
       <c r="F49" s="375" t="n">
         <v>83721.33754615423</v>
       </c>
       <c r="G49" s="455" t="n">
-        <v>88532.13633182229</v>
+        <v>88532.13633182227</v>
       </c>
       <c r="H49" s="371" t="n">
-        <v>952.7165781003768</v>
+        <v>952.7165781003769</v>
       </c>
       <c r="I49" s="372" t="n">
-        <v>1003.202905045392</v>
+        <v>1003.202905045393</v>
       </c>
       <c r="J49" s="372" t="n">
         <v>1047.238095607992</v>
@@ -11768,10 +11768,10 @@
         <v>1098.696127887951</v>
       </c>
       <c r="M49" s="371" t="n">
-        <v>952.7165781003768</v>
+        <v>952.7165781003769</v>
       </c>
       <c r="N49" s="372" t="n">
-        <v>1003.202905045392</v>
+        <v>1003.202905045393</v>
       </c>
       <c r="O49" s="372" t="n">
         <v>1047.238095607992</v>
@@ -11788,25 +11788,25 @@
         </is>
       </c>
       <c r="T49" s="374" t="n">
-        <v>52457.69518490259</v>
+        <v>52457.6951849026</v>
       </c>
       <c r="U49" s="375" t="n">
         <v>61827.42112122307</v>
       </c>
       <c r="V49" s="375" t="n">
-        <v>71387.52224502443</v>
+        <v>71387.52224502442</v>
       </c>
       <c r="W49" s="375" t="n">
         <v>83721.33754615423</v>
       </c>
       <c r="X49" s="376" t="n">
-        <v>88532.13633182229</v>
+        <v>88532.13633182227</v>
       </c>
       <c r="Y49" s="377" t="n">
-        <v>952.7165781003768</v>
+        <v>952.7165781003769</v>
       </c>
       <c r="Z49" s="372" t="n">
-        <v>1003.202905045392</v>
+        <v>1003.202905045393</v>
       </c>
       <c r="AA49" s="372" t="n">
         <v>1047.238095607992</v>
@@ -11818,10 +11818,10 @@
         <v>1098.696127887951</v>
       </c>
       <c r="AD49" s="377" t="n">
-        <v>952.7165781003768</v>
+        <v>952.7165781003769</v>
       </c>
       <c r="AE49" s="372" t="n">
-        <v>1003.202905045392</v>
+        <v>1003.202905045393</v>
       </c>
       <c r="AF49" s="372" t="n">
         <v>1047.238095607992</v>
@@ -11838,22 +11838,22 @@
         </is>
       </c>
       <c r="AK49" s="379" t="n">
-        <v>54691.44737735791</v>
+        <v>54691.4473773579</v>
       </c>
       <c r="AL49" s="375" t="n">
         <v>63992.30148005931</v>
       </c>
       <c r="AM49" s="375" t="n">
-        <v>73171.07259659997</v>
+        <v>73171.07259659996</v>
       </c>
       <c r="AN49" s="375" t="n">
-        <v>84894.4296458653</v>
+        <v>84894.42964586528</v>
       </c>
       <c r="AO49" s="456" t="n">
-        <v>88684.57737118934</v>
+        <v>88684.57737118931</v>
       </c>
       <c r="AP49" s="381" t="n">
-        <v>916.5022884360633</v>
+        <v>916.5022884360632</v>
       </c>
       <c r="AQ49" s="372" t="n">
         <v>970.2682015072126</v>
@@ -11868,7 +11868,7 @@
         <v>1100.587942393094</v>
       </c>
       <c r="AU49" s="372" t="n">
-        <v>916.5022884360633</v>
+        <v>916.5022884360632</v>
       </c>
       <c r="AV49" s="372" t="n">
         <v>970.2682015072126</v>
@@ -11897,13 +11897,13 @@
         <v>80423.5438285995</v>
       </c>
       <c r="BE49" s="375" t="n">
-        <v>95909.42326451193</v>
+        <v>95909.42326451195</v>
       </c>
       <c r="BF49" s="392" t="n">
         <v>102665.5142198498</v>
       </c>
       <c r="BG49" s="386" t="n">
-        <v>946.3195546081115</v>
+        <v>946.3195546081114</v>
       </c>
       <c r="BH49" s="372" t="n">
         <v>1033.127467198279</v>
@@ -11912,13 +11912,13 @@
         <v>1113.210326224902</v>
       </c>
       <c r="BJ49" s="372" t="n">
-        <v>1207.645015158824</v>
+        <v>1207.645015158825</v>
       </c>
       <c r="BK49" s="387" t="n">
         <v>1274.09331362119</v>
       </c>
       <c r="BL49" s="386" t="n">
-        <v>946.3195546081115</v>
+        <v>946.3195546081114</v>
       </c>
       <c r="BM49" s="372" t="n">
         <v>1033.127467198279</v>
@@ -11927,7 +11927,7 @@
         <v>1113.210326224902</v>
       </c>
       <c r="BO49" s="372" t="n">
-        <v>1207.645015158824</v>
+        <v>1207.645015158825</v>
       </c>
       <c r="BP49" s="387" t="n">
         <v>1274.09331362119</v>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="BS49" s="391" t="n">
-        <v>56440.48883384247</v>
+        <v>56440.48883384246</v>
       </c>
       <c r="BT49" s="375" t="n">
         <v>68103.75309619487</v>
@@ -11947,13 +11947,13 @@
         <v>80385.61208921993</v>
       </c>
       <c r="BV49" s="375" t="n">
-        <v>95866.80313029894</v>
+        <v>95866.80313029897</v>
       </c>
       <c r="BW49" s="392" t="n">
         <v>102620.0729552573</v>
       </c>
       <c r="BX49" s="386" t="n">
-        <v>947.0605786236082</v>
+        <v>947.0605786236081</v>
       </c>
       <c r="BY49" s="372" t="n">
         <v>1033.849289750276</v>
@@ -11965,10 +11965,10 @@
         <v>1208.316346220492</v>
       </c>
       <c r="CB49" s="387" t="n">
-        <v>1274.779506932834</v>
+        <v>1274.779506932835</v>
       </c>
       <c r="CC49" s="386" t="n">
-        <v>947.0605786236081</v>
+        <v>947.060578623608</v>
       </c>
       <c r="CD49" s="372" t="n">
         <v>1033.849289750276</v>
@@ -11980,7 +11980,7 @@
         <v>1208.316346220492</v>
       </c>
       <c r="CG49" s="387" t="n">
-        <v>1274.779506932834</v>
+        <v>1274.779506932835</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" thickBot="1">
@@ -12143,7 +12143,7 @@
         <v>1602.6497825137</v>
       </c>
       <c r="BC50" s="420" t="n">
-        <v>1836.435993649659</v>
+        <v>1836.435993649658</v>
       </c>
       <c r="BD50" s="420" t="n">
         <v>2104.724147440693</v>
@@ -12190,49 +12190,49 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>1592.860731220918</v>
+        <v>1592.860731220917</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>1825.218966490081</v>
+        <v>1825.21896649008</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>2091.868405118663</v>
+        <v>2091.868405118662</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>2338.912036624588</v>
+        <v>2338.912036624587</v>
       </c>
       <c r="BW50" s="421" t="n">
-        <v>2607.845644359087</v>
+        <v>2607.845644359086</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>367.9492727259787</v>
+        <v>367.9492727259786</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>410.9473790975439</v>
+        <v>410.9473790975438</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>457.0923312475085</v>
+        <v>457.0923312475084</v>
       </c>
       <c r="CA50" s="417" t="n">
-        <v>500.9150699099199</v>
+        <v>500.9150699099197</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>547.4100692171795</v>
+        <v>547.4100692171792</v>
       </c>
       <c r="CC50" s="417" t="n">
         <v>367.9492727259787</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>410.9473790975439</v>
+        <v>410.9473790975437</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>457.0923312475085</v>
+        <v>457.0923312475084</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>500.9150699099199</v>
+        <v>500.9150699099197</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>547.4100692171794</v>
+        <v>547.4100692171793</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12266,10 +12266,10 @@
         <v>861.795361488344</v>
       </c>
       <c r="K51" s="427" t="n">
-        <v>937.1390569605106</v>
+        <v>937.1390569605104</v>
       </c>
       <c r="L51" s="428" t="n">
-        <v>946.3352509523446</v>
+        <v>946.3352509523445</v>
       </c>
       <c r="M51" s="427" t="n">
         <v>697.4001541731939</v>
@@ -12281,10 +12281,10 @@
         <v>861.795361488344</v>
       </c>
       <c r="P51" s="427" t="n">
-        <v>937.1390569605106</v>
+        <v>937.1390569605104</v>
       </c>
       <c r="Q51" s="428" t="n">
-        <v>946.3352509523446</v>
+        <v>946.3352509523445</v>
       </c>
       <c r="S51" s="143" t="inlineStr">
         <is>
@@ -12307,34 +12307,34 @@
         <v>144078.6211732953</v>
       </c>
       <c r="Y51" s="432" t="n">
-        <v>697.4001541731941</v>
+        <v>697.400154173194</v>
       </c>
       <c r="Z51" s="433" t="n">
         <v>799.1487400388886</v>
       </c>
       <c r="AA51" s="433" t="n">
-        <v>861.795361488344</v>
+        <v>861.7953614883439</v>
       </c>
       <c r="AB51" s="433" t="n">
         <v>937.1390569605106</v>
       </c>
       <c r="AC51" s="434" t="n">
-        <v>946.3352509523446</v>
+        <v>946.3352509523445</v>
       </c>
       <c r="AD51" s="433" t="n">
-        <v>697.4001541731941</v>
+        <v>697.400154173194</v>
       </c>
       <c r="AE51" s="433" t="n">
         <v>799.1487400388886</v>
       </c>
       <c r="AF51" s="433" t="n">
-        <v>861.795361488344</v>
+        <v>861.7953614883439</v>
       </c>
       <c r="AG51" s="433" t="n">
         <v>937.1390569605106</v>
       </c>
       <c r="AH51" s="434" t="n">
-        <v>946.3352509523446</v>
+        <v>946.3352509523445</v>
       </c>
       <c r="AJ51" s="150" t="inlineStr">
         <is>
@@ -12351,40 +12351,40 @@
         <v>128346.0277352026</v>
       </c>
       <c r="AN51" s="408" t="n">
-        <v>139374.8940333804</v>
+        <v>139374.8940333803</v>
       </c>
       <c r="AO51" s="409" t="n">
-        <v>144231.0622126624</v>
+        <v>144231.0622126623</v>
       </c>
       <c r="AP51" s="436" t="n">
-        <v>691.2057207029316</v>
+        <v>691.2057207029313</v>
       </c>
       <c r="AQ51" s="437" t="n">
         <v>790.5340079754284</v>
       </c>
       <c r="AR51" s="437" t="n">
-        <v>850.3320719752526</v>
+        <v>850.3320719752525</v>
       </c>
       <c r="AS51" s="437" t="n">
-        <v>927.763478727014</v>
+        <v>927.7634787270138</v>
       </c>
       <c r="AT51" s="438" t="n">
-        <v>947.336512125377</v>
+        <v>947.3365121253768</v>
       </c>
       <c r="AU51" s="437" t="n">
-        <v>691.2057207029316</v>
+        <v>691.2057207029313</v>
       </c>
       <c r="AV51" s="437" t="n">
         <v>790.5340079754284</v>
       </c>
       <c r="AW51" s="437" t="n">
-        <v>850.3320719752526</v>
+        <v>850.3320719752525</v>
       </c>
       <c r="AX51" s="437" t="n">
-        <v>927.763478727014</v>
+        <v>927.7634787270138</v>
       </c>
       <c r="AY51" s="438" t="n">
-        <v>947.336512125377</v>
+        <v>947.3365121253768</v>
       </c>
       <c r="BA51" s="155" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>843.753654488491</v>
       </c>
       <c r="BI51" s="443" t="n">
-        <v>935.9143921727225</v>
+        <v>935.9143921727223</v>
       </c>
       <c r="BJ51" s="443" t="n">
         <v>1048.838802157356</v>
@@ -12428,7 +12428,7 @@
         <v>843.753654488491</v>
       </c>
       <c r="BN51" s="443" t="n">
-        <v>935.9143921727225</v>
+        <v>935.9143921727223</v>
       </c>
       <c r="BO51" s="443" t="n">
         <v>1048.838802157356</v>
@@ -12457,34 +12457,34 @@
         <v>166703.5504678674</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>716.3950939260163</v>
+        <v>716.3950939260161</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>845.6707029612517</v>
+        <v>845.6707029612515</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>938.0802560177989</v>
+        <v>938.0802560177987</v>
       </c>
       <c r="CA51" s="417" t="n">
         <v>1051.349998170884</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>1100.008133319518</v>
+        <v>1100.008133319519</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>716.3950939260163</v>
+        <v>716.3950939260161</v>
       </c>
       <c r="CD51" s="417" t="n">
-        <v>845.6707029612517</v>
+        <v>845.6707029612515</v>
       </c>
       <c r="CE51" s="417" t="n">
-        <v>938.0802560177989</v>
+        <v>938.0802560177987</v>
       </c>
       <c r="CF51" s="417" t="n">
         <v>1051.349998170884</v>
       </c>
       <c r="CG51" s="418" t="n">
-        <v>1100.008133319518</v>
+        <v>1100.008133319519</v>
       </c>
     </row>
     <row r="52">
@@ -13653,28 +13653,28 @@
         <v>4951</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>0.6454387887317972</v>
+        <v>0.6454387887318001</v>
       </c>
       <c r="CX58" s="92" t="n">
-        <v>0.5738078228343186</v>
+        <v>0.5738078228343207</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>0.5642210685925358</v>
+        <v>0.5642210685925376</v>
       </c>
       <c r="CZ58" s="92" t="n">
-        <v>0.5462383402166368</v>
+        <v>0.5462383402166385</v>
       </c>
       <c r="DA58" s="93" t="n">
-        <v>0.5331966353622142</v>
+        <v>0.5331966353622157</v>
       </c>
       <c r="DC58" s="393" t="n">
-        <v>0.008301495101931693</v>
+        <v>0.008301495101931695</v>
       </c>
       <c r="DD58" s="394" t="n">
         <v>0.009097557460024304</v>
       </c>
       <c r="DE58" s="394" t="n">
-        <v>0.009932858034555739</v>
+        <v>0.009932858034555738</v>
       </c>
       <c r="DF58" s="394" t="n">
         <v>0.0112498614015952</v>
@@ -13962,19 +13962,19 @@
         <v>8082</v>
       </c>
       <c r="CW59" s="102" t="n">
-        <v>0.1037014274659339</v>
+        <v>0.1037014274659345</v>
       </c>
       <c r="CX59" s="103" t="n">
-        <v>0.08753547266332017</v>
+        <v>0.08753547266332064</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>0.08789084509257702</v>
+        <v>0.08789084509257751</v>
       </c>
       <c r="CZ59" s="103" t="n">
-        <v>0.08712431528231337</v>
+        <v>0.08712431528231385</v>
       </c>
       <c r="DA59" s="104" t="n">
-        <v>0.07552666082297219</v>
+        <v>0.07552666082297266</v>
       </c>
       <c r="DC59" s="396" t="n">
         <v>0.003014280688912939</v>
@@ -14271,19 +14271,19 @@
         <v>8129</v>
       </c>
       <c r="CW60" s="102" t="n">
-        <v>0.07866122670599514</v>
+        <v>0.07866122670599779</v>
       </c>
       <c r="CX60" s="103" t="n">
-        <v>0.07924287032825833</v>
+        <v>0.07924287032826124</v>
       </c>
       <c r="CY60" s="103" t="n">
-        <v>0.07910744016811658</v>
+        <v>0.07910744016811977</v>
       </c>
       <c r="CZ60" s="103" t="n">
-        <v>0.07939665637120069</v>
+        <v>0.0793966563712042</v>
       </c>
       <c r="DA60" s="104" t="n">
-        <v>0.07902089963056634</v>
+        <v>0.07902089963056991</v>
       </c>
       <c r="DC60" s="396" t="n">
         <v>0.001124083354606412</v>
@@ -14580,19 +14580,19 @@
         <v>972</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.01246836212360525</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157651</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989072</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069211</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>0.01372109225177184</v>
+        <v>0.01372109225177174</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0</v>
@@ -14889,19 +14889,19 @@
         <v>22134</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273376</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>0.7533784559974738</v>
+        <v>0.7533784559974792</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>0.7444004017231203</v>
+        <v>0.7444004017231256</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908487</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675301</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15754,10 +15754,10 @@
         </is>
       </c>
       <c r="BS67" s="236" t="n">
-        <v>70.42914438165819</v>
+        <v>70.4291443816582</v>
       </c>
       <c r="BT67" s="237" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547347</v>
       </c>
       <c r="BU67" s="237" t="n">
         <v>52.26333711435105</v>
@@ -15772,7 +15772,7 @@
         <v>1.000000005469159</v>
       </c>
       <c r="BY67" s="463" t="n">
-        <v>0.9999999988686483</v>
+        <v>0.9999999988686485</v>
       </c>
       <c r="BZ67" s="463" t="n">
         <v>1.000000002211857</v>
@@ -15787,7 +15787,7 @@
         <v>69.7837055929264</v>
       </c>
       <c r="CD67" s="200" t="n">
-        <v>57.03491411263914</v>
+        <v>57.03491411263915</v>
       </c>
       <c r="CE67" s="200" t="n">
         <v>51.69911604575851</v>
@@ -16286,13 +16286,13 @@
         <v>65.9532090662488</v>
       </c>
       <c r="BU69" s="237" t="n">
-        <v>72.24469844336645</v>
+        <v>72.24469844336643</v>
       </c>
       <c r="BV69" s="237" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473452</v>
       </c>
       <c r="BW69" s="238" t="n">
-        <v>80.57927387179082</v>
+        <v>80.5792738717908</v>
       </c>
       <c r="BX69" s="462" t="n">
         <v>1.000000006592274</v>
@@ -16301,28 +16301,28 @@
         <v>1.00000000100569</v>
       </c>
       <c r="BZ69" s="463" t="n">
-        <v>1.000000006143738</v>
+        <v>1.000000006143737</v>
       </c>
       <c r="CA69" s="463" t="n">
         <v>1.000000004723198</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.9999999984073444</v>
+        <v>0.9999999984073442</v>
       </c>
       <c r="CC69" s="197" t="n">
-        <v>59.59543716616346</v>
+        <v>59.59543716616347</v>
       </c>
       <c r="CD69" s="190" t="n">
         <v>65.87396619592054</v>
       </c>
       <c r="CE69" s="190" t="n">
-        <v>72.16559100319833</v>
+        <v>72.16559100319832</v>
       </c>
       <c r="CF69" s="190" t="n">
         <v>79.33915971836332</v>
       </c>
       <c r="CG69" s="198" t="n">
-        <v>80.50025297216025</v>
+        <v>80.50025297216024</v>
       </c>
       <c r="CW69" s="465" t="n"/>
       <c r="CX69" s="465" t="n"/>
@@ -16815,7 +16815,7 @@
         <v>150.9363600673066</v>
       </c>
       <c r="BV71" s="272" t="n">
-        <v>150.2267519233178</v>
+        <v>150.2267519233179</v>
       </c>
       <c r="BW71" s="273" t="n">
         <v>152.2490274751186</v>
@@ -20987,19 +20987,19 @@
         <v>1303.538689354053</v>
       </c>
       <c r="AU96" s="379" t="n">
-        <v>66390.65769892576</v>
+        <v>66390.65769892574</v>
       </c>
       <c r="AV96" s="375" t="n">
-        <v>61769.41695598942</v>
+        <v>61769.41695598943</v>
       </c>
       <c r="AW96" s="375" t="n">
-        <v>62526.11635133829</v>
+        <v>62526.11635133828</v>
       </c>
       <c r="AX96" s="375" t="n">
         <v>58001.49964746024</v>
       </c>
       <c r="AY96" s="456" t="n">
-        <v>59334.37238636029</v>
+        <v>59334.37238636028</v>
       </c>
       <c r="BA96" s="83" t="inlineStr">
         <is>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>56692.45154007567</v>
+        <v>56692.45154007563</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>53152.45709114791</v>
+        <v>53152.45709114788</v>
       </c>
       <c r="DE96" s="375" t="n">
-        <v>54365.66030696152</v>
+        <v>54365.66030696148</v>
       </c>
       <c r="DF96" s="375" t="n">
-        <v>49985.42743288454</v>
+        <v>49985.42743288452</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>47629.93996227321</v>
+        <v>47629.93996227318</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21214,19 +21214,19 @@
         <v>3170.471572118063</v>
       </c>
       <c r="AU97" s="379" t="n">
-        <v>58598.88127559348</v>
+        <v>58598.88127559347</v>
       </c>
       <c r="AV97" s="375" t="n">
         <v>57407.08920022815</v>
       </c>
       <c r="AW97" s="375" t="n">
-        <v>60876.37537505453</v>
+        <v>60876.37537505452</v>
       </c>
       <c r="AX97" s="375" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085038</v>
       </c>
       <c r="AY97" s="456" t="n">
-        <v>67766.10007773868</v>
+        <v>67766.10007773869</v>
       </c>
       <c r="BA97" s="101" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>51410.76756020103</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>53321.8451024732</v>
+        <v>53321.84510247321</v>
       </c>
       <c r="DG97" s="392" t="n">
         <v>57463.98155283602</v>
@@ -21547,7 +21547,7 @@
         <v>128891.8287038646</v>
       </c>
       <c r="DE98" s="375" t="n">
-        <v>149628.6636626866</v>
+        <v>149628.6636626867</v>
       </c>
       <c r="DF98" s="375" t="n">
         <v>174895.0914295517</v>
@@ -21668,7 +21668,7 @@
         <v>3063.213788791743</v>
       </c>
       <c r="AU99" s="407" t="n">
-        <v>10750.99190393291</v>
+        <v>10750.9919039329</v>
       </c>
       <c r="AV99" s="458" t="n">
         <v>11640.00260232824</v>
@@ -21771,10 +21771,10 @@
         <v>8916.232863213503</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>9666.763954639384</v>
+        <v>9666.763954639382</v>
       </c>
       <c r="DE99" s="420" t="n">
-        <v>10532.06229950653</v>
+        <v>10532.06229950652</v>
       </c>
       <c r="DF99" s="420" t="n">
         <v>11358.94083284316</v>
@@ -22009,7 +22009,7 @@
         <v>289561.3047977526</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>309619.9738065999</v>
+        <v>309619.9738065998</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23138,19 +23138,19 @@
         <v>2366</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>0.6454387887317972</v>
+        <v>0.6454387887318001</v>
       </c>
       <c r="CX108" s="200" t="n">
-        <v>0.5738078228343186</v>
+        <v>0.5738078228343207</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>0.5642210685925358</v>
+        <v>0.5642210685925376</v>
       </c>
       <c r="CZ108" s="200" t="n">
-        <v>0.5462383402166368</v>
+        <v>0.5462383402166385</v>
       </c>
       <c r="DA108" s="201" t="n">
-        <v>0.5331966353622142</v>
+        <v>0.5331966353622157</v>
       </c>
     </row>
     <row r="109">
@@ -23433,19 +23433,19 @@
         <v>6058</v>
       </c>
       <c r="CW109" s="197" t="n">
-        <v>0.1037014274659339</v>
+        <v>0.1037014274659345</v>
       </c>
       <c r="CX109" s="190" t="n">
-        <v>0.08753547266332017</v>
+        <v>0.08753547266332064</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>0.08789084509257702</v>
+        <v>0.08789084509257751</v>
       </c>
       <c r="CZ109" s="190" t="n">
-        <v>0.08712431528231337</v>
+        <v>0.08712431528231385</v>
       </c>
       <c r="DA109" s="198" t="n">
-        <v>0.07552666082297219</v>
+        <v>0.07552666082297266</v>
       </c>
     </row>
     <row r="110">
@@ -23671,7 +23671,7 @@
         <v>67.39448310737303</v>
       </c>
       <c r="BX110" s="197" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="BY110" s="190" t="n">
         <v>100.5549145594557</v>
@@ -23728,19 +23728,19 @@
         <v>7686</v>
       </c>
       <c r="CW110" s="197" t="n">
-        <v>0.07866122670599514</v>
+        <v>0.07866122670599779</v>
       </c>
       <c r="CX110" s="190" t="n">
-        <v>0.07924287032825833</v>
+        <v>0.07924287032826124</v>
       </c>
       <c r="CY110" s="190" t="n">
-        <v>0.07910744016811658</v>
+        <v>0.07910744016811977</v>
       </c>
       <c r="CZ110" s="190" t="n">
-        <v>0.07939665637120069</v>
+        <v>0.0793966563712042</v>
       </c>
       <c r="DA110" s="198" t="n">
-        <v>0.07902089963056634</v>
+        <v>0.07902089963056991</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" thickBot="1">
@@ -24023,19 +24023,19 @@
         <v>1566</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.01246836212360525</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157651</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989072</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069211</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>0.01372109225177184</v>
+        <v>0.01372109225177174</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24318,19 +24318,19 @@
         <v>17676</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273376</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>0.7533784559974738</v>
+        <v>0.7533784559974792</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>0.7444004017231203</v>
+        <v>0.7444004017231256</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908487</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675301</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -25197,31 +25197,31 @@
         <v>0</v>
       </c>
       <c r="BX117" s="515" t="n">
-        <v>0.06819052146228914</v>
+        <v>0.06819052146228911</v>
       </c>
       <c r="BY117" s="461" t="n">
-        <v>0.07149065642823374</v>
+        <v>0.07149065642823371</v>
       </c>
       <c r="BZ117" s="461" t="n">
-        <v>0.0776010247917919</v>
+        <v>0.07760102479179189</v>
       </c>
       <c r="CA117" s="461" t="n">
-        <v>0.06265916910334453</v>
+        <v>0.06265916910334451</v>
       </c>
       <c r="CB117" s="516" t="n">
         <v>0</v>
       </c>
       <c r="CC117" s="199" t="n">
-        <v>7.181997748466757</v>
+        <v>7.181997748466754</v>
       </c>
       <c r="CD117" s="200" t="n">
-        <v>7.62241185586002</v>
+        <v>7.622411855860017</v>
       </c>
       <c r="CE117" s="200" t="n">
-        <v>8.039122839299147</v>
+        <v>8.039122839299145</v>
       </c>
       <c r="CF117" s="200" t="n">
-        <v>6.317177460038421</v>
+        <v>6.317177460038419</v>
       </c>
       <c r="CG117" s="201" t="n">
         <v>0</v>
@@ -26205,31 +26205,31 @@
         <v>0</v>
       </c>
       <c r="BX121" s="466" t="n">
-        <v>0.02389230806084189</v>
+        <v>0.02389230806084188</v>
       </c>
       <c r="BY121" s="467" t="n">
-        <v>0.02543908173114166</v>
+        <v>0.02543908173114165</v>
       </c>
       <c r="BZ121" s="467" t="n">
-        <v>0.02817940883021451</v>
+        <v>0.0281794088302145</v>
       </c>
       <c r="CA121" s="467" t="n">
-        <v>0.02339062032418742</v>
+        <v>0.02339062032418741</v>
       </c>
       <c r="CB121" s="468" t="n">
         <v>0</v>
       </c>
       <c r="CC121" s="212" t="n">
-        <v>7.181997748466757</v>
+        <v>7.181997748466754</v>
       </c>
       <c r="CD121" s="212" t="n">
-        <v>7.62241185586002</v>
+        <v>7.622411855860017</v>
       </c>
       <c r="CE121" s="212" t="n">
-        <v>8.039122839299147</v>
+        <v>8.039122839299145</v>
       </c>
       <c r="CF121" s="212" t="n">
-        <v>6.317177460038421</v>
+        <v>6.317177460038419</v>
       </c>
       <c r="CG121" s="213" t="n">
         <v>0</v>
@@ -27607,7 +27607,7 @@
         <v>0.3138684532643359</v>
       </c>
       <c r="CA128" s="463" t="n">
-        <v>0.3956794773945754</v>
+        <v>0.3956794773945753</v>
       </c>
       <c r="CB128" s="464" t="n">
         <v>0.4397051120728142</v>
@@ -29501,13 +29501,13 @@
         <v>589027.1056832182</v>
       </c>
       <c r="F141" s="425" t="n">
-        <v>726495.0525627602</v>
+        <v>726495.0525627601</v>
       </c>
       <c r="G141" s="426" t="n">
         <v>811994.5728673091</v>
       </c>
       <c r="H141" s="427" t="n">
-        <v>2893.401733095192</v>
+        <v>2893.401733095193</v>
       </c>
       <c r="I141" s="427" t="n">
         <v>2611.970298418244</v>
@@ -29536,13 +29536,13 @@
         <v>589027.1056832182</v>
       </c>
       <c r="W141" s="430" t="n">
-        <v>726495.0525627602</v>
+        <v>726495.0525627601</v>
       </c>
       <c r="X141" s="431" t="n">
         <v>811994.5728673091</v>
       </c>
       <c r="Y141" s="432" t="n">
-        <v>2893.401733095192</v>
+        <v>2893.401733095193</v>
       </c>
       <c r="Z141" s="433" t="n">
         <v>2611.970298418244</v>
@@ -30296,7 +30296,7 @@
         </is>
       </c>
       <c r="BS146" s="391" t="n">
-        <v>52269.06877845313</v>
+        <v>52269.06877845314</v>
       </c>
       <c r="BT146" s="375" t="n">
         <v>55718.66770437713</v>
@@ -30305,10 +30305,10 @@
         <v>56250.97381120856</v>
       </c>
       <c r="BV146" s="375" t="n">
-        <v>56875.80715475147</v>
+        <v>56875.80715475148</v>
       </c>
       <c r="BW146" s="392" t="n">
-        <v>53692.12532185482</v>
+        <v>53692.12532185483</v>
       </c>
       <c r="BX146" s="386" t="n">
         <v>496.2762703611106</v>
@@ -30320,25 +30320,25 @@
         <v>542.9862561556015</v>
       </c>
       <c r="CA146" s="372" t="n">
-        <v>564.1429009938104</v>
+        <v>564.1429009938105</v>
       </c>
       <c r="CB146" s="387" t="n">
-        <v>586.6102006092929</v>
+        <v>586.610200609293</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>608.4286029140143</v>
+        <v>608.428602914017</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>615.2501466925027</v>
+        <v>615.2501466925049</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>675.0153015009823</v>
+        <v>675.0153015009845</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>702.5569141655973</v>
+        <v>702.5569141655996</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>695.0424432280515</v>
+        <v>695.0424432280536</v>
       </c>
     </row>
     <row r="147">
@@ -30491,7 +30491,7 @@
         <v>102111.6538686104</v>
       </c>
       <c r="BT147" s="375" t="n">
-        <v>107673.7026526406</v>
+        <v>107673.7026526407</v>
       </c>
       <c r="BU147" s="375" t="n">
         <v>111125.8008844626</v>
@@ -30506,7 +30506,7 @@
         <v>1469.30442606657</v>
       </c>
       <c r="BY147" s="372" t="n">
-        <v>1543.36022698548</v>
+        <v>1543.360226985481</v>
       </c>
       <c r="BZ147" s="372" t="n">
         <v>1612.611146564166</v>
@@ -30518,19 +30518,19 @@
         <v>1770.037964168095</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>250.130168807665</v>
+        <v>250.1301688076664</v>
       </c>
       <c r="CX147" s="375" t="n">
-        <v>231.3018082564292</v>
+        <v>231.3018082564304</v>
       </c>
       <c r="CY147" s="375" t="n">
-        <v>245.0000209665502</v>
+        <v>245.0000209665515</v>
       </c>
       <c r="CZ147" s="375" t="n">
-        <v>260.9608164803847</v>
+        <v>260.9608164803861</v>
       </c>
       <c r="DA147" s="392" t="n">
-        <v>239.4551310762364</v>
+        <v>239.4551310762378</v>
       </c>
     </row>
     <row r="148">
@@ -30680,49 +30680,49 @@
         </is>
       </c>
       <c r="BS148" s="391" t="n">
-        <v>55227.55343047367</v>
+        <v>55227.55343047368</v>
       </c>
       <c r="BT148" s="375" t="n">
-        <v>56905.08867343717</v>
+        <v>56905.08867343719</v>
       </c>
       <c r="BU148" s="375" t="n">
         <v>56485.98781674325</v>
       </c>
       <c r="BV148" s="375" t="n">
-        <v>53080.79535181478</v>
+        <v>53080.79535181479</v>
       </c>
       <c r="BW148" s="392" t="n">
-        <v>56852.91156044105</v>
+        <v>56852.91156044107</v>
       </c>
       <c r="BX148" s="386" t="n">
         <v>539.6612028211453</v>
       </c>
       <c r="BY148" s="372" t="n">
-        <v>565.9105666067727</v>
+        <v>565.9105666067728</v>
       </c>
       <c r="BZ148" s="372" t="n">
         <v>590.4642594649166</v>
       </c>
       <c r="CA148" s="372" t="n">
-        <v>616.7228680517162</v>
+        <v>616.7228680517163</v>
       </c>
       <c r="CB148" s="387" t="n">
-        <v>662.0232146481646</v>
+        <v>662.0232146481648</v>
       </c>
       <c r="CW148" s="391" t="n">
-        <v>178.9675433728464</v>
+        <v>178.9675433728524</v>
       </c>
       <c r="CX148" s="375" t="n">
-        <v>190.4056747661365</v>
+        <v>190.4056747661435</v>
       </c>
       <c r="CY148" s="375" t="n">
-        <v>199.9229231739703</v>
+        <v>199.9229231739784</v>
       </c>
       <c r="CZ148" s="375" t="n">
-        <v>211.8809372705713</v>
+        <v>211.8809372705807</v>
       </c>
       <c r="DA148" s="392" t="n">
-        <v>227.409142113798</v>
+        <v>227.4091421138083</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" thickBot="1">
@@ -30902,19 +30902,19 @@
         <v>28770.818246126</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>30.87585814343995</v>
+        <v>30.87585814343973</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>33.4290144749875</v>
+        <v>33.42901447498725</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>36.329466859512</v>
+        <v>36.32946685951174</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>39.07530999124027</v>
+        <v>39.07530999123998</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>42.03063898291106</v>
+        <v>42.03063898291075</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -30924,22 +30924,22 @@
         </is>
       </c>
       <c r="C150" s="425" t="n">
-        <v>857961.4933376428</v>
+        <v>857961.4933376429</v>
       </c>
       <c r="D150" s="425" t="n">
-        <v>845360.4604822556</v>
+        <v>845360.4604822557</v>
       </c>
       <c r="E150" s="425" t="n">
         <v>756823.2926902301</v>
       </c>
       <c r="F150" s="425" t="n">
-        <v>727992.0158194148</v>
+        <v>727992.0158194149</v>
       </c>
       <c r="G150" s="426" t="n">
         <v>772786.3925708712</v>
       </c>
       <c r="H150" s="427" t="n">
-        <v>1850.302136523233</v>
+        <v>1850.302136523234</v>
       </c>
       <c r="I150" s="427" t="n">
         <v>2023.284531473399</v>
@@ -30959,22 +30959,22 @@
         </is>
       </c>
       <c r="T150" s="429" t="n">
-        <v>857961.4933376428</v>
+        <v>857961.4933376429</v>
       </c>
       <c r="U150" s="430" t="n">
-        <v>845360.4604822556</v>
+        <v>845360.4604822557</v>
       </c>
       <c r="V150" s="430" t="n">
         <v>756823.2926902301</v>
       </c>
       <c r="W150" s="430" t="n">
-        <v>727992.0158194148</v>
+        <v>727992.0158194149</v>
       </c>
       <c r="X150" s="431" t="n">
         <v>772786.3925708712</v>
       </c>
       <c r="Y150" s="432" t="n">
-        <v>1850.302136523233</v>
+        <v>1850.302136523234</v>
       </c>
       <c r="Z150" s="433" t="n">
         <v>2023.284531473399</v>
@@ -31094,19 +31094,19 @@
         <v>2516.171986450182</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>1068.402173237966</v>
+        <v>1068.402173237976</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>1070.386644190056</v>
+        <v>1070.386644190066</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>1156.267712501015</v>
+        <v>1156.267712501026</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>1214.473977907794</v>
+        <v>1214.473977907806</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>1203.937355400997</v>
+        <v>1203.93735540101</v>
       </c>
     </row>
     <row r="151">
@@ -38461,34 +38461,34 @@
         <v>0</v>
       </c>
       <c r="AP190" s="194" t="n">
-        <v>70.42914438165815</v>
+        <v>70.42914438165812</v>
       </c>
       <c r="AQ190" s="179" t="n">
-        <v>57.60872193547348</v>
+        <v>57.60872193547345</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>52.26333711435106</v>
+        <v>52.26333711435099</v>
       </c>
       <c r="AS190" s="179" t="n">
-        <v>45.09619353366105</v>
+        <v>45.09619353366108</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>45.51792185462425</v>
+        <v>45.51792185462432</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>70.42914438165815</v>
+        <v>70.42914438165812</v>
       </c>
       <c r="AV190" s="190" t="n">
-        <v>57.60872193547348</v>
+        <v>57.60872193547345</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>52.26333711435106</v>
+        <v>52.26333711435099</v>
       </c>
       <c r="AX190" s="190" t="n">
-        <v>45.09619353366105</v>
+        <v>45.09619353366108</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>45.51792185462428</v>
+        <v>45.51792185462432</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38511,34 +38511,34 @@
         <v>0</v>
       </c>
       <c r="BG190" s="197" t="n">
-        <v>70.42914438165815</v>
+        <v>70.42914438165812</v>
       </c>
       <c r="BH190" s="190" t="n">
-        <v>57.60872193547348</v>
+        <v>57.60872193547345</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>52.26333711435106</v>
+        <v>52.26333711435099</v>
       </c>
       <c r="BJ190" s="190" t="n">
-        <v>45.09619353366105</v>
+        <v>45.09619353366108</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>45.51792185462425</v>
+        <v>45.51792185462432</v>
       </c>
       <c r="BL190" s="199" t="n">
-        <v>70.42914438165815</v>
+        <v>70.42914438165812</v>
       </c>
       <c r="BM190" s="200" t="n">
-        <v>57.60872193547348</v>
+        <v>57.60872193547345</v>
       </c>
       <c r="BN190" s="200" t="n">
-        <v>52.26333711435106</v>
+        <v>52.26333711435099</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>45.09619353366105</v>
+        <v>45.09619353366108</v>
       </c>
       <c r="BP190" s="201" t="n">
-        <v>45.51792185462425</v>
+        <v>45.51792185462432</v>
       </c>
       <c r="BR190" s="83" t="inlineStr">
         <is>
@@ -38561,34 +38561,34 @@
         <v>0</v>
       </c>
       <c r="BX190" s="197" t="n">
-        <v>69.78370559292635</v>
+        <v>69.78370559292632</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>57.03491411263916</v>
+        <v>57.03491411263914</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>51.69911604575852</v>
+        <v>51.69911604575845</v>
       </c>
       <c r="CA190" s="190" t="n">
-        <v>44.54995519344441</v>
+        <v>44.54995519344444</v>
       </c>
       <c r="CB190" s="198" t="n">
-        <v>44.98472521926203</v>
+        <v>44.9847252192621</v>
       </c>
       <c r="CC190" s="199" t="n">
-        <v>69.78370559292635</v>
+        <v>69.78370559292632</v>
       </c>
       <c r="CD190" s="200" t="n">
-        <v>57.03491411263916</v>
+        <v>57.03491411263914</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>51.69911604575852</v>
+        <v>51.69911604575845</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>44.54995519344441</v>
+        <v>44.54995519344444</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>44.98472521926203</v>
+        <v>44.9847252192621</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>0</v>
@@ -38618,34 +38618,34 @@
         <v>4951</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>0.6454387887317972</v>
+        <v>0.6454387887317998</v>
       </c>
       <c r="CX190" s="92" t="n">
-        <v>0.5738078228343186</v>
+        <v>0.5738078228343207</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>0.5642210685925358</v>
+        <v>0.5642210685925376</v>
       </c>
       <c r="CZ190" s="92" t="n">
-        <v>0.5462383402166368</v>
+        <v>0.5462383402166385</v>
       </c>
       <c r="DA190" s="93" t="n">
-        <v>0.5331966353622142</v>
+        <v>0.5331966353622157</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.008301495056945583</v>
+        <v>0.008301495056945586</v>
       </c>
       <c r="DD190" s="394" t="n">
-        <v>0.00909755747021432</v>
+        <v>0.009097557470214323</v>
       </c>
       <c r="DE190" s="394" t="n">
-        <v>0.009932858012822858</v>
+        <v>0.009932858012822871</v>
       </c>
       <c r="DF190" s="394" t="n">
-        <v>0.01124986151792982</v>
+        <v>0.01124986151792981</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.01085111771704302</v>
+        <v>0.010851117717043</v>
       </c>
     </row>
     <row r="191">
@@ -38773,31 +38773,31 @@
         <v>24.29450129484404</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>21.72553967537752</v>
+        <v>21.72553967537748</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>21.83867583929184</v>
+        <v>21.83867583929182</v>
       </c>
       <c r="AS191" s="179" t="n">
         <v>21.02927526959128</v>
       </c>
       <c r="AT191" s="195" t="n">
-        <v>21.37413930497723</v>
+        <v>21.37413930497722</v>
       </c>
       <c r="AU191" s="190" t="n">
         <v>24.29450129484404</v>
       </c>
       <c r="AV191" s="190" t="n">
-        <v>21.72553967537752</v>
+        <v>21.72553967537748</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>21.83867583929184</v>
+        <v>21.83867583929182</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>21.02927526959128</v>
+        <v>21.0292752695913</v>
       </c>
       <c r="AY191" s="196" t="n">
-        <v>21.37413930497723</v>
+        <v>21.37413930497722</v>
       </c>
       <c r="BA191" s="101" t="inlineStr">
         <is>
@@ -38823,31 +38823,31 @@
         <v>24.29450129484404</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>21.72553967537752</v>
+        <v>21.72553967537748</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>21.83867583929184</v>
+        <v>21.83867583929182</v>
       </c>
       <c r="BJ191" s="190" t="n">
         <v>21.02927526959128</v>
       </c>
       <c r="BK191" s="198" t="n">
-        <v>21.37413930497723</v>
+        <v>21.37413930497722</v>
       </c>
       <c r="BL191" s="197" t="n">
         <v>24.29450129484404</v>
       </c>
       <c r="BM191" s="190" t="n">
-        <v>21.72553967537752</v>
+        <v>21.72553967537748</v>
       </c>
       <c r="BN191" s="190" t="n">
-        <v>21.83867583929184</v>
+        <v>21.83867583929182</v>
       </c>
       <c r="BO191" s="190" t="n">
         <v>21.02927526959128</v>
       </c>
       <c r="BP191" s="198" t="n">
-        <v>21.37413930497723</v>
+        <v>21.37413930497722</v>
       </c>
       <c r="BR191" s="101" t="inlineStr">
         <is>
@@ -38873,31 +38873,31 @@
         <v>24.1907998673781</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>21.6380042027142</v>
+        <v>21.63800420271416</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>21.75078499419926</v>
+        <v>21.75078499419925</v>
       </c>
       <c r="CA191" s="190" t="n">
         <v>20.94215095430897</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>21.29861264415426</v>
+        <v>21.29861264415425</v>
       </c>
       <c r="CC191" s="197" t="n">
         <v>24.1907998673781</v>
       </c>
       <c r="CD191" s="190" t="n">
-        <v>21.6380042027142</v>
+        <v>21.63800420271416</v>
       </c>
       <c r="CE191" s="190" t="n">
-        <v>21.75078499419926</v>
+        <v>21.75078499419925</v>
       </c>
       <c r="CF191" s="190" t="n">
         <v>20.94215095430897</v>
       </c>
       <c r="CG191" s="198" t="n">
-        <v>21.29861264415426</v>
+        <v>21.29861264415425</v>
       </c>
       <c r="CI191" s="197" t="n">
         <v>0</v>
@@ -38927,34 +38927,34 @@
         <v>8082</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>0.1037014274659339</v>
+        <v>0.1037014274659345</v>
       </c>
       <c r="CX191" s="103" t="n">
-        <v>0.08753547266332015</v>
+        <v>0.08753547266332064</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>0.08789084509257702</v>
+        <v>0.08789084509257751</v>
       </c>
       <c r="CZ191" s="103" t="n">
-        <v>0.08712431528231337</v>
+        <v>0.08712431528231383</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>0.07552666082297217</v>
+        <v>0.07552666082297264</v>
       </c>
       <c r="DC191" s="396" t="n">
         <v>0.003014280652330888</v>
       </c>
       <c r="DD191" s="397" t="n">
-        <v>0.002774916966255237</v>
+        <v>0.002774916966255243</v>
       </c>
       <c r="DE191" s="397" t="n">
-        <v>0.002770316402479111</v>
+        <v>0.002770316402479113</v>
       </c>
       <c r="DF191" s="397" t="n">
         <v>0.002888767623633596</v>
       </c>
       <c r="DG191" s="398" t="n">
-        <v>0.002279319615990404</v>
+        <v>0.002279319615990406</v>
       </c>
     </row>
     <row r="192">
@@ -39079,10 +39079,10 @@
         <v>0</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>59.67409839286945</v>
+        <v>59.67409839286942</v>
       </c>
       <c r="AQ192" s="179" t="n">
-        <v>65.95320906624883</v>
+        <v>65.95320906624882</v>
       </c>
       <c r="AR192" s="179" t="n">
         <v>72.2446984433664</v>
@@ -39091,13 +39091,13 @@
         <v>79.41855637473452</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>80.57927387179082</v>
+        <v>80.57927387179086</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>59.67409839286945</v>
+        <v>59.67409839286942</v>
       </c>
       <c r="AV192" s="190" t="n">
-        <v>65.95320906624883</v>
+        <v>65.95320906624882</v>
       </c>
       <c r="AW192" s="190" t="n">
         <v>72.2446984433664</v>
@@ -39106,7 +39106,7 @@
         <v>79.41855637473452</v>
       </c>
       <c r="AY192" s="196" t="n">
-        <v>80.57927387179082</v>
+        <v>80.57927387179086</v>
       </c>
       <c r="BA192" s="111" t="inlineStr">
         <is>
@@ -39129,10 +39129,10 @@
         <v>0</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>59.67409839286945</v>
+        <v>59.67409839286942</v>
       </c>
       <c r="BH192" s="190" t="n">
-        <v>65.95320906624883</v>
+        <v>65.95320906624882</v>
       </c>
       <c r="BI192" s="190" t="n">
         <v>72.2446984433664</v>
@@ -39141,13 +39141,13 @@
         <v>79.41855637473452</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>80.57927387179082</v>
+        <v>80.57927387179086</v>
       </c>
       <c r="BL192" s="197" t="n">
-        <v>59.67409839286945</v>
+        <v>59.67409839286942</v>
       </c>
       <c r="BM192" s="190" t="n">
-        <v>65.95320906624883</v>
+        <v>65.95320906624882</v>
       </c>
       <c r="BN192" s="190" t="n">
         <v>72.2446984433664</v>
@@ -39156,7 +39156,7 @@
         <v>79.41855637473452</v>
       </c>
       <c r="BP192" s="198" t="n">
-        <v>80.57927387179082</v>
+        <v>80.57927387179086</v>
       </c>
       <c r="BR192" s="111" t="inlineStr">
         <is>
@@ -39179,10 +39179,10 @@
         <v>0</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>59.59543716616346</v>
+        <v>59.59543716616343</v>
       </c>
       <c r="BY192" s="190" t="n">
-        <v>65.87396619592057</v>
+        <v>65.87396619592056</v>
       </c>
       <c r="BZ192" s="190" t="n">
         <v>72.16559100319829</v>
@@ -39191,13 +39191,13 @@
         <v>79.33915971836332</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>80.50025297216025</v>
+        <v>80.5002529721603</v>
       </c>
       <c r="CC192" s="197" t="n">
-        <v>59.59543716616346</v>
+        <v>59.59543716616343</v>
       </c>
       <c r="CD192" s="190" t="n">
-        <v>65.87396619592057</v>
+        <v>65.87396619592056</v>
       </c>
       <c r="CE192" s="190" t="n">
         <v>72.16559100319829</v>
@@ -39206,7 +39206,7 @@
         <v>79.33915971836332</v>
       </c>
       <c r="CG192" s="198" t="n">
-        <v>80.50025297216025</v>
+        <v>80.5002529721603</v>
       </c>
       <c r="CI192" s="197" t="n">
         <v>0</v>
@@ -39236,25 +39236,25 @@
         <v>8129</v>
       </c>
       <c r="CW192" s="102" t="n">
-        <v>0.07866122670599514</v>
+        <v>0.07866122670599779</v>
       </c>
       <c r="CX192" s="103" t="n">
-        <v>0.07924287032825833</v>
+        <v>0.07924287032826124</v>
       </c>
       <c r="CY192" s="103" t="n">
-        <v>0.07910744016811658</v>
+        <v>0.07910744016811977</v>
       </c>
       <c r="CZ192" s="103" t="n">
-        <v>0.07939665637120069</v>
+        <v>0.0793966563712042</v>
       </c>
       <c r="DA192" s="104" t="n">
-        <v>0.07902089963056634</v>
+        <v>0.07902089963056991</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.001124083347205914</v>
+        <v>0.001124083347205915</v>
       </c>
       <c r="DD192" s="397" t="n">
-        <v>0.001007404309347209</v>
+        <v>0.00100740430934721</v>
       </c>
       <c r="DE192" s="397" t="n">
         <v>0.000900895965300793</v>
@@ -39263,7 +39263,7 @@
         <v>0.000805627196036726</v>
       </c>
       <c r="DG192" s="398" t="n">
-        <v>0.000786563309120032</v>
+        <v>0.000786563309120031</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" thickBot="1">
@@ -39388,7 +39388,7 @@
         <v>0</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>4.341491071594501</v>
+        <v>4.341491071594504</v>
       </c>
       <c r="AQ193" s="207" t="n">
         <v>4.454283009634523</v>
@@ -39397,13 +39397,13 @@
         <v>4.589648670297318</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>4.682726745330951</v>
+        <v>4.682726745330946</v>
       </c>
       <c r="AT193" s="208" t="n">
         <v>4.777692443726263</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>4.341491071594501</v>
+        <v>4.341491071594504</v>
       </c>
       <c r="AV193" s="209" t="n">
         <v>4.454283009634523</v>
@@ -39412,7 +39412,7 @@
         <v>4.589648670297318</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>4.682726745330951</v>
+        <v>4.682726745330946</v>
       </c>
       <c r="AY193" s="210" t="n">
         <v>4.777692443726263</v>
@@ -39438,7 +39438,7 @@
         <v>0</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>4.341491071594501</v>
+        <v>4.341491071594504</v>
       </c>
       <c r="BH193" s="212" t="n">
         <v>4.454283009634523</v>
@@ -39447,13 +39447,13 @@
         <v>4.589648670297318</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>4.682726745330951</v>
+        <v>4.682726745330946</v>
       </c>
       <c r="BK193" s="213" t="n">
         <v>4.777692443726263</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>4.341491071594501</v>
+        <v>4.341491071594504</v>
       </c>
       <c r="BM193" s="212" t="n">
         <v>4.454283009634523</v>
@@ -39462,7 +39462,7 @@
         <v>4.589648670297318</v>
       </c>
       <c r="BO193" s="212" t="n">
-        <v>4.682726745330951</v>
+        <v>4.682726745330946</v>
       </c>
       <c r="BP193" s="213" t="n">
         <v>4.777692443726263</v>
@@ -39488,7 +39488,7 @@
         <v>0</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>4.329022709470896</v>
+        <v>4.329022709470899</v>
       </c>
       <c r="BY193" s="212" t="n">
         <v>4.441490719462946</v>
@@ -39497,13 +39497,13 @@
         <v>4.576467622427428</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>4.66927838581026</v>
+        <v>4.669278385810254</v>
       </c>
       <c r="CB193" s="213" t="n">
         <v>4.763971351474491</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>4.329022709470896</v>
+        <v>4.329022709470899</v>
       </c>
       <c r="CD193" s="212" t="n">
         <v>4.441490719462946</v>
@@ -39512,7 +39512,7 @@
         <v>4.576467622427428</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>4.66927838581026</v>
+        <v>4.669278385810254</v>
       </c>
       <c r="CG193" s="213" t="n">
         <v>4.763971351474491</v>
@@ -39545,19 +39545,19 @@
         <v>972</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.01246836212360525</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157651</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989072</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069211</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>0.01372109225177184</v>
+        <v>0.01372109225177174</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0</v>
@@ -39703,13 +39703,13 @@
         <v>149.7417536867343</v>
       </c>
       <c r="AR194" s="207" t="n">
-        <v>150.9363600673066</v>
+        <v>150.9363600673065</v>
       </c>
       <c r="AS194" s="207" t="n">
         <v>150.2267519233178</v>
       </c>
       <c r="AT194" s="208" t="n">
-        <v>152.2490274751186</v>
+        <v>152.2490274751187</v>
       </c>
       <c r="AU194" s="207" t="n">
         <v>158.7392351409661</v>
@@ -39718,13 +39718,13 @@
         <v>149.7417536867343</v>
       </c>
       <c r="AW194" s="207" t="n">
-        <v>150.9363600673066</v>
+        <v>150.9363600673065</v>
       </c>
       <c r="AX194" s="207" t="n">
         <v>150.2267519233178</v>
       </c>
       <c r="AY194" s="208" t="n">
-        <v>152.2490274751186</v>
+        <v>152.2490274751187</v>
       </c>
       <c r="BA194" s="155" t="inlineStr">
         <is>
@@ -39753,13 +39753,13 @@
         <v>149.7417536867343</v>
       </c>
       <c r="BI194" s="222" t="n">
-        <v>150.9363600673066</v>
+        <v>150.9363600673065</v>
       </c>
       <c r="BJ194" s="222" t="n">
         <v>150.2267519233178</v>
       </c>
       <c r="BK194" s="214" t="n">
-        <v>152.2490274751186</v>
+        <v>152.2490274751187</v>
       </c>
       <c r="BL194" s="222" t="n">
         <v>158.7392351409661</v>
@@ -39768,13 +39768,13 @@
         <v>149.7417536867343</v>
       </c>
       <c r="BN194" s="222" t="n">
-        <v>150.9363600673066</v>
+        <v>150.9363600673065</v>
       </c>
       <c r="BO194" s="222" t="n">
         <v>150.2267519233178</v>
       </c>
       <c r="BP194" s="214" t="n">
-        <v>152.2490274751186</v>
+        <v>152.2490274751187</v>
       </c>
       <c r="BR194" s="155" t="inlineStr">
         <is>
@@ -39800,31 +39800,31 @@
         <v>157.8989653359388</v>
       </c>
       <c r="BY194" s="222" t="n">
-        <v>148.9883752307369</v>
+        <v>148.9883752307368</v>
       </c>
       <c r="BZ194" s="222" t="n">
-        <v>150.1919596655835</v>
+        <v>150.1919596655834</v>
       </c>
       <c r="CA194" s="222" t="n">
         <v>149.500544251927</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>151.547562187051</v>
+        <v>151.5475621870511</v>
       </c>
       <c r="CC194" s="222" t="n">
         <v>157.8989653359388</v>
       </c>
       <c r="CD194" s="222" t="n">
-        <v>148.9883752307369</v>
+        <v>148.9883752307368</v>
       </c>
       <c r="CE194" s="222" t="n">
-        <v>150.1919596655835</v>
+        <v>150.1919596655834</v>
       </c>
       <c r="CF194" s="222" t="n">
         <v>149.500544251927</v>
       </c>
       <c r="CG194" s="214" t="n">
-        <v>151.547562187051</v>
+        <v>151.5475621870511</v>
       </c>
       <c r="CI194" s="349" t="n">
         <v>0</v>
@@ -39854,19 +39854,19 @@
         <v>22134</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273374</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>0.7533784559974737</v>
+        <v>0.7533784559974792</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>0.7444004017231203</v>
+        <v>0.7444004017231256</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908487</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675301</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40691,7 +40691,7 @@
         <v>1.000000000391096</v>
       </c>
       <c r="DA198" s="397" t="n">
-        <v>0.9999999992658873</v>
+        <v>0.9999999992658871</v>
       </c>
       <c r="DB198" s="397" t="n">
         <v>1.000000003205685</v>
@@ -40837,19 +40837,19 @@
         <v>0</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>70.42914438165815</v>
+        <v>70.42914438165812</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>57.60872193547348</v>
+        <v>57.60872193547345</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>52.26333711435106</v>
+        <v>52.26333711435099</v>
       </c>
       <c r="AX199" s="190" t="n">
-        <v>45.09619353366105</v>
+        <v>45.09619353366108</v>
       </c>
       <c r="AY199" s="196" t="n">
-        <v>45.51792185462425</v>
+        <v>45.51792185462432</v>
       </c>
       <c r="BA199" s="83" t="inlineStr">
         <is>
@@ -40887,19 +40887,19 @@
         <v>0</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>70.42914438165815</v>
+        <v>70.42914438165812</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>57.60872193547348</v>
+        <v>57.60872193547345</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>52.26333711435106</v>
+        <v>52.26333711435099</v>
       </c>
       <c r="BO199" s="200" t="n">
-        <v>45.09619353366105</v>
+        <v>45.09619353366108</v>
       </c>
       <c r="BP199" s="201" t="n">
-        <v>45.51792185462425</v>
+        <v>45.51792185462432</v>
       </c>
       <c r="BR199" s="83" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>70.42914438165819</v>
       </c>
       <c r="BT199" s="336" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547346</v>
       </c>
       <c r="BU199" s="336" t="n">
         <v>52.26333711435105</v>
@@ -40925,22 +40925,22 @@
         <v>1.000000000000001</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.9999999999999996</v>
+        <v>1</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.9999999999999998</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CA199" s="463" t="n">
         <v>1.000000000000001</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>1</v>
+        <v>0.9999999999999986</v>
       </c>
       <c r="CC199" s="199" t="n">
-        <v>69.7837055929264</v>
+        <v>69.78370559292642</v>
       </c>
       <c r="CD199" s="200" t="n">
-        <v>57.03491411263914</v>
+        <v>57.03491411263915</v>
       </c>
       <c r="CE199" s="200" t="n">
         <v>51.69911604575851</v>
@@ -40983,10 +40983,10 @@
       </c>
       <c r="CS199" s="465" t="n"/>
       <c r="CT199" s="396" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU199" s="397" t="n">
         <v>0.9999999999999999</v>
-      </c>
-      <c r="CU199" s="397" t="n">
-        <v>1</v>
       </c>
       <c r="CV199" s="397" t="n">
         <v>1</v>
@@ -40995,10 +40995,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="CX199" s="398" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="CY199" s="396" t="n">
-        <v>0.9999999968512379</v>
+        <v>0.9999999968512376</v>
       </c>
       <c r="CZ199" s="397" t="n">
         <v>1.000000003555635</v>
@@ -41153,16 +41153,16 @@
         <v>24.29450129484404</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>21.72553967537752</v>
+        <v>21.72553967537748</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>21.83867583929184</v>
+        <v>21.83867583929182</v>
       </c>
       <c r="AX200" s="190" t="n">
         <v>21.02927526959128</v>
       </c>
       <c r="AY200" s="196" t="n">
-        <v>21.37413930497723</v>
+        <v>21.37413930497722</v>
       </c>
       <c r="BA200" s="101" t="inlineStr">
         <is>
@@ -41203,16 +41203,16 @@
         <v>24.29450129484404</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>21.72553967537752</v>
+        <v>21.72553967537748</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>21.83867583929184</v>
+        <v>21.83867583929182</v>
       </c>
       <c r="BO200" s="190" t="n">
         <v>21.02927526959128</v>
       </c>
       <c r="BP200" s="198" t="n">
-        <v>21.37413930497723</v>
+        <v>21.37413930497722</v>
       </c>
       <c r="BR200" s="101" t="inlineStr">
         <is>
@@ -41238,16 +41238,16 @@
         <v>1</v>
       </c>
       <c r="BY200" s="463" t="n">
-        <v>0.9999999999999983</v>
+        <v>1</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.9999999999999986</v>
+        <v>0.9999999999999992</v>
       </c>
       <c r="CA200" s="463" t="n">
         <v>1.000000000000001</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>24.1907998673781</v>
@@ -41314,7 +41314,7 @@
         <v>0.9999999975730698</v>
       </c>
       <c r="CZ200" s="397" t="n">
-        <v>0.9999999996034324</v>
+        <v>0.9999999996034322</v>
       </c>
       <c r="DA200" s="397" t="n">
         <v>0.9999999973604107</v>
@@ -41463,10 +41463,10 @@
         <v>0</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>59.67409839286945</v>
+        <v>59.67409839286942</v>
       </c>
       <c r="AV201" s="190" t="n">
-        <v>65.95320906624883</v>
+        <v>65.95320906624882</v>
       </c>
       <c r="AW201" s="190" t="n">
         <v>72.2446984433664</v>
@@ -41475,7 +41475,7 @@
         <v>79.41855637473452</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>80.57927387179082</v>
+        <v>80.57927387179086</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41513,10 +41513,10 @@
         <v>0</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>59.67409839286945</v>
+        <v>59.67409839286942</v>
       </c>
       <c r="BM201" s="190" t="n">
-        <v>65.95320906624883</v>
+        <v>65.95320906624882</v>
       </c>
       <c r="BN201" s="190" t="n">
         <v>72.2446984433664</v>
@@ -41525,7 +41525,7 @@
         <v>79.41855637473452</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>80.57927387179082</v>
+        <v>80.57927387179086</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41539,43 +41539,43 @@
         <v>65.9532090662488</v>
       </c>
       <c r="BU201" s="336" t="n">
-        <v>72.24469844336645</v>
+        <v>72.24469844336643</v>
       </c>
       <c r="BV201" s="336" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473452</v>
       </c>
       <c r="BW201" s="337" t="n">
-        <v>80.57927387179082</v>
+        <v>80.5792738717908</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>1</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="CC201" s="197" t="n">
-        <v>59.59543716616345</v>
+        <v>59.59543716616346</v>
       </c>
       <c r="CD201" s="190" t="n">
         <v>65.87396619592054</v>
       </c>
       <c r="CE201" s="190" t="n">
-        <v>72.16559100319833</v>
+        <v>72.16559100319832</v>
       </c>
       <c r="CF201" s="190" t="n">
-        <v>79.33915971836331</v>
+        <v>79.33915971836332</v>
       </c>
       <c r="CG201" s="198" t="n">
-        <v>80.50025297216025</v>
+        <v>80.50025297216024</v>
       </c>
       <c r="CI201" s="422" t="n">
         <v>1</v>
@@ -41775,7 +41775,7 @@
         <v>0</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>4.341491071594501</v>
+        <v>4.341491071594504</v>
       </c>
       <c r="AV202" s="209" t="n">
         <v>4.454283009634523</v>
@@ -41784,7 +41784,7 @@
         <v>4.589648670297318</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>4.682726745330951</v>
+        <v>4.682726745330946</v>
       </c>
       <c r="AY202" s="210" t="n">
         <v>4.777692443726263</v>
@@ -41825,7 +41825,7 @@
         <v>0</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>4.341491071594501</v>
+        <v>4.341491071594504</v>
       </c>
       <c r="BM202" s="212" t="n">
         <v>4.454283009634523</v>
@@ -41834,7 +41834,7 @@
         <v>4.589648670297318</v>
       </c>
       <c r="BO202" s="212" t="n">
-        <v>4.682726745330951</v>
+        <v>4.682726745330946</v>
       </c>
       <c r="BP202" s="213" t="n">
         <v>4.777692443726263</v>
@@ -41860,7 +41860,7 @@
         <v>4.777692443726261</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>1</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="BY202" s="467" t="n">
         <v>1.000000000000001</v>
@@ -41869,7 +41869,7 @@
         <v>1</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.9999999999999994</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CB202" s="468" t="n">
         <v>0.9999999999999997</v>
@@ -41884,7 +41884,7 @@
         <v>4.576467622427428</v>
       </c>
       <c r="CF202" s="212" t="n">
-        <v>4.669278385810257</v>
+        <v>4.669278385810258</v>
       </c>
       <c r="CG202" s="213" t="n">
         <v>4.763971351474489</v>
@@ -42043,13 +42043,13 @@
         <v>149.7417536867343</v>
       </c>
       <c r="AW203" s="207" t="n">
-        <v>150.9363600673066</v>
+        <v>150.9363600673065</v>
       </c>
       <c r="AX203" s="207" t="n">
         <v>150.2267519233178</v>
       </c>
       <c r="AY203" s="208" t="n">
-        <v>152.2490274751186</v>
+        <v>152.2490274751187</v>
       </c>
       <c r="BA203" s="155" t="inlineStr">
         <is>
@@ -42093,13 +42093,13 @@
         <v>149.7417536867343</v>
       </c>
       <c r="BN203" s="222" t="n">
-        <v>150.9363600673066</v>
+        <v>150.9363600673065</v>
       </c>
       <c r="BO203" s="222" t="n">
         <v>150.2267519233178</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>152.2490274751186</v>
+        <v>152.2490274751187</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42116,28 +42116,28 @@
         <v>150.9363600673066</v>
       </c>
       <c r="BV203" s="272" t="n">
-        <v>150.2267519233178</v>
+        <v>150.2267519233179</v>
       </c>
       <c r="BW203" s="273" t="n">
         <v>152.2490274751186</v>
       </c>
       <c r="BX203" s="466" t="n">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="BY203" s="467" t="n">
         <v>1</v>
       </c>
-      <c r="BY203" s="467" t="n">
-        <v>0.9999999999999997</v>
-      </c>
       <c r="BZ203" s="467" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CA203" s="467" t="n">
         <v>1</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>1</v>
+        <v>0.9999999999999992</v>
       </c>
       <c r="CC203" s="212" t="n">
-        <v>157.8989653359388</v>
+        <v>157.8989653359389</v>
       </c>
       <c r="CD203" s="212" t="n">
         <v>148.9883752307368</v>
@@ -42949,7 +42949,7 @@
         <v>0</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>6.244070087641002e-16</v>
+        <v>0</v>
       </c>
       <c r="AU208" s="463" t="n">
         <v>0</v>
@@ -43201,7 +43201,7 @@
         <v>0</v>
       </c>
       <c r="AS209" s="463" t="n">
-        <v>0</v>
+        <v>6.75765309694298e-16</v>
       </c>
       <c r="AT209" s="474" t="n">
         <v>0</v>
@@ -44740,10 +44740,10 @@
         <v>0</v>
       </c>
       <c r="AN219" s="368" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>0</v>
@@ -44775,10 +44775,10 @@
         <v>0</v>
       </c>
       <c r="BE219" s="375" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>0</v>
@@ -44935,7 +44935,7 @@
         <v>1.455191522836685e-11</v>
       </c>
       <c r="AN220" s="368" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="AO220" s="380" t="n">
         <v>0</v>
@@ -44970,7 +44970,7 @@
         <v>1.455191522836685e-11</v>
       </c>
       <c r="BE220" s="375" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="BF220" s="392" t="n">
         <v>0</v>
@@ -45127,7 +45127,7 @@
         <v>0</v>
       </c>
       <c r="AM221" s="368" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AN221" s="368" t="n">
         <v>0</v>
@@ -45162,7 +45162,7 @@
         <v>0</v>
       </c>
       <c r="BD221" s="375" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BE221" s="375" t="n">
         <v>0</v>
@@ -45517,13 +45517,13 @@
         <v>0</v>
       </c>
       <c r="AM223" s="408" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="AN223" s="408" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="AO223" s="409" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP223" s="436" t="n">
         <v>0</v>
@@ -45552,13 +45552,13 @@
         <v>0</v>
       </c>
       <c r="BD223" s="440" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="BE223" s="440" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="BF223" s="441" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG223" s="442" t="n">
         <v>0</v>
@@ -47638,10 +47638,10 @@
         <v>0</v>
       </c>
       <c r="AN237" s="368" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>0</v>
@@ -47673,10 +47673,10 @@
         <v>0</v>
       </c>
       <c r="BE237" s="375" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>0</v>
@@ -47833,7 +47833,7 @@
         <v>1.455191522836685e-11</v>
       </c>
       <c r="AN238" s="368" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="AO238" s="380" t="n">
         <v>0</v>
@@ -47868,7 +47868,7 @@
         <v>1.455191522836685e-11</v>
       </c>
       <c r="BE238" s="375" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="BF238" s="392" t="n">
         <v>0</v>
@@ -48025,7 +48025,7 @@
         <v>0</v>
       </c>
       <c r="AM239" s="368" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AN239" s="368" t="n">
         <v>0</v>
@@ -48060,7 +48060,7 @@
         <v>0</v>
       </c>
       <c r="BD239" s="375" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BE239" s="375" t="n">
         <v>0</v>
@@ -48415,13 +48415,13 @@
         <v>0</v>
       </c>
       <c r="AM241" s="408" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="AN241" s="408" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="AO241" s="409" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP241" s="436" t="n">
         <v>0</v>
@@ -48450,13 +48450,13 @@
         <v>0</v>
       </c>
       <c r="BD241" s="440" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="BE241" s="440" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="BF241" s="441" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG241" s="442" t="n">
         <v>0</v>
@@ -49039,7 +49039,7 @@
         <v>66390.65769892579</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>61769.41695598943</v>
+        <v>61769.41695598939</v>
       </c>
       <c r="AM246" s="368" t="n">
         <v>62526.11635133826</v>
@@ -49048,7 +49048,7 @@
         <v>58001.49964746024</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>59334.37238636035</v>
+        <v>59334.37238636029</v>
       </c>
       <c r="AP246" s="381" t="n">
         <v>942.6588705782099</v>
@@ -49063,7 +49063,7 @@
         <v>1286.172847465061</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>1303.538693543106</v>
+        <v>1303.538693543104</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>66390.65769892579</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>61769.41695598943</v>
+        <v>61769.41695598939</v>
       </c>
       <c r="BD246" s="375" t="n">
         <v>62526.11635133826</v>
@@ -49083,7 +49083,7 @@
         <v>58001.49964746024</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>59334.37238636035</v>
+        <v>59334.37238636029</v>
       </c>
       <c r="BG246" s="386" t="n">
         <v>942.6588705782099</v>
@@ -49098,7 +49098,7 @@
         <v>1286.172847465061</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>1303.538693543106</v>
+        <v>1303.538693543104</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>65782.22909930955</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>61154.1668086079</v>
+        <v>61154.16680860786</v>
       </c>
       <c r="BU246" s="375" t="n">
         <v>61851.10105131054</v>
@@ -49118,7 +49118,7 @@
         <v>57298.94272602393</v>
       </c>
       <c r="BW246" s="392" t="n">
-        <v>58639.32994090823</v>
+        <v>58639.32994090817</v>
       </c>
       <c r="BX246" s="386" t="n">
         <v>942.6588705782099</v>
@@ -49133,7 +49133,7 @@
         <v>1286.172847465061</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>1303.538693543106</v>
+        <v>1303.538693543104</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49215,34 +49215,34 @@
         </is>
       </c>
       <c r="AK247" s="506" t="n">
-        <v>58598.88127559342</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>57407.08920022813</v>
+        <v>57407.08920022819</v>
       </c>
       <c r="AM247" s="368" t="n">
-        <v>60876.37537505451</v>
+        <v>60876.37537505453</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085034</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>67766.10007773874</v>
+        <v>67766.10007773868</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>2412.022398156966</v>
+        <v>2412.022398156969</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>2642.378051776894</v>
+        <v>2642.378051776896</v>
       </c>
       <c r="AR247" s="372" t="n">
-        <v>2787.548834180694</v>
+        <v>2787.548834180695</v>
       </c>
       <c r="AS247" s="372" t="n">
-        <v>2995.269601644735</v>
+        <v>2995.269601644733</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>3170.47152686454</v>
+        <v>3170.471526864538</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49250,34 +49250,34 @@
         </is>
       </c>
       <c r="BB247" s="391" t="n">
-        <v>58598.88127559342</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>57407.08920022813</v>
+        <v>57407.08920022819</v>
       </c>
       <c r="BD247" s="375" t="n">
-        <v>60876.37537505451</v>
+        <v>60876.37537505453</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085034</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>67766.10007773874</v>
+        <v>67766.10007773868</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>2412.022398156966</v>
+        <v>2412.022398156969</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>2642.378051776894</v>
+        <v>2642.378051776896</v>
       </c>
       <c r="BI247" s="372" t="n">
-        <v>2787.548834180694</v>
+        <v>2787.548834180695</v>
       </c>
       <c r="BJ247" s="372" t="n">
-        <v>2995.269601644735</v>
+        <v>2995.269601644733</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>3170.47152686454</v>
+        <v>3170.471526864538</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49285,34 +49285,34 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>58348.75110982313</v>
+        <v>58348.75110982321</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>57175.78738851468</v>
+        <v>57175.78738851473</v>
       </c>
       <c r="BU247" s="375" t="n">
-        <v>60631.37535228482</v>
+        <v>60631.37535228484</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>62727.38814771608</v>
+        <v>62727.38814771605</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>67526.64495008008</v>
+        <v>67526.64495008002</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>2412.022398156966</v>
+        <v>2412.022398156969</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>2642.378051776894</v>
+        <v>2642.378051776896</v>
       </c>
       <c r="BZ247" s="372" t="n">
-        <v>2787.548834180694</v>
+        <v>2787.548834180695</v>
       </c>
       <c r="CA247" s="372" t="n">
-        <v>2995.269601644735</v>
+        <v>2995.269601644733</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>3170.47152686454</v>
+        <v>3170.471526864538</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49400,10 +49400,10 @@
         <v>158473.1245926057</v>
       </c>
       <c r="AM248" s="368" t="n">
-        <v>182579.1755779381</v>
+        <v>182579.175577938</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>211939.3794528705</v>
+        <v>211939.3794528704</v>
       </c>
       <c r="AO248" s="380" t="n">
         <v>231893.8870371914</v>
@@ -49415,13 +49415,13 @@
         <v>2402.81143005521</v>
       </c>
       <c r="AR248" s="372" t="n">
-        <v>2527.232856013516</v>
+        <v>2527.232856013515</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2668.638025251066</v>
+        <v>2668.638025251065</v>
       </c>
       <c r="AT248" s="382" t="n">
-        <v>2877.835402259324</v>
+        <v>2877.835402259325</v>
       </c>
       <c r="BA248" s="111" t="inlineStr">
         <is>
@@ -49435,10 +49435,10 @@
         <v>158473.1245926057</v>
       </c>
       <c r="BD248" s="375" t="n">
-        <v>182579.1755779381</v>
+        <v>182579.175577938</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>211939.3794528705</v>
+        <v>211939.3794528704</v>
       </c>
       <c r="BF248" s="392" t="n">
         <v>231893.8870371914</v>
@@ -49450,13 +49450,13 @@
         <v>2402.81143005521</v>
       </c>
       <c r="BI248" s="372" t="n">
-        <v>2527.232856013516</v>
+        <v>2527.232856013515</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2668.638025251066</v>
+        <v>2668.638025251065</v>
       </c>
       <c r="BK248" s="387" t="n">
-        <v>2877.835402259324</v>
+        <v>2877.835402259325</v>
       </c>
       <c r="BR248" s="111" t="inlineStr">
         <is>
@@ -49470,10 +49470,10 @@
         <v>158282.7189180313</v>
       </c>
       <c r="BU248" s="375" t="n">
-        <v>182379.2526559911</v>
+        <v>182379.252655991</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>211727.4985165998</v>
+        <v>211727.4985165997</v>
       </c>
       <c r="BW248" s="392" t="n">
         <v>231666.4778947156</v>
@@ -49485,13 +49485,13 @@
         <v>2402.81143005521</v>
       </c>
       <c r="BZ248" s="372" t="n">
-        <v>2527.232856013516</v>
+        <v>2527.232856013515</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2668.638025251066</v>
+        <v>2668.638025251065</v>
       </c>
       <c r="CB248" s="387" t="n">
-        <v>2877.835402259324</v>
+        <v>2877.835402259325</v>
       </c>
       <c r="CI248" s="225" t="n"/>
       <c r="CJ248" s="225" t="n"/>
@@ -49573,31 +49573,31 @@
         </is>
       </c>
       <c r="AK249" s="435" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="AL249" s="408" t="n">
-        <v>11640.00260232831</v>
+        <v>11640.0026023282</v>
       </c>
       <c r="AM249" s="408" t="n">
         <v>12649.94277298776</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>13606.04680805822</v>
+        <v>13606.04680805834</v>
       </c>
       <c r="AO249" s="409" t="n">
         <v>14635.09201340942</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>2476.336292788151</v>
+        <v>2476.336292788124</v>
       </c>
       <c r="AQ249" s="411" t="n">
-        <v>2613.215769226195</v>
+        <v>2613.215769226169</v>
       </c>
       <c r="AR249" s="411" t="n">
         <v>2756.18978265532</v>
       </c>
       <c r="AS249" s="411" t="n">
-        <v>2905.582056989793</v>
+        <v>2905.582056989817</v>
       </c>
       <c r="AT249" s="412" t="n">
         <v>3063.213504848331</v>
@@ -49608,31 +49608,31 @@
         </is>
       </c>
       <c r="BB249" s="419" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="BC249" s="420" t="n">
-        <v>11640.00260232831</v>
+        <v>11640.0026023282</v>
       </c>
       <c r="BD249" s="420" t="n">
         <v>12649.94277298776</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>13606.04680805822</v>
+        <v>13606.04680805834</v>
       </c>
       <c r="BF249" s="421" t="n">
         <v>14635.09201340942</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>2476.336292788151</v>
+        <v>2476.336292788124</v>
       </c>
       <c r="BH249" s="417" t="n">
-        <v>2613.215769226195</v>
+        <v>2613.215769226169</v>
       </c>
       <c r="BI249" s="417" t="n">
         <v>2756.18978265532</v>
       </c>
       <c r="BJ249" s="417" t="n">
-        <v>2905.582056989793</v>
+        <v>2905.582056989817</v>
       </c>
       <c r="BK249" s="418" t="n">
         <v>3063.213504848331</v>
@@ -49643,31 +49643,31 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>10720.11604629892</v>
+        <v>10720.1160462988</v>
       </c>
       <c r="BT249" s="420" t="n">
-        <v>11606.57358792469</v>
+        <v>11606.57358792457</v>
       </c>
       <c r="BU249" s="420" t="n">
         <v>12613.61330351852</v>
       </c>
       <c r="BV249" s="420" t="n">
-        <v>13566.97149594171</v>
+        <v>13566.97149594183</v>
       </c>
       <c r="BW249" s="421" t="n">
         <v>14593.06137832891</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>2476.336292788151</v>
+        <v>2476.336292788124</v>
       </c>
       <c r="BY249" s="417" t="n">
-        <v>2613.215769226195</v>
+        <v>2613.215769226169</v>
       </c>
       <c r="BZ249" s="417" t="n">
         <v>2756.18978265532</v>
       </c>
       <c r="CA249" s="417" t="n">
-        <v>2905.582056989793</v>
+        <v>2905.582056989817</v>
       </c>
       <c r="CB249" s="418" t="n">
         <v>3063.213504848331</v>
@@ -49761,10 +49761,10 @@
         <v>318631.6100773186</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>346535.2748692393</v>
+        <v>346535.2748692394</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>373629.4515146999</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="AP250" s="436" t="n">
         <v>1710.409888945313</v>
@@ -49796,10 +49796,10 @@
         <v>318631.6100773186</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>346535.2748692393</v>
+        <v>346535.2748692394</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>373629.4515146999</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="BG250" s="442" t="n">
         <v>1710.409888945313</v>
@@ -49825,7 +49825,7 @@
         <v>270440.755383566</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>288219.2467030786</v>
+        <v>288219.2467030784</v>
       </c>
       <c r="BU250" s="440" t="n">
         <v>317475.3423631049</v>
@@ -49840,7 +49840,7 @@
         <v>1712.745582646056</v>
       </c>
       <c r="BY250" s="443" t="n">
-        <v>1934.508288020532</v>
+        <v>1934.508288020531</v>
       </c>
       <c r="BZ250" s="443" t="n">
         <v>2113.797190413086</v>
@@ -49849,7 +49849,7 @@
         <v>2309.82972411665</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>2457.482712305755</v>
+        <v>2457.482712305754</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51945,7 +51945,7 @@
         <v>66390.65769892579</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>61769.41695598943</v>
+        <v>61769.41695598939</v>
       </c>
       <c r="AM264" s="368" t="n">
         <v>62526.11635133826</v>
@@ -51954,22 +51954,22 @@
         <v>58001.49964746024</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>59334.37238636035</v>
+        <v>59334.37238636029</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>942.6588705827853</v>
+        <v>942.6588705827857</v>
       </c>
       <c r="AQ264" s="372" t="n">
         <v>1072.223352310719</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>1196.36670376659</v>
+        <v>1196.366703766591</v>
       </c>
       <c r="AS264" s="372" t="n">
-        <v>1286.172847474728</v>
+        <v>1286.172847474727</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>1303.538693525229</v>
+        <v>1303.538693525225</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>66390.65769892579</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>61769.41695598943</v>
+        <v>61769.41695598939</v>
       </c>
       <c r="BD264" s="375" t="n">
         <v>62526.11635133826</v>
@@ -51989,22 +51989,22 @@
         <v>58001.49964746024</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>59334.37238636035</v>
+        <v>59334.37238636029</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>942.6588705827853</v>
+        <v>942.6588705827857</v>
       </c>
       <c r="BH264" s="372" t="n">
         <v>1072.223352310719</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>1196.36670376659</v>
+        <v>1196.366703766591</v>
       </c>
       <c r="BJ264" s="372" t="n">
-        <v>1286.172847474728</v>
+        <v>1286.172847474727</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>1303.538693525229</v>
+        <v>1303.538693525225</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52015,31 +52015,31 @@
         <v>65782.22909930955</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>61154.16680860791</v>
+        <v>61154.16680860786</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>61851.10105131055</v>
+        <v>61851.10105131054</v>
       </c>
       <c r="BV264" s="375" t="n">
         <v>57298.94272602393</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>58639.32994090824</v>
+        <v>58639.32994090818</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>942.6588705827853</v>
+        <v>942.6588705827857</v>
       </c>
       <c r="BY264" s="372" t="n">
         <v>1072.223352310719</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>1196.36670376659</v>
+        <v>1196.366703766591</v>
       </c>
       <c r="CA264" s="372" t="n">
-        <v>1286.172847474728</v>
+        <v>1286.172847474727</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>1303.538693525229</v>
+        <v>1303.538693525225</v>
       </c>
       <c r="CI264" s="396" t="n">
         <v>1</v>
@@ -52069,10 +52069,10 @@
         <v>1.000000000118858</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>1.000000000031783</v>
+        <v>1.000000000031784</v>
       </c>
       <c r="CT264" s="396" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CU264" s="397" t="n">
         <v>0.9999999999999998</v>
@@ -52093,13 +52093,13 @@
         <v>1.000000000000091</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>0.9999999999971357</v>
+        <v>0.9999999999971356</v>
       </c>
       <c r="DB264" s="103" t="n">
         <v>0.9999999999959689</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>0.9999999999967922</v>
+        <v>0.999999999996793</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52117,19 +52117,19 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>56692.45153990574</v>
+        <v>56692.4515399057</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>53152.45709120956</v>
+        <v>53152.45709120953</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>54365.66030675423</v>
+        <v>54365.66030675419</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>49985.42743407265</v>
+        <v>49985.42743407263</v>
       </c>
       <c r="DO264" s="392" t="n">
-        <v>47629.93996276433</v>
+        <v>47629.93996276429</v>
       </c>
     </row>
     <row r="265">
@@ -52209,31 +52209,31 @@
         </is>
       </c>
       <c r="AK265" s="506" t="n">
-        <v>58598.88127559342</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>57407.08920022813</v>
+        <v>57407.08920022819</v>
       </c>
       <c r="AM265" s="368" t="n">
-        <v>60876.37537505451</v>
+        <v>60876.37537505453</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085034</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>67766.10007773874</v>
+        <v>67766.10007773868</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>2412.02239817245</v>
+        <v>2412.022398172454</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>2642.378051730979</v>
+        <v>2642.378051730987</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>2787.548834143442</v>
+        <v>2787.548834143444</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>2995.26960170295</v>
+        <v>2995.269601702948</v>
       </c>
       <c r="AT265" s="382" t="n">
         <v>3170.471526867917</v>
@@ -52244,31 +52244,31 @@
         </is>
       </c>
       <c r="BB265" s="391" t="n">
-        <v>58598.88127559342</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>57407.08920022813</v>
+        <v>57407.08920022819</v>
       </c>
       <c r="BD265" s="375" t="n">
-        <v>60876.37537505451</v>
+        <v>60876.37537505453</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085034</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>67766.10007773874</v>
+        <v>67766.10007773868</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>2412.02239817245</v>
+        <v>2412.022398172454</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>2642.378051730979</v>
+        <v>2642.378051730987</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>2787.548834143442</v>
+        <v>2787.548834143444</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>2995.26960170295</v>
+        <v>2995.269601702948</v>
       </c>
       <c r="BK265" s="387" t="n">
         <v>3170.471526867917</v>
@@ -52279,31 +52279,31 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>58348.75110982313</v>
+        <v>58348.75110982321</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>57175.78738851468</v>
+        <v>57175.78738851474</v>
       </c>
       <c r="BU265" s="375" t="n">
         <v>60631.37535228483</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>62727.38814771608</v>
+        <v>62727.38814771604</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>67526.6449500801</v>
+        <v>67526.64495008004</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>2412.02239817245</v>
+        <v>2412.022398172454</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>2642.378051730979</v>
+        <v>2642.378051730987</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>2787.548834143442</v>
+        <v>2787.548834143444</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>2995.26960170295</v>
+        <v>2995.269601702948</v>
       </c>
       <c r="CB265" s="387" t="n">
         <v>3170.471526867917</v>
@@ -52324,25 +52324,25 @@
         <v>1</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999999999549125</v>
+        <v>0.9999999999549111</v>
       </c>
       <c r="CO265" s="103" t="n">
-        <v>1.000000000056473</v>
+        <v>1.000000000056472</v>
       </c>
       <c r="CP265" s="103" t="n">
         <v>1.00000000002884</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>0.9999999999490421</v>
+        <v>0.9999999999490425</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>0.9999999999532583</v>
+        <v>0.9999999999532592</v>
       </c>
       <c r="CT265" s="396" t="n">
         <v>1</v>
       </c>
       <c r="CU265" s="397" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CV265" s="397" t="n">
         <v>1</v>
@@ -52354,7 +52354,7 @@
         <v>1</v>
       </c>
       <c r="CY265" s="102" t="n">
-        <v>1.000000000002534</v>
+        <v>1.000000000002533</v>
       </c>
       <c r="CZ265" s="103" t="n">
         <v>0.999999999998616</v>
@@ -52366,7 +52366,7 @@
         <v>1.000000000000836</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>1.000000000001392</v>
+        <v>1.000000000001393</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52384,7 +52384,7 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>49357.38537389892</v>
+        <v>49357.38537389891</v>
       </c>
       <c r="DL265" s="375" t="n">
         <v>48368.75020661164</v>
@@ -52482,28 +52482,28 @@
         <v>158473.1245926057</v>
       </c>
       <c r="AM266" s="368" t="n">
-        <v>182579.1755779381</v>
+        <v>182579.175577938</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>211939.3794528705</v>
+        <v>211939.3794528704</v>
       </c>
       <c r="AO266" s="380" t="n">
         <v>231893.8870371914</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2275.168462143915</v>
+        <v>2275.168462143916</v>
       </c>
       <c r="AQ266" s="372" t="n">
-        <v>2402.811430046144</v>
+        <v>2402.811430046145</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2527.232856000699</v>
+        <v>2527.232856000698</v>
       </c>
       <c r="AS266" s="372" t="n">
         <v>2668.638025259987</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2877.835402266795</v>
+        <v>2877.835402266794</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52517,28 +52517,28 @@
         <v>158473.1245926057</v>
       </c>
       <c r="BD266" s="375" t="n">
-        <v>182579.1755779381</v>
+        <v>182579.175577938</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>211939.3794528705</v>
+        <v>211939.3794528704</v>
       </c>
       <c r="BF266" s="392" t="n">
         <v>231893.8870371914</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2275.168462143915</v>
+        <v>2275.168462143916</v>
       </c>
       <c r="BH266" s="372" t="n">
-        <v>2402.811430046144</v>
+        <v>2402.811430046145</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2527.232856000699</v>
+        <v>2527.232856000698</v>
       </c>
       <c r="BJ266" s="372" t="n">
         <v>2668.638025259987</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2877.835402266795</v>
+        <v>2877.835402266794</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>135589.6591281345</v>
+        <v>135589.6591281344</v>
       </c>
       <c r="BT266" s="375" t="n">
         <v>158282.7189180313</v>
@@ -52561,19 +52561,19 @@
         <v>231666.4778947156</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2275.168462143915</v>
+        <v>2275.168462143916</v>
       </c>
       <c r="BY266" s="372" t="n">
-        <v>2402.811430046144</v>
+        <v>2402.811430046145</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2527.232856000699</v>
+        <v>2527.232856000698</v>
       </c>
       <c r="CA266" s="372" t="n">
         <v>2668.638025259987</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2877.835402266795</v>
+        <v>2877.835402266794</v>
       </c>
       <c r="CI266" s="396" t="n">
         <v>1</v>
@@ -52597,13 +52597,13 @@
         <v>1.00000000000128</v>
       </c>
       <c r="CP266" s="103" t="n">
-        <v>0.9999999999936119</v>
+        <v>0.9999999999936122</v>
       </c>
       <c r="CQ266" s="103" t="n">
-        <v>0.9999999999958892</v>
+        <v>0.9999999999958894</v>
       </c>
       <c r="CR266" s="104" t="n">
-        <v>1.000000000000737</v>
+        <v>1.000000000000736</v>
       </c>
       <c r="CT266" s="396" t="n">
         <v>1</v>
@@ -52627,13 +52627,13 @@
         <v>1.000000000001832</v>
       </c>
       <c r="DA266" s="103" t="n">
-        <v>1.000000000000259</v>
+        <v>1.00000000000026</v>
       </c>
       <c r="DB266" s="103" t="n">
         <v>1.000000000000489</v>
       </c>
       <c r="DC266" s="104" t="n">
-        <v>0.9999999999993366</v>
+        <v>0.9999999999993364</v>
       </c>
       <c r="DE266" s="391" t="n">
         <v>0</v>
@@ -52651,13 +52651,13 @@
         <v>0</v>
       </c>
       <c r="DK266" s="391" t="n">
-        <v>109408.1421862742</v>
+        <v>109408.1421862743</v>
       </c>
       <c r="DL266" s="375" t="n">
         <v>128891.8287037453</v>
       </c>
       <c r="DM266" s="375" t="n">
-        <v>149628.6636613694</v>
+        <v>149628.6636613695</v>
       </c>
       <c r="DN266" s="375" t="n">
         <v>174895.0914278394</v>
@@ -52743,31 +52743,31 @@
         </is>
       </c>
       <c r="AK267" s="435" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="AL267" s="408" t="n">
-        <v>11640.00260232831</v>
+        <v>11640.0026023282</v>
       </c>
       <c r="AM267" s="408" t="n">
         <v>12649.94277298776</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>13606.04680805822</v>
+        <v>13606.04680805834</v>
       </c>
       <c r="AO267" s="409" t="n">
         <v>14635.09201340942</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>2476.336292449054</v>
+        <v>2476.336292449026</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>2613.21576944061</v>
+        <v>2613.215769440583</v>
       </c>
       <c r="AR267" s="411" t="n">
         <v>2756.189783077295</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>2905.582056784442</v>
+        <v>2905.58205678447</v>
       </c>
       <c r="AT267" s="412" t="n">
         <v>3063.213504382689</v>
@@ -52778,31 +52778,31 @@
         </is>
       </c>
       <c r="BB267" s="419" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="BC267" s="420" t="n">
-        <v>11640.00260232831</v>
+        <v>11640.0026023282</v>
       </c>
       <c r="BD267" s="420" t="n">
         <v>12649.94277298776</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>13606.04680805822</v>
+        <v>13606.04680805834</v>
       </c>
       <c r="BF267" s="421" t="n">
         <v>14635.09201340942</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>2476.336292449054</v>
+        <v>2476.336292449026</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>2613.21576944061</v>
+        <v>2613.215769440583</v>
       </c>
       <c r="BI267" s="417" t="n">
         <v>2756.189783077295</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>2905.582056784442</v>
+        <v>2905.58205678447</v>
       </c>
       <c r="BK267" s="418" t="n">
         <v>3063.213504382689</v>
@@ -52813,31 +52813,31 @@
         </is>
       </c>
       <c r="BS267" s="419" t="n">
-        <v>10720.11604629892</v>
+        <v>10720.1160462988</v>
       </c>
       <c r="BT267" s="420" t="n">
-        <v>11606.57358792469</v>
+        <v>11606.57358792457</v>
       </c>
       <c r="BU267" s="420" t="n">
         <v>12613.61330351852</v>
       </c>
       <c r="BV267" s="420" t="n">
-        <v>13566.97149594171</v>
+        <v>13566.97149594183</v>
       </c>
       <c r="BW267" s="421" t="n">
         <v>14593.06137832891</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>2476.336292449054</v>
+        <v>2476.336292449026</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>2613.21576944061</v>
+        <v>2613.215769440583</v>
       </c>
       <c r="BZ267" s="417" t="n">
         <v>2756.189783077295</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>2905.582056784442</v>
+        <v>2905.58205678447</v>
       </c>
       <c r="CB267" s="418" t="n">
         <v>3063.213504382689</v>
@@ -52858,16 +52858,16 @@
         <v>1</v>
       </c>
       <c r="CN267" s="132" t="n">
-        <v>0.9999999999587359</v>
+        <v>0.9999999999587467</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>0.9999999999655645</v>
+        <v>0.9999999999655748</v>
       </c>
       <c r="CP267" s="133" t="n">
         <v>1.000000000207868</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>1.000000000152359</v>
+        <v>1.00000000015235</v>
       </c>
       <c r="CR267" s="134" t="n">
         <v>0.9999999997045294</v>
@@ -52891,16 +52891,16 @@
         <v>1.000000000000111</v>
       </c>
       <c r="CZ267" s="133" t="n">
-        <v>0.9999999999994139</v>
+        <v>0.999999999999414</v>
       </c>
       <c r="DA267" s="133" t="n">
         <v>1.000000000000026</v>
       </c>
       <c r="DB267" s="133" t="n">
-        <v>0.99999999999986</v>
+        <v>0.9999999999998598</v>
       </c>
       <c r="DC267" s="134" t="n">
-        <v>0.9999999999990653</v>
+        <v>0.9999999999990652</v>
       </c>
       <c r="DE267" s="419" t="n">
         <v>0</v>
@@ -52921,7 +52921,7 @@
         <v>8916.232863165696</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>9666.763954628112</v>
+        <v>9666.76395462811</v>
       </c>
       <c r="DM267" s="420" t="n">
         <v>10532.06230041419</v>
@@ -53019,10 +53019,10 @@
         <v>318631.6100773186</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>346535.2748692393</v>
+        <v>346535.2748692394</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>373629.4515146999</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="AP268" s="436" t="n">
         <v>1710.409888945678</v>
@@ -53031,13 +53031,13 @@
         <v>1931.923636718967</v>
       </c>
       <c r="AR268" s="437" t="n">
-        <v>2111.032821615892</v>
+        <v>2111.032821615894</v>
       </c>
       <c r="AS268" s="437" t="n">
         <v>2306.748102003336</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>2454.06790250769</v>
+        <v>2454.067902507688</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53054,10 +53054,10 @@
         <v>318631.6100773186</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>346535.2748692393</v>
+        <v>346535.2748692394</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>373629.4515146999</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="BG268" s="442" t="n">
         <v>1710.409888945678</v>
@@ -53066,13 +53066,13 @@
         <v>1931.923636718967</v>
       </c>
       <c r="BI268" s="443" t="n">
-        <v>2111.032821615892</v>
+        <v>2111.032821615894</v>
       </c>
       <c r="BJ268" s="443" t="n">
         <v>2306.748102003336</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>2454.06790250769</v>
+        <v>2454.067902507688</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,19 +53080,19 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>270440.7553835661</v>
+        <v>270440.755383566</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>288219.2467030786</v>
+        <v>288219.2467030785</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>317475.342363105</v>
+        <v>317475.3423631049</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>345320.8008862815</v>
+        <v>345320.8008862816</v>
       </c>
       <c r="BW268" s="441" t="n">
-        <v>372425.5141640328</v>
+        <v>372425.5141640327</v>
       </c>
       <c r="BX268" s="442" t="n">
         <v>1712.745582646399</v>
@@ -53101,13 +53101,13 @@
         <v>1934.508288023923</v>
       </c>
       <c r="BZ268" s="443" t="n">
-        <v>2113.797190408818</v>
+        <v>2113.797190408819</v>
       </c>
       <c r="CA268" s="443" t="n">
         <v>2309.829724127112</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2457.482712287765</v>
+        <v>2457.482712287762</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,7 +53125,7 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>224374.2119632446</v>
+        <v>224374.2119632445</v>
       </c>
       <c r="DL268" s="440" t="n">
         <v>240079.7999561946</v>
@@ -53137,7 +53137,7 @@
         <v>289561.3047971948</v>
       </c>
       <c r="DO268" s="441" t="n">
-        <v>309619.9738031466</v>
+        <v>309619.9738031464</v>
       </c>
     </row>
     <row r="269">
@@ -54071,7 +54071,7 @@
         <v>99.20268881209788</v>
       </c>
       <c r="AT276" s="195" t="n">
-        <v>89.68714935167567</v>
+        <v>89.68714935167566</v>
       </c>
       <c r="AU276" s="190" t="n">
         <v>120.2436157232417</v>
@@ -54121,7 +54121,7 @@
         <v>99.20268881209788</v>
       </c>
       <c r="BK276" s="198" t="n">
-        <v>89.68714935167567</v>
+        <v>89.68714935167566</v>
       </c>
       <c r="BL276" s="199" t="n">
         <v>120.2436157232417</v>
@@ -54171,7 +54171,7 @@
         <v>100.81808537262</v>
       </c>
       <c r="CB276" s="198" t="n">
-        <v>91.52947777942927</v>
+        <v>91.52947777942926</v>
       </c>
       <c r="CC276" s="199" t="n">
         <v>120.8890545119735</v>
@@ -54324,25 +54324,25 @@
         </is>
       </c>
       <c r="AK277" s="194" t="n">
-        <v>27.10789901090663</v>
+        <v>27.10789901090662</v>
       </c>
       <c r="AL277" s="179" t="n">
-        <v>49.58255201573819</v>
+        <v>49.58255201573821</v>
       </c>
       <c r="AM277" s="179" t="n">
         <v>67.83338551434517</v>
       </c>
       <c r="AN277" s="179" t="n">
-        <v>74.47154139200723</v>
+        <v>74.47154139200721</v>
       </c>
       <c r="AO277" s="195" t="n">
-        <v>79.83556699614779</v>
+        <v>79.8355669961478</v>
       </c>
       <c r="AP277" s="194" t="n">
-        <v>69.20027670287119</v>
+        <v>69.20027670287121</v>
       </c>
       <c r="AQ277" s="179" t="n">
-        <v>69.32151457152676</v>
+        <v>69.32151457152678</v>
       </c>
       <c r="AR277" s="179" t="n">
         <v>68.27813854510515</v>
@@ -54366,7 +54366,7 @@
         <v>142.3789668149968</v>
       </c>
       <c r="AY277" s="196" t="n">
-        <v>146.750093231066</v>
+        <v>146.7500932310661</v>
       </c>
       <c r="BA277" s="101" t="inlineStr">
         <is>
@@ -54374,25 +54374,25 @@
         </is>
       </c>
       <c r="BB277" s="197" t="n">
-        <v>27.10789901090663</v>
+        <v>27.10789901090662</v>
       </c>
       <c r="BC277" s="190" t="n">
-        <v>49.58255201573819</v>
+        <v>49.58255201573821</v>
       </c>
       <c r="BD277" s="190" t="n">
         <v>67.83338551434517</v>
       </c>
       <c r="BE277" s="190" t="n">
-        <v>74.47154139200723</v>
+        <v>74.47154139200721</v>
       </c>
       <c r="BF277" s="198" t="n">
-        <v>79.83556699614779</v>
+        <v>79.8355669961478</v>
       </c>
       <c r="BG277" s="197" t="n">
-        <v>69.20027670287119</v>
+        <v>69.20027670287121</v>
       </c>
       <c r="BH277" s="190" t="n">
-        <v>69.32151457152676</v>
+        <v>69.32151457152678</v>
       </c>
       <c r="BI277" s="190" t="n">
         <v>68.27813854510515</v>
@@ -54416,7 +54416,7 @@
         <v>142.3789668149968</v>
       </c>
       <c r="BP277" s="198" t="n">
-        <v>146.750093231066</v>
+        <v>146.7500932310661</v>
       </c>
       <c r="BR277" s="101" t="inlineStr">
         <is>
@@ -54424,25 +54424,25 @@
         </is>
       </c>
       <c r="BS277" s="197" t="n">
-        <v>26.91528265947908</v>
+        <v>26.91528265947907</v>
       </c>
       <c r="BT277" s="190" t="n">
-        <v>49.2258398159764</v>
+        <v>49.22583981597641</v>
       </c>
       <c r="BU277" s="190" t="n">
         <v>67.28893941810736</v>
       </c>
       <c r="BV277" s="190" t="n">
-        <v>73.75964655793224</v>
+        <v>73.75964655793223</v>
       </c>
       <c r="BW277" s="198" t="n">
-        <v>78.9550664367614</v>
+        <v>78.95506643676141</v>
       </c>
       <c r="BX277" s="197" t="n">
-        <v>69.49659448176469</v>
+        <v>69.4965944817647</v>
       </c>
       <c r="BY277" s="190" t="n">
-        <v>69.76576224395188</v>
+        <v>69.7657622439519</v>
       </c>
       <c r="BZ277" s="190" t="n">
         <v>68.91047548643553</v>
@@ -54466,7 +54466,7 @@
         <v>142.4660911302791</v>
       </c>
       <c r="CG277" s="198" t="n">
-        <v>146.825619891889</v>
+        <v>146.8256198918891</v>
       </c>
       <c r="CI277" s="197" t="n">
         <v>0</v>
@@ -54610,7 +54610,7 @@
         <v>28.60615917579112</v>
       </c>
       <c r="AM278" s="179" t="n">
-        <v>44.31839797899375</v>
+        <v>44.31839797899376</v>
       </c>
       <c r="AN278" s="179" t="n">
         <v>57.06556265358646</v>
@@ -54625,13 +54625,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="AR278" s="179" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778419</v>
       </c>
       <c r="AS278" s="179" t="n">
         <v>85.27800681733345</v>
       </c>
       <c r="AT278" s="195" t="n">
-        <v>84.87934076273497</v>
+        <v>84.87934076273498</v>
       </c>
       <c r="AU278" s="190" t="n">
         <v>118.5676032367616</v>
@@ -54640,13 +54640,13 @@
         <v>128.6957436340165</v>
       </c>
       <c r="AW278" s="190" t="n">
-        <v>139.345594676778</v>
+        <v>139.3455946767779</v>
       </c>
       <c r="AX278" s="190" t="n">
         <v>142.3435694709199</v>
       </c>
       <c r="AY278" s="196" t="n">
-        <v>153.192981760672</v>
+        <v>153.1929817606721</v>
       </c>
       <c r="BA278" s="111" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>28.60615917579112</v>
       </c>
       <c r="BD278" s="190" t="n">
-        <v>44.31839797899375</v>
+        <v>44.31839797899376</v>
       </c>
       <c r="BE278" s="190" t="n">
         <v>57.06556265358646</v>
@@ -54675,13 +54675,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="BI278" s="190" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778419</v>
       </c>
       <c r="BJ278" s="190" t="n">
         <v>85.27800681733345</v>
       </c>
       <c r="BK278" s="198" t="n">
-        <v>84.87934076273497</v>
+        <v>84.87934076273498</v>
       </c>
       <c r="BL278" s="197" t="n">
         <v>118.5676032367616</v>
@@ -54690,13 +54690,13 @@
         <v>128.6957436340165</v>
       </c>
       <c r="BN278" s="190" t="n">
-        <v>139.345594676778</v>
+        <v>139.3455946767779</v>
       </c>
       <c r="BO278" s="190" t="n">
         <v>142.3435694709199</v>
       </c>
       <c r="BP278" s="198" t="n">
-        <v>153.192981760672</v>
+        <v>153.1929817606721</v>
       </c>
       <c r="BR278" s="111" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>28.22007194488907</v>
       </c>
       <c r="BU278" s="190" t="n">
-        <v>43.76101560028664</v>
+        <v>43.76101560028665</v>
       </c>
       <c r="BV278" s="190" t="n">
         <v>56.35384480623186</v>
@@ -54725,13 +54725,13 @@
         <v>100.5549145594557</v>
       </c>
       <c r="BZ278" s="190" t="n">
-        <v>95.66368651665945</v>
+        <v>95.66368651665942</v>
       </c>
       <c r="CA278" s="190" t="n">
         <v>86.06912132105926</v>
       </c>
       <c r="CB278" s="198" t="n">
-        <v>85.87751955292957</v>
+        <v>85.87751955292958</v>
       </c>
       <c r="CC278" s="197" t="n">
         <v>118.6462644634676</v>
@@ -54908,7 +54908,7 @@
         <v>16.97838544135367</v>
       </c>
       <c r="AS279" s="207" t="n">
-        <v>14.30888200976918</v>
+        <v>14.30888200976917</v>
       </c>
       <c r="AT279" s="208" t="n">
         <v>14.51253046850165</v>
@@ -54958,7 +54958,7 @@
         <v>16.97838544135367</v>
       </c>
       <c r="BJ279" s="212" t="n">
-        <v>14.30888200976918</v>
+        <v>14.30888200976917</v>
       </c>
       <c r="BK279" s="213" t="n">
         <v>14.51253046850165</v>
@@ -55164,16 +55164,16 @@
         </is>
       </c>
       <c r="AK280" s="206" t="n">
-        <v>64.90820670948204</v>
+        <v>64.90820670948202</v>
       </c>
       <c r="AL280" s="207" t="n">
-        <v>139.6623002618838</v>
+        <v>139.6623002618839</v>
       </c>
       <c r="AM280" s="207" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="AN280" s="207" t="n">
-        <v>263.2818605592663</v>
+        <v>263.2818605592662</v>
       </c>
       <c r="AO280" s="208" t="n">
         <v>294.5160029551956</v>
@@ -55214,16 +55214,16 @@
         </is>
       </c>
       <c r="BB280" s="221" t="n">
-        <v>64.90820670948204</v>
+        <v>64.90820670948202</v>
       </c>
       <c r="BC280" s="222" t="n">
-        <v>139.6623002618838</v>
+        <v>139.6623002618839</v>
       </c>
       <c r="BD280" s="222" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="BE280" s="222" t="n">
-        <v>263.2818605592663</v>
+        <v>263.2818605592662</v>
       </c>
       <c r="BF280" s="214" t="n">
         <v>294.5160029551956</v>
@@ -55285,7 +55285,7 @@
         <v>299.633922970141</v>
       </c>
       <c r="BZ280" s="222" t="n">
-        <v>285.2835873078872</v>
+        <v>285.2835873078871</v>
       </c>
       <c r="CA280" s="222" t="n">
         <v>270.0731050516882</v>
@@ -58318,7 +58318,7 @@
         <v>99.20268881209788</v>
       </c>
       <c r="AT294" s="195" t="n">
-        <v>89.68714935167567</v>
+        <v>89.68714935167566</v>
       </c>
       <c r="AU294" s="190" t="n">
         <v>120.2436157232417</v>
@@ -58368,7 +58368,7 @@
         <v>99.20268881209788</v>
       </c>
       <c r="BK294" s="198" t="n">
-        <v>89.68714935167567</v>
+        <v>89.68714935167566</v>
       </c>
       <c r="BL294" s="199" t="n">
         <v>120.2436157232417</v>
@@ -58418,7 +58418,7 @@
         <v>100.81808537262</v>
       </c>
       <c r="CB294" s="198" t="n">
-        <v>91.52947777942929</v>
+        <v>91.52947777942927</v>
       </c>
       <c r="CC294" s="199" t="n">
         <v>120.8890545119735</v>
@@ -58463,19 +58463,19 @@
         <v>2366</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>0.6454387887317972</v>
+        <v>0.6454387887317998</v>
       </c>
       <c r="CX294" s="200" t="n">
-        <v>0.5738078228343186</v>
+        <v>0.5738078228343207</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>0.5642210685925358</v>
+        <v>0.5642210685925376</v>
       </c>
       <c r="CZ294" s="200" t="n">
-        <v>0.5462383402166368</v>
+        <v>0.5462383402166385</v>
       </c>
       <c r="DA294" s="201" t="n">
-        <v>0.5331966353622142</v>
+        <v>0.5331966353622157</v>
       </c>
     </row>
     <row r="295">
@@ -58586,25 +58586,25 @@
         </is>
       </c>
       <c r="AK295" s="194" t="n">
-        <v>27.10789901090663</v>
+        <v>27.10789901090662</v>
       </c>
       <c r="AL295" s="179" t="n">
-        <v>49.58255201573819</v>
+        <v>49.58255201573821</v>
       </c>
       <c r="AM295" s="179" t="n">
         <v>67.83338551434517</v>
       </c>
       <c r="AN295" s="179" t="n">
-        <v>74.47154139200723</v>
+        <v>74.47154139200721</v>
       </c>
       <c r="AO295" s="195" t="n">
-        <v>79.83556699614779</v>
+        <v>79.8355669961478</v>
       </c>
       <c r="AP295" s="194" t="n">
-        <v>69.20027670287119</v>
+        <v>69.20027670287121</v>
       </c>
       <c r="AQ295" s="179" t="n">
-        <v>69.32151457152676</v>
+        <v>69.32151457152678</v>
       </c>
       <c r="AR295" s="179" t="n">
         <v>68.27813854510515</v>
@@ -58628,7 +58628,7 @@
         <v>142.3789668149968</v>
       </c>
       <c r="AY295" s="196" t="n">
-        <v>146.750093231066</v>
+        <v>146.7500932310661</v>
       </c>
       <c r="BA295" s="101" t="inlineStr">
         <is>
@@ -58636,25 +58636,25 @@
         </is>
       </c>
       <c r="BB295" s="197" t="n">
-        <v>27.10789901090663</v>
+        <v>27.10789901090662</v>
       </c>
       <c r="BC295" s="190" t="n">
-        <v>49.58255201573819</v>
+        <v>49.58255201573821</v>
       </c>
       <c r="BD295" s="190" t="n">
         <v>67.83338551434517</v>
       </c>
       <c r="BE295" s="190" t="n">
-        <v>74.47154139200723</v>
+        <v>74.47154139200721</v>
       </c>
       <c r="BF295" s="198" t="n">
-        <v>79.83556699614779</v>
+        <v>79.8355669961478</v>
       </c>
       <c r="BG295" s="197" t="n">
-        <v>69.20027670287119</v>
+        <v>69.20027670287121</v>
       </c>
       <c r="BH295" s="190" t="n">
-        <v>69.32151457152676</v>
+        <v>69.32151457152678</v>
       </c>
       <c r="BI295" s="190" t="n">
         <v>68.27813854510515</v>
@@ -58678,7 +58678,7 @@
         <v>142.3789668149968</v>
       </c>
       <c r="BP295" s="198" t="n">
-        <v>146.750093231066</v>
+        <v>146.7500932310661</v>
       </c>
       <c r="BR295" s="101" t="inlineStr">
         <is>
@@ -58686,25 +58686,25 @@
         </is>
       </c>
       <c r="BS295" s="197" t="n">
-        <v>26.91528265947908</v>
+        <v>26.91528265947907</v>
       </c>
       <c r="BT295" s="190" t="n">
-        <v>49.2258398159764</v>
+        <v>49.22583981597641</v>
       </c>
       <c r="BU295" s="190" t="n">
         <v>67.28893941810736</v>
       </c>
       <c r="BV295" s="190" t="n">
-        <v>73.75964655793224</v>
+        <v>73.75964655793223</v>
       </c>
       <c r="BW295" s="198" t="n">
-        <v>78.9550664367614</v>
+        <v>78.95506643676141</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>69.49659448176469</v>
+        <v>69.4965944817647</v>
       </c>
       <c r="BY295" s="190" t="n">
-        <v>69.76576224395188</v>
+        <v>69.7657622439519</v>
       </c>
       <c r="BZ295" s="190" t="n">
         <v>68.91047548643553</v>
@@ -58728,7 +58728,7 @@
         <v>142.4660911302791</v>
       </c>
       <c r="CG295" s="198" t="n">
-        <v>146.825619891889</v>
+        <v>146.8256198918891</v>
       </c>
       <c r="CI295" s="197" t="n">
         <v>0</v>
@@ -58758,19 +58758,19 @@
         <v>6058</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>0.1037014274659339</v>
+        <v>0.1037014274659345</v>
       </c>
       <c r="CX295" s="190" t="n">
-        <v>0.08753547266332015</v>
+        <v>0.08753547266332064</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>0.08789084509257702</v>
+        <v>0.08789084509257751</v>
       </c>
       <c r="CZ295" s="190" t="n">
-        <v>0.08712431528231337</v>
+        <v>0.08712431528231383</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>0.07552666082297217</v>
+        <v>0.07552666082297264</v>
       </c>
     </row>
     <row r="296">
@@ -58887,7 +58887,7 @@
         <v>28.60615917579112</v>
       </c>
       <c r="AM296" s="179" t="n">
-        <v>44.31839797899375</v>
+        <v>44.31839797899376</v>
       </c>
       <c r="AN296" s="179" t="n">
         <v>57.06556265358646</v>
@@ -58902,13 +58902,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="AR296" s="179" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778419</v>
       </c>
       <c r="AS296" s="179" t="n">
         <v>85.27800681733345</v>
       </c>
       <c r="AT296" s="195" t="n">
-        <v>84.87934076273497</v>
+        <v>84.87934076273498</v>
       </c>
       <c r="AU296" s="190" t="n">
         <v>118.5676032367616</v>
@@ -58917,13 +58917,13 @@
         <v>128.6957436340165</v>
       </c>
       <c r="AW296" s="190" t="n">
-        <v>139.345594676778</v>
+        <v>139.3455946767779</v>
       </c>
       <c r="AX296" s="190" t="n">
         <v>142.3435694709199</v>
       </c>
       <c r="AY296" s="196" t="n">
-        <v>153.192981760672</v>
+        <v>153.1929817606721</v>
       </c>
       <c r="BA296" s="111" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>28.60615917579112</v>
       </c>
       <c r="BD296" s="190" t="n">
-        <v>44.31839797899375</v>
+        <v>44.31839797899376</v>
       </c>
       <c r="BE296" s="190" t="n">
         <v>57.06556265358646</v>
@@ -58952,13 +58952,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="BI296" s="190" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778419</v>
       </c>
       <c r="BJ296" s="190" t="n">
         <v>85.27800681733345</v>
       </c>
       <c r="BK296" s="198" t="n">
-        <v>84.87934076273497</v>
+        <v>84.87934076273498</v>
       </c>
       <c r="BL296" s="197" t="n">
         <v>118.5676032367616</v>
@@ -58967,13 +58967,13 @@
         <v>128.6957436340165</v>
       </c>
       <c r="BN296" s="190" t="n">
-        <v>139.345594676778</v>
+        <v>139.3455946767779</v>
       </c>
       <c r="BO296" s="190" t="n">
         <v>142.3435694709199</v>
       </c>
       <c r="BP296" s="198" t="n">
-        <v>153.192981760672</v>
+        <v>153.1929817606721</v>
       </c>
       <c r="BR296" s="111" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>28.22007194488907</v>
       </c>
       <c r="BU296" s="190" t="n">
-        <v>43.76101560028664</v>
+        <v>43.76101560028665</v>
       </c>
       <c r="BV296" s="190" t="n">
         <v>56.35384480623186</v>
@@ -59002,13 +59002,13 @@
         <v>100.5549145594557</v>
       </c>
       <c r="BZ296" s="190" t="n">
-        <v>95.66368651665945</v>
+        <v>95.66368651665942</v>
       </c>
       <c r="CA296" s="190" t="n">
         <v>86.06912132105926</v>
       </c>
       <c r="CB296" s="198" t="n">
-        <v>85.87751955292957</v>
+        <v>85.87751955292958</v>
       </c>
       <c r="CC296" s="197" t="n">
         <v>118.6462644634676</v>
@@ -59053,19 +59053,19 @@
         <v>7686</v>
       </c>
       <c r="CW296" s="197" t="n">
-        <v>0.07866122670599514</v>
+        <v>0.07866122670599779</v>
       </c>
       <c r="CX296" s="190" t="n">
-        <v>0.07924287032825833</v>
+        <v>0.07924287032826124</v>
       </c>
       <c r="CY296" s="190" t="n">
-        <v>0.07910744016811658</v>
+        <v>0.07910744016811977</v>
       </c>
       <c r="CZ296" s="190" t="n">
-        <v>0.07939665637120069</v>
+        <v>0.0793966563712042</v>
       </c>
       <c r="DA296" s="198" t="n">
-        <v>0.07902089963056634</v>
+        <v>0.07902089963056991</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" thickBot="1">
@@ -59200,7 +59200,7 @@
         <v>16.97838544135367</v>
       </c>
       <c r="AS297" s="207" t="n">
-        <v>14.30888200976918</v>
+        <v>14.30888200976917</v>
       </c>
       <c r="AT297" s="208" t="n">
         <v>14.51253046850165</v>
@@ -59250,7 +59250,7 @@
         <v>16.97838544135367</v>
       </c>
       <c r="BJ297" s="212" t="n">
-        <v>14.30888200976918</v>
+        <v>14.30888200976917</v>
       </c>
       <c r="BK297" s="213" t="n">
         <v>14.51253046850165</v>
@@ -59348,19 +59348,19 @@
         <v>1566</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.01246836212360525</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157651</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989072</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069211</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>0.01372109225177184</v>
+        <v>0.01372109225177174</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59471,16 +59471,16 @@
         </is>
       </c>
       <c r="AK298" s="206" t="n">
-        <v>64.90820670948204</v>
+        <v>64.90820670948202</v>
       </c>
       <c r="AL298" s="207" t="n">
-        <v>139.6623002618838</v>
+        <v>139.6623002618839</v>
       </c>
       <c r="AM298" s="207" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="AN298" s="207" t="n">
-        <v>263.2818605592663</v>
+        <v>263.2818605592662</v>
       </c>
       <c r="AO298" s="208" t="n">
         <v>294.5160029551956</v>
@@ -59521,16 +59521,16 @@
         </is>
       </c>
       <c r="BB298" s="221" t="n">
-        <v>64.90820670948204</v>
+        <v>64.90820670948202</v>
       </c>
       <c r="BC298" s="222" t="n">
-        <v>139.6623002618838</v>
+        <v>139.6623002618839</v>
       </c>
       <c r="BD298" s="222" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="BE298" s="222" t="n">
-        <v>263.2818605592663</v>
+        <v>263.2818605592662</v>
       </c>
       <c r="BF298" s="214" t="n">
         <v>294.5160029551956</v>
@@ -59643,19 +59643,19 @@
         <v>17676</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273374</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>0.7533784559974737</v>
+        <v>0.7533784559974792</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>0.7444004017231203</v>
+        <v>0.7444004017231256</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908487</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675301</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -60428,7 +60428,7 @@
         <v>0.4800766142998141</v>
       </c>
       <c r="AR303" s="190" t="n">
-        <v>0.8000276527462006</v>
+        <v>0.8000276527462007</v>
       </c>
       <c r="AS303" s="190" t="n">
         <v>1.069158220305477</v>
@@ -60449,7 +60449,7 @@
         <v>100.2718470324034</v>
       </c>
       <c r="AY303" s="196" t="n">
-        <v>90.99628114406707</v>
+        <v>90.99628114406705</v>
       </c>
       <c r="BA303" s="83" t="inlineStr">
         <is>
@@ -60478,7 +60478,7 @@
         <v>0.4800766142998141</v>
       </c>
       <c r="BI303" s="190" t="n">
-        <v>0.8000276527462006</v>
+        <v>0.8000276527462007</v>
       </c>
       <c r="BJ303" s="190" t="n">
         <v>1.069158220305477</v>
@@ -60499,7 +60499,7 @@
         <v>100.2718470324034</v>
       </c>
       <c r="BP303" s="201" t="n">
-        <v>90.99628114406707</v>
+        <v>90.99628114406705</v>
       </c>
       <c r="BR303" s="83" t="inlineStr">
         <is>
@@ -60522,34 +60522,34 @@
         <v>0</v>
       </c>
       <c r="BX303" s="462" t="n">
-        <v>0.06819052146228914</v>
+        <v>0.06819052146228913</v>
       </c>
       <c r="BY303" s="463" t="n">
-        <v>0.07149065642823374</v>
+        <v>0.07149065642823371</v>
       </c>
       <c r="BZ303" s="463" t="n">
-        <v>0.07760102479179193</v>
+        <v>0.07760102479179189</v>
       </c>
       <c r="CA303" s="463" t="n">
-        <v>0.06265916910334451</v>
+        <v>0.0626591691033445</v>
       </c>
       <c r="CB303" s="464" t="n">
-        <v>-0.005894079759251489</v>
+        <v>-0.005894079759251507</v>
       </c>
       <c r="CC303" s="199" t="n">
-        <v>7.181997748466757</v>
+        <v>7.181997748466756</v>
       </c>
       <c r="CD303" s="200" t="n">
-        <v>7.622411855860021</v>
+        <v>7.622411855860018</v>
       </c>
       <c r="CE303" s="200" t="n">
-        <v>8.039122839299148</v>
+        <v>8.039122839299145</v>
       </c>
       <c r="CF303" s="200" t="n">
-        <v>6.31717746003842</v>
+        <v>6.317177460038419</v>
       </c>
       <c r="CG303" s="201" t="n">
-        <v>-0.5394820423545931</v>
+        <v>-0.5394820423545946</v>
       </c>
     </row>
     <row r="304">
@@ -60677,7 +60677,7 @@
         <v>0.1926163514275556</v>
       </c>
       <c r="AQ304" s="190" t="n">
-        <v>0.3567121997617949</v>
+        <v>0.356712199761795</v>
       </c>
       <c r="AR304" s="190" t="n">
         <v>0.5444460962378013</v>
@@ -60686,13 +60686,13 @@
         <v>0.7118948340749839</v>
       </c>
       <c r="AT304" s="196" t="n">
-        <v>0.8805005593863963</v>
+        <v>0.8805005593863965</v>
       </c>
       <c r="AU304" s="190" t="n">
-        <v>69.39289305429875</v>
+        <v>69.39289305429877</v>
       </c>
       <c r="AV304" s="190" t="n">
-        <v>69.67822677128856</v>
+        <v>69.67822677128858</v>
       </c>
       <c r="AW304" s="190" t="n">
         <v>68.82258464134296</v>
@@ -60727,7 +60727,7 @@
         <v>0.1926163514275556</v>
       </c>
       <c r="BH304" s="190" t="n">
-        <v>0.3567121997617949</v>
+        <v>0.356712199761795</v>
       </c>
       <c r="BI304" s="190" t="n">
         <v>0.5444460962378013</v>
@@ -60736,13 +60736,13 @@
         <v>0.7118948340749839</v>
       </c>
       <c r="BK304" s="198" t="n">
-        <v>0.8805005593863963</v>
+        <v>0.8805005593863965</v>
       </c>
       <c r="BL304" s="197" t="n">
-        <v>69.39289305429875</v>
+        <v>69.39289305429877</v>
       </c>
       <c r="BM304" s="190" t="n">
-        <v>69.67822677128856</v>
+        <v>69.67822677128858</v>
       </c>
       <c r="BN304" s="190" t="n">
         <v>68.82258464134296</v>
@@ -60774,34 +60774,34 @@
         <v>0</v>
       </c>
       <c r="BX304" s="462" t="n">
-        <v>-0.001496646519192103</v>
+        <v>-0.00149664651919211</v>
       </c>
       <c r="BY304" s="463" t="n">
-        <v>-0.001257861806368482</v>
+        <v>-0.001257861806368489</v>
       </c>
       <c r="BZ304" s="463" t="n">
-        <v>-0.001278696975840338</v>
+        <v>-0.001278696975840345</v>
       </c>
       <c r="CA304" s="463" t="n">
-        <v>-0.001271290290425321</v>
+        <v>-0.001271290290425328</v>
       </c>
       <c r="CB304" s="464" t="n">
-        <v>-0.00111528674420369</v>
+        <v>-0.001115286744203697</v>
       </c>
       <c r="CC304" s="197" t="n">
-        <v>-0.1040118362268382</v>
+        <v>-0.1040118362268388</v>
       </c>
       <c r="CD304" s="190" t="n">
-        <v>-0.08775568771885137</v>
+        <v>-0.08775568771885185</v>
       </c>
       <c r="CE304" s="190" t="n">
-        <v>-0.08811561660822487</v>
+        <v>-0.08811561660822537</v>
       </c>
       <c r="CF304" s="190" t="n">
-        <v>-0.08734583587447008</v>
+        <v>-0.08734583587447053</v>
       </c>
       <c r="CG304" s="198" t="n">
-        <v>-0.07569512859027183</v>
+        <v>-0.0756951285902723</v>
       </c>
     </row>
     <row r="305">
@@ -60932,13 +60932,13 @@
         <v>0.3860872309020495</v>
       </c>
       <c r="AR305" s="190" t="n">
-        <v>0.5573823787071119</v>
+        <v>0.5573823787071118</v>
       </c>
       <c r="AS305" s="190" t="n">
         <v>0.7117178473545995</v>
       </c>
       <c r="AT305" s="196" t="n">
-        <v>0.9191578905640323</v>
+        <v>0.9191578905640324</v>
       </c>
       <c r="AU305" s="190" t="n">
         <v>102.2587926087093</v>
@@ -60947,13 +60947,13 @@
         <v>100.4756716891274</v>
       </c>
       <c r="AW305" s="190" t="n">
-        <v>95.58457907649134</v>
+        <v>95.58457907649131</v>
       </c>
       <c r="AX305" s="190" t="n">
         <v>85.98972466468805</v>
       </c>
       <c r="AY305" s="196" t="n">
-        <v>85.79849865329901</v>
+        <v>85.79849865329902</v>
       </c>
       <c r="BA305" s="111" t="inlineStr">
         <is>
@@ -60982,13 +60982,13 @@
         <v>0.3860872309020495</v>
       </c>
       <c r="BI305" s="190" t="n">
-        <v>0.5573823787071119</v>
+        <v>0.5573823787071118</v>
       </c>
       <c r="BJ305" s="190" t="n">
         <v>0.7117178473545995</v>
       </c>
       <c r="BK305" s="198" t="n">
-        <v>0.9191578905640323</v>
+        <v>0.9191578905640324</v>
       </c>
       <c r="BL305" s="197" t="n">
         <v>102.2587926087093</v>
@@ -60997,13 +60997,13 @@
         <v>100.4756716891274</v>
       </c>
       <c r="BN305" s="190" t="n">
-        <v>95.58457907649134</v>
+        <v>95.58457907649131</v>
       </c>
       <c r="BO305" s="190" t="n">
         <v>85.98972466468805</v>
       </c>
       <c r="BP305" s="198" t="n">
-        <v>85.79849865329901</v>
+        <v>85.79849865329902</v>
       </c>
       <c r="BR305" s="111" t="inlineStr">
         <is>
@@ -61026,34 +61026,34 @@
         <v>0</v>
       </c>
       <c r="BX305" s="462" t="n">
-        <v>-0.0007698289837964475</v>
+        <v>-0.0007698289837964736</v>
       </c>
       <c r="BY305" s="463" t="n">
-        <v>-0.0007892996918374466</v>
+        <v>-0.0007892996918374756</v>
       </c>
       <c r="BZ305" s="463" t="n">
-        <v>-0.0008283027015389342</v>
+        <v>-0.0008283027015389678</v>
       </c>
       <c r="CA305" s="463" t="n">
-        <v>-0.0009241805753961784</v>
+        <v>-0.0009241805753962193</v>
       </c>
       <c r="CB305" s="464" t="n">
-        <v>-0.0009218546554570507</v>
+        <v>-0.0009218546554570921</v>
       </c>
       <c r="CC305" s="197" t="n">
-        <v>-0.07878233809043364</v>
+        <v>-0.07878233809043633</v>
       </c>
       <c r="CD305" s="190" t="n">
-        <v>-0.07936796307451914</v>
+        <v>-0.07936796307452207</v>
       </c>
       <c r="CE305" s="190" t="n">
-        <v>-0.07923848998092274</v>
+        <v>-0.07923848998092593</v>
       </c>
       <c r="CF305" s="190" t="n">
-        <v>-0.07954341006634004</v>
+        <v>-0.07954341006634355</v>
       </c>
       <c r="CG305" s="198" t="n">
-        <v>-0.07916659119897201</v>
+        <v>-0.07916659119897559</v>
       </c>
     </row>
     <row r="306" ht="15.75" customHeight="1" thickBot="1">
@@ -61187,7 +61187,7 @@
         <v>0.1222831016062601</v>
       </c>
       <c r="AS306" s="209" t="n">
-        <v>0.1571234163722211</v>
+        <v>0.157123416372221</v>
       </c>
       <c r="AT306" s="210" t="n">
         <v>0.1942670562963336</v>
@@ -61237,7 +61237,7 @@
         <v>0.1222831016062601</v>
       </c>
       <c r="BJ306" s="212" t="n">
-        <v>0.1571234163722211</v>
+        <v>0.157123416372221</v>
       </c>
       <c r="BK306" s="213" t="n">
         <v>0.1942670562963336</v>
@@ -61278,34 +61278,34 @@
         <v>0</v>
       </c>
       <c r="BX306" s="466" t="n">
-        <v>-0.0005324438391599065</v>
+        <v>-0.0005324438391599025</v>
       </c>
       <c r="BY306" s="467" t="n">
-        <v>-0.0005643681599164509</v>
+        <v>-0.0005643681599164468</v>
       </c>
       <c r="BZ306" s="467" t="n">
-        <v>-0.0007713859555817255</v>
+        <v>-0.0007713859555817198</v>
       </c>
       <c r="CA306" s="467" t="n">
-        <v>-0.0009305176557131352</v>
+        <v>-0.0009305176557131287</v>
       </c>
       <c r="CB306" s="468" t="n">
-        <v>-0.0009338474699130162</v>
+        <v>-0.0009338474699130095</v>
       </c>
       <c r="CC306" s="212" t="n">
-        <v>-0.0124816395287996</v>
+        <v>-0.01248163952879951</v>
       </c>
       <c r="CD306" s="212" t="n">
-        <v>-0.01280672929410711</v>
+        <v>-0.01280672929410701</v>
       </c>
       <c r="CE306" s="212" t="n">
-        <v>-0.01320138322030419</v>
+        <v>-0.01320138322030409</v>
       </c>
       <c r="CF306" s="212" t="n">
-        <v>-0.01347338739264097</v>
+        <v>-0.01347338739264087</v>
       </c>
       <c r="CG306" s="213" t="n">
-        <v>-0.01374671906633936</v>
+        <v>-0.01374671906633926</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" thickBot="1">
@@ -61457,7 +61457,7 @@
         <v>269.3468973802973</v>
       </c>
       <c r="AY307" s="208" t="n">
-        <v>259.2966041164688</v>
+        <v>259.2966041164687</v>
       </c>
       <c r="BA307" s="155" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>269.3468973802973</v>
       </c>
       <c r="BP307" s="214" t="n">
-        <v>259.2966041164688</v>
+        <v>259.2966041164687</v>
       </c>
       <c r="BR307" s="155" t="inlineStr">
         <is>
@@ -61530,34 +61530,34 @@
         <v>0</v>
       </c>
       <c r="BX307" s="466" t="n">
-        <v>0.02324268520315748</v>
+        <v>0.02324268520315747</v>
       </c>
       <c r="BY307" s="467" t="n">
-        <v>0.02483858103247608</v>
+        <v>0.02483858103247606</v>
       </c>
       <c r="BZ307" s="467" t="n">
-        <v>0.0275465105569094</v>
+        <v>0.02754651055690938</v>
       </c>
       <c r="CA307" s="467" t="n">
-        <v>0.02272279139209537</v>
+        <v>0.02272279139209536</v>
       </c>
       <c r="CB307" s="468" t="n">
-        <v>-0.002723445150311651</v>
+        <v>-0.002723445150311673</v>
       </c>
       <c r="CC307" s="212" t="n">
-        <v>6.986721934620685</v>
+        <v>6.986721934620681</v>
       </c>
       <c r="CD307" s="212" t="n">
-        <v>7.442481475772543</v>
+        <v>7.442481475772537</v>
       </c>
       <c r="CE307" s="212" t="n">
-        <v>7.858567349489697</v>
+        <v>7.858567349489689</v>
       </c>
       <c r="CF307" s="212" t="n">
-        <v>6.136814826704969</v>
+        <v>6.136814826704964</v>
       </c>
       <c r="CG307" s="213" t="n">
-        <v>-0.7080904812101763</v>
+        <v>-0.7080904812101818</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1" thickBot="1">
@@ -62319,7 +62319,7 @@
         <v>0.3403102479022413</v>
       </c>
       <c r="AR312" s="463" t="n">
-        <v>0.4888610330320406</v>
+        <v>0.4888610330320405</v>
       </c>
       <c r="AS312" s="463" t="n">
         <v>0.5360710560512085</v>
@@ -62369,7 +62369,7 @@
         <v>0.3403102479022413</v>
       </c>
       <c r="BI312" s="463" t="n">
-        <v>0.4888610330320406</v>
+        <v>0.4888610330320405</v>
       </c>
       <c r="BJ312" s="463" t="n">
         <v>0.5360710560512085</v>
@@ -62419,13 +62419,13 @@
         <v>0.3361050670351812</v>
       </c>
       <c r="BZ312" s="463" t="n">
-        <v>0.4834970839713138</v>
+        <v>0.4834970839713137</v>
       </c>
       <c r="CA312" s="463" t="n">
         <v>0.5297178783402193</v>
       </c>
       <c r="CB312" s="464" t="n">
-        <v>0.581525637732653</v>
+        <v>0.5815256377326531</v>
       </c>
       <c r="CC312" s="478" t="n">
         <v>0</v>
@@ -62553,22 +62553,22 @@
         </is>
       </c>
       <c r="AK313" s="233" t="n">
-        <v>26.91528265947908</v>
+        <v>26.91528265947907</v>
       </c>
       <c r="AL313" s="190" t="n">
-        <v>49.2258398159764</v>
+        <v>49.22583981597641</v>
       </c>
       <c r="AM313" s="190" t="n">
         <v>67.28893941810736</v>
       </c>
       <c r="AN313" s="190" t="n">
-        <v>73.75964655793224</v>
+        <v>73.75964655793223</v>
       </c>
       <c r="AO313" s="196" t="n">
-        <v>78.9550664367614</v>
+        <v>78.95506643676141</v>
       </c>
       <c r="AP313" s="473" t="n">
-        <v>0.2814703820314248</v>
+        <v>0.2814703820314247</v>
       </c>
       <c r="AQ313" s="463" t="n">
         <v>0.4169962679901199</v>
@@ -62577,13 +62577,13 @@
         <v>0.4983662183131322</v>
       </c>
       <c r="AS313" s="463" t="n">
-        <v>0.5230515648338244</v>
+        <v>0.5230515648338243</v>
       </c>
       <c r="AT313" s="474" t="n">
         <v>0.5440239609963472</v>
       </c>
       <c r="AU313" s="463" t="n">
-        <v>0.2794703820314248</v>
+        <v>0.2794703820314247</v>
       </c>
       <c r="AV313" s="463" t="n">
         <v>0.4139962679901198</v>
@@ -62603,22 +62603,22 @@
         </is>
       </c>
       <c r="BB313" s="197" t="n">
-        <v>26.91528265947908</v>
+        <v>26.91528265947907</v>
       </c>
       <c r="BC313" s="190" t="n">
-        <v>49.2258398159764</v>
+        <v>49.22583981597641</v>
       </c>
       <c r="BD313" s="190" t="n">
         <v>67.28893941810736</v>
       </c>
       <c r="BE313" s="190" t="n">
-        <v>73.75964655793224</v>
+        <v>73.75964655793223</v>
       </c>
       <c r="BF313" s="198" t="n">
-        <v>78.9550664367614</v>
+        <v>78.95506643676141</v>
       </c>
       <c r="BG313" s="462" t="n">
-        <v>0.2814703820314248</v>
+        <v>0.2814703820314247</v>
       </c>
       <c r="BH313" s="463" t="n">
         <v>0.4169962679901199</v>
@@ -62627,13 +62627,13 @@
         <v>0.4983662183131322</v>
       </c>
       <c r="BJ313" s="463" t="n">
-        <v>0.5230515648338244</v>
+        <v>0.5230515648338243</v>
       </c>
       <c r="BK313" s="464" t="n">
         <v>0.5440239609963472</v>
       </c>
       <c r="BL313" s="462" t="n">
-        <v>0.2794703820314248</v>
+        <v>0.2794703820314247</v>
       </c>
       <c r="BM313" s="463" t="n">
         <v>0.4139962679901198</v>
@@ -62677,7 +62677,7 @@
         <v>0.494047198846395</v>
       </c>
       <c r="CA313" s="463" t="n">
-        <v>0.5177347533911226</v>
+        <v>0.5177347533911225</v>
       </c>
       <c r="CB313" s="464" t="n">
         <v>0.5377472030759874</v>
@@ -62814,7 +62814,7 @@
         <v>28.22007194488907</v>
       </c>
       <c r="AM314" s="190" t="n">
-        <v>43.76101560028664</v>
+        <v>43.76101560028665</v>
       </c>
       <c r="AN314" s="190" t="n">
         <v>56.35384480623186</v>
@@ -62829,7 +62829,7 @@
         <v>0.2222774302244291</v>
       </c>
       <c r="AR314" s="463" t="n">
-        <v>0.318046638516226</v>
+        <v>0.3180466385162261</v>
       </c>
       <c r="AS314" s="463" t="n">
         <v>0.4009001802167444</v>
@@ -62844,13 +62844,13 @@
         <v>0.2192774302244291</v>
       </c>
       <c r="AW314" s="463" t="n">
-        <v>0.314046638516226</v>
+        <v>0.3140466385162261</v>
       </c>
       <c r="AX314" s="463" t="n">
         <v>0.3959001802167444</v>
       </c>
       <c r="AY314" s="474" t="n">
-        <v>0.4399319233348499</v>
+        <v>0.4399319233348498</v>
       </c>
       <c r="BA314" s="111" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>28.22007194488907</v>
       </c>
       <c r="BD314" s="190" t="n">
-        <v>43.76101560028664</v>
+        <v>43.76101560028665</v>
       </c>
       <c r="BE314" s="190" t="n">
         <v>56.35384480623186</v>
@@ -62879,7 +62879,7 @@
         <v>0.2222774302244291</v>
       </c>
       <c r="BI314" s="463" t="n">
-        <v>0.318046638516226</v>
+        <v>0.3180466385162261</v>
       </c>
       <c r="BJ314" s="463" t="n">
         <v>0.4009001802167444</v>
@@ -62894,13 +62894,13 @@
         <v>0.2192774302244291</v>
       </c>
       <c r="BN314" s="463" t="n">
-        <v>0.314046638516226</v>
+        <v>0.3140466385162261</v>
       </c>
       <c r="BO314" s="463" t="n">
         <v>0.3959001802167444</v>
       </c>
       <c r="BP314" s="464" t="n">
-        <v>0.4399319233348499</v>
+        <v>0.4399319233348498</v>
       </c>
       <c r="BR314" s="111" t="inlineStr">
         <is>
@@ -62923,13 +62923,13 @@
         <v>0</v>
       </c>
       <c r="BX314" s="462" t="n">
-        <v>0.1374574303017682</v>
+        <v>0.1374574303017681</v>
       </c>
       <c r="BY314" s="463" t="n">
-        <v>0.2191424958443848</v>
+        <v>0.2191424958443847</v>
       </c>
       <c r="BZ314" s="463" t="n">
-        <v>0.3138684532643358</v>
+        <v>0.3138684532643359</v>
       </c>
       <c r="CA314" s="463" t="n">
         <v>0.3956794773945754</v>
@@ -63102,7 +63102,7 @@
         <v>0.4406203860277455</v>
       </c>
       <c r="AX315" s="490" t="n">
-        <v>0.5396610587987779</v>
+        <v>0.539661058798778</v>
       </c>
       <c r="AY315" s="491" t="n">
         <v>0.5457758673493976</v>
@@ -63152,7 +63152,7 @@
         <v>0.4406203860277455</v>
       </c>
       <c r="BO315" s="467" t="n">
-        <v>0.5396610587987779</v>
+        <v>0.539661058798778</v>
       </c>
       <c r="BP315" s="468" t="n">
         <v>0.5457758673493976</v>
@@ -63318,13 +63318,13 @@
         </is>
       </c>
       <c r="AK316" s="206" t="n">
-        <v>64.1803291067195</v>
+        <v>64.18032910671948</v>
       </c>
       <c r="AL316" s="207" t="n">
         <v>138.3506068079177</v>
       </c>
       <c r="AM316" s="207" t="n">
-        <v>221.4956204181794</v>
+        <v>221.4956204181795</v>
       </c>
       <c r="AN316" s="207" t="n">
         <v>260.631966241159</v>
@@ -63333,16 +63333,16 @@
         <v>291.2129456565575</v>
       </c>
       <c r="AP316" s="500" t="n">
-        <v>0.1783492347151064</v>
+        <v>0.1783492347151063</v>
       </c>
       <c r="AQ316" s="501" t="n">
-        <v>0.3194244047789944</v>
+        <v>0.3194244047789945</v>
       </c>
       <c r="AR316" s="501" t="n">
-        <v>0.4417082706806997</v>
+        <v>0.4417082706806998</v>
       </c>
       <c r="AS316" s="501" t="n">
-        <v>0.496778038958396</v>
+        <v>0.4967780389583959</v>
       </c>
       <c r="AT316" s="502" t="n">
         <v>0.5349879998932332</v>
@@ -63354,7 +63354,7 @@
         <v>0.3164244047789945</v>
       </c>
       <c r="AW316" s="501" t="n">
-        <v>0.4377082706806997</v>
+        <v>0.4377082706806998</v>
       </c>
       <c r="AX316" s="501" t="n">
         <v>0.491778038958396</v>
@@ -63368,13 +63368,13 @@
         </is>
       </c>
       <c r="BB316" s="221" t="n">
-        <v>64.1803291067195</v>
+        <v>64.18032910671948</v>
       </c>
       <c r="BC316" s="222" t="n">
         <v>138.3506068079177</v>
       </c>
       <c r="BD316" s="222" t="n">
-        <v>221.4956204181794</v>
+        <v>221.4956204181795</v>
       </c>
       <c r="BE316" s="222" t="n">
         <v>260.631966241159</v>
@@ -63383,16 +63383,16 @@
         <v>291.2129456565575</v>
       </c>
       <c r="BG316" s="503" t="n">
-        <v>0.1783492347151064</v>
+        <v>0.1783492347151063</v>
       </c>
       <c r="BH316" s="504" t="n">
-        <v>0.3194244047789944</v>
+        <v>0.3194244047789945</v>
       </c>
       <c r="BI316" s="504" t="n">
-        <v>0.4417082706806997</v>
+        <v>0.4417082706806998</v>
       </c>
       <c r="BJ316" s="504" t="n">
-        <v>0.496778038958396</v>
+        <v>0.4967780389583959</v>
       </c>
       <c r="BK316" s="505" t="n">
         <v>0.5349879998932332</v>
@@ -63404,7 +63404,7 @@
         <v>0.3164244047789945</v>
       </c>
       <c r="BN316" s="504" t="n">
-        <v>0.4377082706806997</v>
+        <v>0.4377082706806998</v>
       </c>
       <c r="BO316" s="504" t="n">
         <v>0.491778038958396</v>
@@ -63442,7 +63442,7 @@
         <v>0.4370653275457707</v>
       </c>
       <c r="CA316" s="504" t="n">
-        <v>0.4911050983670368</v>
+        <v>0.4911050983670367</v>
       </c>
       <c r="CB316" s="505" t="n">
         <v>0.5283148153784277</v>
@@ -64107,7 +64107,7 @@
         </is>
       </c>
       <c r="AK323" s="506" t="n">
-        <v>9300.448898384631</v>
+        <v>9300.44889838463</v>
       </c>
       <c r="AL323" s="368" t="n">
         <v>34513.2223587984</v>
@@ -64122,7 +64122,7 @@
         <v>89580.48173789636</v>
       </c>
       <c r="AP323" s="381" t="n">
-        <v>588.3746268593677</v>
+        <v>588.3746268593676</v>
       </c>
       <c r="AQ323" s="372" t="n">
         <v>633.7546894227795</v>
@@ -64142,7 +64142,7 @@
         </is>
       </c>
       <c r="BB323" s="391" t="n">
-        <v>9300.448898384631</v>
+        <v>9300.44889838463</v>
       </c>
       <c r="BC323" s="375" t="n">
         <v>34513.2223587984</v>
@@ -64157,7 +64157,7 @@
         <v>89580.48173789636</v>
       </c>
       <c r="BG323" s="386" t="n">
-        <v>588.3746268593677</v>
+        <v>588.3746268593676</v>
       </c>
       <c r="BH323" s="372" t="n">
         <v>633.7546894227795</v>
@@ -64177,7 +64177,7 @@
         </is>
       </c>
       <c r="BS323" s="391" t="n">
-        <v>9158.952313317865</v>
+        <v>9158.952313317863</v>
       </c>
       <c r="BT323" s="375" t="n">
         <v>34208.97155320368</v>
@@ -64192,7 +64192,7 @@
         <v>88667.86459026212</v>
       </c>
       <c r="BX323" s="386" t="n">
-        <v>588.3746268593677</v>
+        <v>588.3746268593676</v>
       </c>
       <c r="BY323" s="372" t="n">
         <v>633.7546894227795</v>
@@ -64305,7 +64305,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="AL324" s="368" t="n">
-        <v>90066.83119143535</v>
+        <v>90066.83119143533</v>
       </c>
       <c r="AM324" s="368" t="n">
         <v>128629.5373619414</v>
@@ -64320,13 +64320,13 @@
         <v>1635.517697833116</v>
       </c>
       <c r="AQ324" s="372" t="n">
-        <v>1816.502530221657</v>
+        <v>1816.502530221656</v>
       </c>
       <c r="AR324" s="372" t="n">
         <v>1896.257077346365</v>
       </c>
       <c r="AS324" s="372" t="n">
-        <v>1944.27038939918</v>
+        <v>1944.270389399181</v>
       </c>
       <c r="AT324" s="382" t="n">
         <v>1996.685743610652</v>
@@ -64340,7 +64340,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="BC324" s="375" t="n">
-        <v>90066.83119143535</v>
+        <v>90066.83119143533</v>
       </c>
       <c r="BD324" s="375" t="n">
         <v>128629.5373619414</v>
@@ -64355,13 +64355,13 @@
         <v>1635.517697833116</v>
       </c>
       <c r="BH324" s="372" t="n">
-        <v>1816.502530221657</v>
+        <v>1816.502530221656</v>
       </c>
       <c r="BI324" s="372" t="n">
         <v>1896.257077346365</v>
       </c>
       <c r="BJ324" s="372" t="n">
-        <v>1944.27038939918</v>
+        <v>1944.270389399181</v>
       </c>
       <c r="BK324" s="387" t="n">
         <v>1996.685743610652</v>
@@ -64375,7 +64375,7 @@
         <v>44020.42113175881</v>
       </c>
       <c r="BT324" s="375" t="n">
-        <v>89418.86257800712</v>
+        <v>89418.86257800709</v>
       </c>
       <c r="BU324" s="375" t="n">
         <v>127597.1275987169</v>
@@ -64390,13 +64390,13 @@
         <v>1635.517697833116</v>
       </c>
       <c r="BY324" s="372" t="n">
-        <v>1816.502530221657</v>
+        <v>1816.502530221656</v>
       </c>
       <c r="BZ324" s="372" t="n">
         <v>1896.257077346365</v>
       </c>
       <c r="CA324" s="372" t="n">
-        <v>1944.27038939918</v>
+        <v>1944.270389399181</v>
       </c>
       <c r="CB324" s="387" t="n">
         <v>1996.685743610652</v>
@@ -64500,13 +64500,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="AL325" s="368" t="n">
-        <v>49819.67164514306</v>
+        <v>49819.67164514307</v>
       </c>
       <c r="AM325" s="368" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="AN325" s="368" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="AO325" s="380" t="n">
         <v>112279.5677980626</v>
@@ -64535,13 +64535,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="BC325" s="375" t="n">
-        <v>49819.67164514306</v>
+        <v>49819.67164514307</v>
       </c>
       <c r="BD325" s="375" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="BE325" s="375" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="BF325" s="392" t="n">
         <v>112279.5677980626</v>
@@ -64570,13 +64570,13 @@
         <v>26769.83350407975</v>
       </c>
       <c r="BT325" s="375" t="n">
-        <v>49147.27312593883</v>
+        <v>49147.27312593884</v>
       </c>
       <c r="BU325" s="375" t="n">
         <v>73574.4154376738</v>
       </c>
       <c r="BV325" s="375" t="n">
-        <v>87640.41389023532</v>
+        <v>87640.41389023533</v>
       </c>
       <c r="BW325" s="392" t="n">
         <v>110768.8497455169</v>
@@ -64713,7 +64713,7 @@
         <v>26075.56952842507</v>
       </c>
       <c r="AR326" s="411" t="n">
-        <v>23846.44159897524</v>
+        <v>23846.44159897525</v>
       </c>
       <c r="AS326" s="411" t="n">
         <v>24329.2099056213</v>
@@ -64748,7 +64748,7 @@
         <v>26075.56952842507</v>
       </c>
       <c r="BI326" s="417" t="n">
-        <v>23846.44159897524</v>
+        <v>23846.44159897525</v>
       </c>
       <c r="BJ326" s="417" t="n">
         <v>24329.2099056213</v>
@@ -64768,7 +64768,7 @@
         <v>180610.8970057784</v>
       </c>
       <c r="BU326" s="420" t="n">
-        <v>321214.116535682</v>
+        <v>321214.1165356821</v>
       </c>
       <c r="BV326" s="420" t="n">
         <v>412591.2330931693</v>
@@ -64783,7 +64783,7 @@
         <v>26075.56952842507</v>
       </c>
       <c r="BZ326" s="417" t="n">
-        <v>23846.44159897524</v>
+        <v>23846.44159897525</v>
       </c>
       <c r="CA326" s="417" t="n">
         <v>24329.2099056213</v>
@@ -64826,13 +64826,13 @@
         <v>589027.1056832182</v>
       </c>
       <c r="F327" s="425" t="n">
-        <v>726495.0525627602</v>
+        <v>726495.0525627601</v>
       </c>
       <c r="G327" s="426" t="n">
         <v>811994.5728673091</v>
       </c>
       <c r="H327" s="427" t="n">
-        <v>2893.401733095192</v>
+        <v>2893.401733095193</v>
       </c>
       <c r="I327" s="427" t="n">
         <v>2611.970298418244</v>
@@ -64861,13 +64861,13 @@
         <v>589027.1056832182</v>
       </c>
       <c r="W327" s="430" t="n">
-        <v>726495.0525627602</v>
+        <v>726495.0525627601</v>
       </c>
       <c r="X327" s="431" t="n">
         <v>811994.5728673091</v>
       </c>
       <c r="Y327" s="432" t="n">
-        <v>2893.401733095192</v>
+        <v>2893.401733095193</v>
       </c>
       <c r="Z327" s="433" t="n">
         <v>2611.970298418244</v>
@@ -64902,7 +64902,7 @@
         <v>812602.7137558617</v>
       </c>
       <c r="AP327" s="436" t="n">
-        <v>2766.195750005258</v>
+        <v>2766.195750005259</v>
       </c>
       <c r="AQ327" s="437" t="n">
         <v>2558.50423525106</v>
@@ -64937,7 +64937,7 @@
         <v>812602.7137558617</v>
       </c>
       <c r="BG327" s="442" t="n">
-        <v>2766.195750005258</v>
+        <v>2766.195750005259</v>
       </c>
       <c r="BH327" s="443" t="n">
         <v>2558.50423525106</v>
@@ -64969,7 +64969,7 @@
         <v>720066.080142892</v>
       </c>
       <c r="BW327" s="441" t="n">
-        <v>803513.4754289293</v>
+        <v>803513.4754289294</v>
       </c>
       <c r="BX327" s="442" t="n">
         <v>2768.108534927736</v>
@@ -64981,10 +64981,10 @@
         <v>2637.666976477417</v>
       </c>
       <c r="CA327" s="443" t="n">
-        <v>2762.769626948312</v>
+        <v>2762.769626948313</v>
       </c>
       <c r="CB327" s="444" t="n">
-        <v>2759.195590077078</v>
+        <v>2759.195590077079</v>
       </c>
       <c r="CI327" s="349" t="n">
         <v>0</v>
@@ -67005,7 +67005,7 @@
         </is>
       </c>
       <c r="AK341" s="506" t="n">
-        <v>9300.448898384631</v>
+        <v>9300.44889838463</v>
       </c>
       <c r="AL341" s="368" t="n">
         <v>34513.2223587984</v>
@@ -67020,7 +67020,7 @@
         <v>89580.48173789636</v>
       </c>
       <c r="AP341" s="381" t="n">
-        <v>588.3746268593677</v>
+        <v>588.3746268593676</v>
       </c>
       <c r="AQ341" s="372" t="n">
         <v>633.7546894227795</v>
@@ -67040,7 +67040,7 @@
         </is>
       </c>
       <c r="BB341" s="391" t="n">
-        <v>9300.448898384631</v>
+        <v>9300.44889838463</v>
       </c>
       <c r="BC341" s="375" t="n">
         <v>34513.2223587984</v>
@@ -67055,7 +67055,7 @@
         <v>89580.48173789636</v>
       </c>
       <c r="BG341" s="386" t="n">
-        <v>588.3746268593677</v>
+        <v>588.3746268593676</v>
       </c>
       <c r="BH341" s="372" t="n">
         <v>633.7546894227795</v>
@@ -67075,7 +67075,7 @@
         </is>
       </c>
       <c r="BS341" s="391" t="n">
-        <v>9158.952313317865</v>
+        <v>9158.952313317863</v>
       </c>
       <c r="BT341" s="375" t="n">
         <v>34208.97155320368</v>
@@ -67090,7 +67090,7 @@
         <v>88667.86459026212</v>
       </c>
       <c r="BX341" s="386" t="n">
-        <v>588.3746268593677</v>
+        <v>588.3746268593676</v>
       </c>
       <c r="BY341" s="372" t="n">
         <v>633.7546894227795</v>
@@ -67203,7 +67203,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="AL342" s="368" t="n">
-        <v>90066.83119143535</v>
+        <v>90066.83119143533</v>
       </c>
       <c r="AM342" s="368" t="n">
         <v>128629.5373619414</v>
@@ -67218,13 +67218,13 @@
         <v>1635.517697833116</v>
       </c>
       <c r="AQ342" s="372" t="n">
-        <v>1816.502530221657</v>
+        <v>1816.502530221656</v>
       </c>
       <c r="AR342" s="372" t="n">
         <v>1896.257077346365</v>
       </c>
       <c r="AS342" s="372" t="n">
-        <v>1944.27038939918</v>
+        <v>1944.270389399181</v>
       </c>
       <c r="AT342" s="382" t="n">
         <v>1996.685743610652</v>
@@ -67238,7 +67238,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="BC342" s="375" t="n">
-        <v>90066.83119143535</v>
+        <v>90066.83119143533</v>
       </c>
       <c r="BD342" s="375" t="n">
         <v>128629.5373619414</v>
@@ -67253,13 +67253,13 @@
         <v>1635.517697833116</v>
       </c>
       <c r="BH342" s="372" t="n">
-        <v>1816.502530221657</v>
+        <v>1816.502530221656</v>
       </c>
       <c r="BI342" s="372" t="n">
         <v>1896.257077346365</v>
       </c>
       <c r="BJ342" s="372" t="n">
-        <v>1944.27038939918</v>
+        <v>1944.270389399181</v>
       </c>
       <c r="BK342" s="387" t="n">
         <v>1996.685743610652</v>
@@ -67273,7 +67273,7 @@
         <v>44020.42113175881</v>
       </c>
       <c r="BT342" s="375" t="n">
-        <v>89418.86257800712</v>
+        <v>89418.86257800709</v>
       </c>
       <c r="BU342" s="375" t="n">
         <v>127597.1275987169</v>
@@ -67288,13 +67288,13 @@
         <v>1635.517697833116</v>
       </c>
       <c r="BY342" s="372" t="n">
-        <v>1816.502530221657</v>
+        <v>1816.502530221656</v>
       </c>
       <c r="BZ342" s="372" t="n">
         <v>1896.257077346365</v>
       </c>
       <c r="CA342" s="372" t="n">
-        <v>1944.27038939918</v>
+        <v>1944.270389399181</v>
       </c>
       <c r="CB342" s="387" t="n">
         <v>1996.685743610652</v>
@@ -67398,13 +67398,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="AL343" s="368" t="n">
-        <v>49819.67164514306</v>
+        <v>49819.67164514307</v>
       </c>
       <c r="AM343" s="368" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="AN343" s="368" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="AO343" s="380" t="n">
         <v>112279.5677980626</v>
@@ -67433,13 +67433,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="BC343" s="375" t="n">
-        <v>49819.67164514306</v>
+        <v>49819.67164514307</v>
       </c>
       <c r="BD343" s="375" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="BE343" s="375" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="BF343" s="392" t="n">
         <v>112279.5677980626</v>
@@ -67468,13 +67468,13 @@
         <v>26769.83350407975</v>
       </c>
       <c r="BT343" s="375" t="n">
-        <v>49147.27312593883</v>
+        <v>49147.27312593884</v>
       </c>
       <c r="BU343" s="375" t="n">
         <v>73574.4154376738</v>
       </c>
       <c r="BV343" s="375" t="n">
-        <v>87640.41389023532</v>
+        <v>87640.41389023533</v>
       </c>
       <c r="BW343" s="392" t="n">
         <v>110768.8497455169</v>
@@ -67611,7 +67611,7 @@
         <v>26075.56952842507</v>
       </c>
       <c r="AR344" s="411" t="n">
-        <v>23846.44159897524</v>
+        <v>23846.44159897525</v>
       </c>
       <c r="AS344" s="411" t="n">
         <v>24329.2099056213</v>
@@ -67646,7 +67646,7 @@
         <v>26075.56952842507</v>
       </c>
       <c r="BI344" s="417" t="n">
-        <v>23846.44159897524</v>
+        <v>23846.44159897525</v>
       </c>
       <c r="BJ344" s="417" t="n">
         <v>24329.2099056213</v>
@@ -67666,7 +67666,7 @@
         <v>180610.8970057784</v>
       </c>
       <c r="BU344" s="420" t="n">
-        <v>321214.116535682</v>
+        <v>321214.1165356821</v>
       </c>
       <c r="BV344" s="420" t="n">
         <v>412591.2330931693</v>
@@ -67681,7 +67681,7 @@
         <v>26075.56952842507</v>
       </c>
       <c r="BZ344" s="417" t="n">
-        <v>23846.44159897524</v>
+        <v>23846.44159897525</v>
       </c>
       <c r="CA344" s="417" t="n">
         <v>24329.2099056213</v>
@@ -67724,13 +67724,13 @@
         <v>589027.1056832182</v>
       </c>
       <c r="F345" s="425" t="n">
-        <v>726495.0525627602</v>
+        <v>726495.0525627601</v>
       </c>
       <c r="G345" s="426" t="n">
         <v>811994.5728673091</v>
       </c>
       <c r="H345" s="427" t="n">
-        <v>2893.401733095192</v>
+        <v>2893.401733095193</v>
       </c>
       <c r="I345" s="427" t="n">
         <v>2611.970298418244</v>
@@ -67759,13 +67759,13 @@
         <v>589027.1056832182</v>
       </c>
       <c r="W345" s="430" t="n">
-        <v>726495.0525627602</v>
+        <v>726495.0525627601</v>
       </c>
       <c r="X345" s="431" t="n">
         <v>811994.5728673091</v>
       </c>
       <c r="Y345" s="432" t="n">
-        <v>2893.401733095192</v>
+        <v>2893.401733095193</v>
       </c>
       <c r="Z345" s="433" t="n">
         <v>2611.970298418244</v>
@@ -67800,7 +67800,7 @@
         <v>812602.7137558617</v>
       </c>
       <c r="AP345" s="436" t="n">
-        <v>2766.195750005258</v>
+        <v>2766.195750005259</v>
       </c>
       <c r="AQ345" s="437" t="n">
         <v>2558.50423525106</v>
@@ -67835,7 +67835,7 @@
         <v>812602.7137558617</v>
       </c>
       <c r="BG345" s="442" t="n">
-        <v>2766.195750005258</v>
+        <v>2766.195750005259</v>
       </c>
       <c r="BH345" s="443" t="n">
         <v>2558.50423525106</v>
@@ -67867,7 +67867,7 @@
         <v>720066.080142892</v>
       </c>
       <c r="BW345" s="441" t="n">
-        <v>803513.4754289293</v>
+        <v>803513.4754289294</v>
       </c>
       <c r="BX345" s="442" t="n">
         <v>2768.108534927736</v>
@@ -67879,10 +67879,10 @@
         <v>2637.666976477417</v>
       </c>
       <c r="CA345" s="443" t="n">
-        <v>2762.769626948312</v>
+        <v>2762.769626948313</v>
       </c>
       <c r="CB345" s="444" t="n">
-        <v>2759.195590077078</v>
+        <v>2759.195590077079</v>
       </c>
       <c r="CI345" s="349" t="n">
         <v>0</v>
@@ -68431,25 +68431,25 @@
         <v>55144.4170261594</v>
       </c>
       <c r="AN350" s="368" t="n">
-        <v>55574.29755313223</v>
+        <v>55574.29755313224</v>
       </c>
       <c r="AO350" s="380" t="n">
-        <v>52234.63231220671</v>
+        <v>52234.63231220672</v>
       </c>
       <c r="AP350" s="381" t="n">
         <v>493.5238756900339</v>
       </c>
       <c r="AQ350" s="372" t="n">
-        <v>519.6117749504772</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="AR350" s="372" t="n">
         <v>539.4082092873381</v>
       </c>
       <c r="AS350" s="372" t="n">
-        <v>560.2095892622104</v>
+        <v>560.2095892622106</v>
       </c>
       <c r="AT350" s="382" t="n">
-        <v>582.4093271978968</v>
+        <v>582.4093271978969</v>
       </c>
       <c r="BA350" s="83" t="inlineStr">
         <is>
@@ -68466,25 +68466,25 @@
         <v>55144.4170261594</v>
       </c>
       <c r="BE350" s="375" t="n">
-        <v>55574.29755313223</v>
+        <v>55574.29755313224</v>
       </c>
       <c r="BF350" s="392" t="n">
-        <v>52234.63231220671</v>
+        <v>52234.63231220672</v>
       </c>
       <c r="BG350" s="386" t="n">
         <v>493.5238756900339</v>
       </c>
       <c r="BH350" s="372" t="n">
-        <v>519.6117749504772</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="BI350" s="372" t="n">
         <v>539.4082092873381</v>
       </c>
       <c r="BJ350" s="372" t="n">
-        <v>560.2095892622104</v>
+        <v>560.2095892622106</v>
       </c>
       <c r="BK350" s="387" t="n">
-        <v>582.4093271978968</v>
+        <v>582.4093271978969</v>
       </c>
       <c r="BR350" s="83" t="inlineStr">
         <is>
@@ -68495,28 +68495,28 @@
         <v>52269.06877515536</v>
       </c>
       <c r="BT350" s="375" t="n">
-        <v>55718.66770506615</v>
+        <v>55718.66770506614</v>
       </c>
       <c r="BU350" s="375" t="n">
-        <v>56250.9738097353</v>
+        <v>56250.97380973532</v>
       </c>
       <c r="BV350" s="375" t="n">
-        <v>56875.80716202218</v>
+        <v>56875.80716202219</v>
       </c>
       <c r="BW350" s="392" t="n">
-        <v>53692.12532407887</v>
+        <v>53692.12532407886</v>
       </c>
       <c r="BX350" s="386" t="n">
         <v>496.2762703297993</v>
       </c>
       <c r="BY350" s="372" t="n">
-        <v>522.5857910681439</v>
+        <v>522.5857910681437</v>
       </c>
       <c r="BZ350" s="372" t="n">
         <v>542.9862561413803</v>
       </c>
       <c r="CA350" s="372" t="n">
-        <v>564.1429010659274</v>
+        <v>564.1429010659275</v>
       </c>
       <c r="CB350" s="387" t="n">
         <v>586.6102006335916</v>
@@ -68607,19 +68607,19 @@
         <v>106892.3579266921</v>
       </c>
       <c r="AM351" s="368" t="n">
-        <v>110003.6379453574</v>
+        <v>110003.6379453573</v>
       </c>
       <c r="AN351" s="368" t="n">
-        <v>114758.823953272</v>
+        <v>114758.8239532721</v>
       </c>
       <c r="AO351" s="380" t="n">
         <v>118336.8554245862</v>
       </c>
       <c r="AP351" s="381" t="n">
-        <v>1467.895618937488</v>
+        <v>1467.895618937487</v>
       </c>
       <c r="AQ351" s="372" t="n">
-        <v>1541.979551188244</v>
+        <v>1541.979551188243</v>
       </c>
       <c r="AR351" s="372" t="n">
         <v>1611.110675969702</v>
@@ -68642,19 +68642,19 @@
         <v>106892.3579266921</v>
       </c>
       <c r="BD351" s="375" t="n">
-        <v>110003.6379453574</v>
+        <v>110003.6379453573</v>
       </c>
       <c r="BE351" s="375" t="n">
-        <v>114758.823953272</v>
+        <v>114758.8239532721</v>
       </c>
       <c r="BF351" s="392" t="n">
         <v>118336.8554245862</v>
       </c>
       <c r="BG351" s="386" t="n">
-        <v>1467.895618937488</v>
+        <v>1467.895618937487</v>
       </c>
       <c r="BH351" s="372" t="n">
-        <v>1541.979551188244</v>
+        <v>1541.979551188243</v>
       </c>
       <c r="BI351" s="372" t="n">
         <v>1611.110675969702</v>
@@ -68671,7 +68671,7 @@
         </is>
       </c>
       <c r="BS351" s="391" t="n">
-        <v>102111.6538655731</v>
+        <v>102111.653865573</v>
       </c>
       <c r="BT351" s="375" t="n">
         <v>107673.7026560977</v>
@@ -68680,22 +68680,22 @@
         <v>111125.8008862658</v>
       </c>
       <c r="BV351" s="375" t="n">
-        <v>116222.837502215</v>
+        <v>116222.8375022151</v>
       </c>
       <c r="BW351" s="392" t="n">
         <v>120133.4562612584</v>
       </c>
       <c r="BX351" s="386" t="n">
-        <v>1469.304426022865</v>
+        <v>1469.304426022864</v>
       </c>
       <c r="BY351" s="372" t="n">
         <v>1543.360227035032</v>
       </c>
       <c r="BZ351" s="372" t="n">
-        <v>1612.611146590333</v>
+        <v>1612.611146590332</v>
       </c>
       <c r="CA351" s="372" t="n">
-        <v>1691.585676214611</v>
+        <v>1691.585676214612</v>
       </c>
       <c r="CB351" s="387" t="n">
         <v>1770.03796411774</v>
@@ -68786,13 +68786,13 @@
         <v>56496.75148806424</v>
       </c>
       <c r="AM352" s="368" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="AN352" s="368" t="n">
         <v>52431.33015542696</v>
       </c>
       <c r="AO352" s="380" t="n">
-        <v>56018.87435173048</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="AP352" s="381" t="n">
         <v>538.3261867538652</v>
@@ -68804,10 +68804,10 @@
         <v>588.8613564801755</v>
       </c>
       <c r="AS352" s="372" t="n">
-        <v>614.8282788519615</v>
+        <v>614.8282788519614</v>
       </c>
       <c r="AT352" s="382" t="n">
-        <v>659.9824391699888</v>
+        <v>659.9824391699885</v>
       </c>
       <c r="BA352" s="111" t="inlineStr">
         <is>
@@ -68821,13 +68821,13 @@
         <v>56496.75148806424</v>
       </c>
       <c r="BD352" s="375" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="BE352" s="375" t="n">
         <v>52431.33015542696</v>
       </c>
       <c r="BF352" s="392" t="n">
-        <v>56018.87435173048</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="BG352" s="386" t="n">
         <v>538.3261867538652</v>
@@ -68839,10 +68839,10 @@
         <v>588.8613564801755</v>
       </c>
       <c r="BJ352" s="372" t="n">
-        <v>614.8282788519615</v>
+        <v>614.8282788519614</v>
       </c>
       <c r="BK352" s="387" t="n">
-        <v>659.9824391699888</v>
+        <v>659.9824391699885</v>
       </c>
       <c r="BR352" s="111" t="inlineStr">
         <is>
@@ -68853,31 +68853,31 @@
         <v>55227.55342929587</v>
       </c>
       <c r="BT352" s="375" t="n">
-        <v>56905.08867324545</v>
+        <v>56905.08867324547</v>
       </c>
       <c r="BU352" s="375" t="n">
-        <v>56485.98781551626</v>
+        <v>56485.98781551625</v>
       </c>
       <c r="BV352" s="375" t="n">
         <v>53080.79535081491</v>
       </c>
       <c r="BW352" s="392" t="n">
-        <v>56852.9115608031</v>
+        <v>56852.91156080308</v>
       </c>
       <c r="BX352" s="386" t="n">
         <v>539.6612028096363</v>
       </c>
       <c r="BY352" s="372" t="n">
-        <v>565.9105666048658</v>
+        <v>565.9105666048659</v>
       </c>
       <c r="BZ352" s="372" t="n">
-        <v>590.4642594520905</v>
+        <v>590.4642594520906</v>
       </c>
       <c r="CA352" s="372" t="n">
         <v>616.7228680400991</v>
       </c>
       <c r="CB352" s="387" t="n">
-        <v>662.0232146523805</v>
+        <v>662.0232146523803</v>
       </c>
       <c r="CI352" s="225" t="n"/>
       <c r="CJ352" s="225" t="n"/>
@@ -68959,7 +68959,7 @@
         </is>
       </c>
       <c r="AK353" s="435" t="n">
-        <v>590580.957886965</v>
+        <v>590580.9578869651</v>
       </c>
       <c r="AL353" s="408" t="n">
         <v>546108.3143469056</v>
@@ -68971,7 +68971,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="AO353" s="409" t="n">
-        <v>417885.453398537</v>
+        <v>417885.4533985371</v>
       </c>
       <c r="AP353" s="410" t="n">
         <v>25268.66956059994</v>
@@ -68994,7 +68994,7 @@
         </is>
       </c>
       <c r="BB353" s="419" t="n">
-        <v>590580.957886965</v>
+        <v>590580.9578869651</v>
       </c>
       <c r="BC353" s="420" t="n">
         <v>546108.3143469056</v>
@@ -69006,7 +69006,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="BF353" s="421" t="n">
-        <v>417885.453398537</v>
+        <v>417885.4533985371</v>
       </c>
       <c r="BG353" s="416" t="n">
         <v>25268.66956059994</v>
@@ -69041,7 +69041,7 @@
         <v>402245.7525736701</v>
       </c>
       <c r="BW353" s="421" t="n">
-        <v>423521.3656159502</v>
+        <v>423521.3656159503</v>
       </c>
       <c r="BX353" s="416" t="n">
         <v>25256.546832515</v>
@@ -69056,7 +69056,7 @@
         <v>27780.45073578561</v>
       </c>
       <c r="CB353" s="418" t="n">
-        <v>28770.8182458609</v>
+        <v>28770.81824586091</v>
       </c>
       <c r="CI353" s="225" t="n"/>
       <c r="CJ353" s="225" t="n"/>
@@ -69068,22 +69068,22 @@
         </is>
       </c>
       <c r="C354" s="425" t="n">
-        <v>857961.4933376428</v>
+        <v>857961.4933376429</v>
       </c>
       <c r="D354" s="425" t="n">
-        <v>845360.4604822556</v>
+        <v>845360.4604822557</v>
       </c>
       <c r="E354" s="425" t="n">
         <v>756823.2926902301</v>
       </c>
       <c r="F354" s="425" t="n">
-        <v>727992.0158194148</v>
+        <v>727992.0158194149</v>
       </c>
       <c r="G354" s="426" t="n">
         <v>772786.3925708712</v>
       </c>
       <c r="H354" s="427" t="n">
-        <v>1850.302136523233</v>
+        <v>1850.302136523234</v>
       </c>
       <c r="I354" s="427" t="n">
         <v>2023.284531473399</v>
@@ -69103,22 +69103,22 @@
         </is>
       </c>
       <c r="T354" s="429" t="n">
-        <v>857961.4933376428</v>
+        <v>857961.4933376429</v>
       </c>
       <c r="U354" s="430" t="n">
-        <v>845360.4604822556</v>
+        <v>845360.4604822557</v>
       </c>
       <c r="V354" s="430" t="n">
         <v>756823.2926902301</v>
       </c>
       <c r="W354" s="430" t="n">
-        <v>727992.0158194148</v>
+        <v>727992.0158194149</v>
       </c>
       <c r="X354" s="431" t="n">
         <v>772786.3925708712</v>
       </c>
       <c r="Y354" s="432" t="n">
-        <v>1850.302136523233</v>
+        <v>1850.302136523234</v>
       </c>
       <c r="Z354" s="433" t="n">
         <v>2023.284531473399</v>
@@ -69138,13 +69138,13 @@
         </is>
       </c>
       <c r="AK354" s="435" t="n">
-        <v>798622.624669048</v>
+        <v>798622.6246690482</v>
       </c>
       <c r="AL354" s="408" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="AM354" s="408" t="n">
-        <v>666853.7543426913</v>
+        <v>666853.7543426912</v>
       </c>
       <c r="AN354" s="408" t="n">
         <v>620602.53611857</v>
@@ -69153,13 +69153,13 @@
         <v>644475.8154870603</v>
       </c>
       <c r="AP354" s="436" t="n">
-        <v>2670.705402387384</v>
+        <v>2670.705402387385</v>
       </c>
       <c r="AQ354" s="437" t="n">
-        <v>2568.653893492042</v>
+        <v>2568.653893492041</v>
       </c>
       <c r="AR354" s="437" t="n">
-        <v>2360.418532840139</v>
+        <v>2360.418532840138</v>
       </c>
       <c r="AS354" s="437" t="n">
         <v>2326.994788066118</v>
@@ -69173,13 +69173,13 @@
         </is>
       </c>
       <c r="BB354" s="439" t="n">
-        <v>798622.624669048</v>
+        <v>798622.6246690482</v>
       </c>
       <c r="BC354" s="440" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="BD354" s="440" t="n">
-        <v>666853.7543426913</v>
+        <v>666853.7543426912</v>
       </c>
       <c r="BE354" s="440" t="n">
         <v>620602.53611857</v>
@@ -69188,13 +69188,13 @@
         <v>644475.8154870603</v>
       </c>
       <c r="BG354" s="442" t="n">
-        <v>2670.705402387384</v>
+        <v>2670.705402387385</v>
       </c>
       <c r="BH354" s="443" t="n">
-        <v>2568.653893492042</v>
+        <v>2568.653893492041</v>
       </c>
       <c r="BI354" s="443" t="n">
-        <v>2360.418532840139</v>
+        <v>2360.418532840138</v>
       </c>
       <c r="BJ354" s="443" t="n">
         <v>2326.994788066118</v>
@@ -69208,7 +69208,7 @@
         </is>
       </c>
       <c r="BS354" s="439" t="n">
-        <v>801676.5659446716</v>
+        <v>801676.5659446715</v>
       </c>
       <c r="BT354" s="440" t="n">
         <v>768586.292102884</v>
@@ -69217,7 +69217,7 @@
         <v>672857.3486787787</v>
       </c>
       <c r="BV354" s="440" t="n">
-        <v>628425.1925887222</v>
+        <v>628425.1925887223</v>
       </c>
       <c r="BW354" s="441" t="n">
         <v>654199.8587620906</v>
@@ -69229,10 +69229,10 @@
         <v>2565.084368566222</v>
       </c>
       <c r="BZ354" s="443" t="n">
-        <v>2358.556112632619</v>
+        <v>2358.55611263262</v>
       </c>
       <c r="CA354" s="443" t="n">
-        <v>2326.870691061409</v>
+        <v>2326.87069106141</v>
       </c>
       <c r="CB354" s="444" t="n">
         <v>2516.171986431975</v>
@@ -71122,25 +71122,25 @@
         <v>55144.4170261594</v>
       </c>
       <c r="AN368" s="368" t="n">
-        <v>55574.29755313223</v>
+        <v>55574.29755313224</v>
       </c>
       <c r="AO368" s="380" t="n">
-        <v>52234.63231220671</v>
+        <v>52234.63231220672</v>
       </c>
       <c r="AP368" s="381" t="n">
         <v>493.5238756900339</v>
       </c>
       <c r="AQ368" s="372" t="n">
-        <v>519.6117749504772</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="AR368" s="372" t="n">
         <v>539.4082092873381</v>
       </c>
       <c r="AS368" s="372" t="n">
-        <v>560.2095892622104</v>
+        <v>560.2095892622106</v>
       </c>
       <c r="AT368" s="382" t="n">
-        <v>582.4093271978968</v>
+        <v>582.4093271978969</v>
       </c>
       <c r="BA368" s="83" t="inlineStr">
         <is>
@@ -71157,25 +71157,25 @@
         <v>55144.4170261594</v>
       </c>
       <c r="BE368" s="375" t="n">
-        <v>55574.29755313223</v>
+        <v>55574.29755313224</v>
       </c>
       <c r="BF368" s="392" t="n">
-        <v>52234.63231220671</v>
+        <v>52234.63231220672</v>
       </c>
       <c r="BG368" s="386" t="n">
         <v>493.5238756900339</v>
       </c>
       <c r="BH368" s="372" t="n">
-        <v>519.6117749504772</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="BI368" s="372" t="n">
         <v>539.4082092873381</v>
       </c>
       <c r="BJ368" s="372" t="n">
-        <v>560.2095892622104</v>
+        <v>560.2095892622106</v>
       </c>
       <c r="BK368" s="387" t="n">
-        <v>582.4093271978968</v>
+        <v>582.4093271978969</v>
       </c>
       <c r="BR368" s="83" t="inlineStr">
         <is>
@@ -71189,43 +71189,43 @@
         <v>55718.66770506615</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>56250.97380973529</v>
+        <v>56250.9738097353</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>56875.80716202218</v>
+        <v>56875.80716202219</v>
       </c>
       <c r="BW368" s="392" t="n">
-        <v>53692.12532407886</v>
+        <v>53692.12532407887</v>
       </c>
       <c r="BX368" s="386" t="n">
         <v>496.2762703297993</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>522.5857910681439</v>
+        <v>522.5857910681437</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>542.9862561413802</v>
+        <v>542.9862561413803</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>564.1429010659274</v>
+        <v>564.1429010659275</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>586.6102006335915</v>
+        <v>586.6102006335916</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>608.4285996162369</v>
+        <v>608.4285996162396</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>615.2501473815283</v>
+        <v>615.2501473815304</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>675.0153000277152</v>
+        <v>675.0153000277181</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>702.5569214363007</v>
+        <v>702.5569214363027</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>695.0424454521085</v>
+        <v>695.0424454521087</v>
       </c>
     </row>
     <row r="369">
@@ -71311,19 +71311,19 @@
         <v>106892.3579266921</v>
       </c>
       <c r="AM369" s="368" t="n">
-        <v>110003.6379453574</v>
+        <v>110003.6379453573</v>
       </c>
       <c r="AN369" s="368" t="n">
-        <v>114758.823953272</v>
+        <v>114758.8239532721</v>
       </c>
       <c r="AO369" s="380" t="n">
         <v>118336.8554245862</v>
       </c>
       <c r="AP369" s="381" t="n">
-        <v>1467.895618937488</v>
+        <v>1467.895618937487</v>
       </c>
       <c r="AQ369" s="372" t="n">
-        <v>1541.979551188244</v>
+        <v>1541.979551188243</v>
       </c>
       <c r="AR369" s="372" t="n">
         <v>1611.110675969702</v>
@@ -71346,19 +71346,19 @@
         <v>106892.3579266921</v>
       </c>
       <c r="BD369" s="375" t="n">
-        <v>110003.6379453574</v>
+        <v>110003.6379453573</v>
       </c>
       <c r="BE369" s="375" t="n">
-        <v>114758.823953272</v>
+        <v>114758.8239532721</v>
       </c>
       <c r="BF369" s="392" t="n">
         <v>118336.8554245862</v>
       </c>
       <c r="BG369" s="386" t="n">
-        <v>1467.895618937488</v>
+        <v>1467.895618937487</v>
       </c>
       <c r="BH369" s="372" t="n">
-        <v>1541.979551188244</v>
+        <v>1541.979551188243</v>
       </c>
       <c r="BI369" s="372" t="n">
         <v>1611.110675969702</v>
@@ -71375,7 +71375,7 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>102111.6538655731</v>
+        <v>102111.653865573</v>
       </c>
       <c r="BT369" s="375" t="n">
         <v>107673.7026560977</v>
@@ -71384,40 +71384,40 @@
         <v>111125.8008862658</v>
       </c>
       <c r="BV369" s="375" t="n">
-        <v>116222.837502215</v>
+        <v>116222.8375022151</v>
       </c>
       <c r="BW369" s="392" t="n">
         <v>120133.4562612584</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>1469.304426022865</v>
+        <v>1469.304426022864</v>
       </c>
       <c r="BY369" s="372" t="n">
         <v>1543.360227035032</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>1612.611146590333</v>
+        <v>1612.611146590332</v>
       </c>
       <c r="CA369" s="372" t="n">
-        <v>1691.585676214611</v>
+        <v>1691.585676214612</v>
       </c>
       <c r="CB369" s="387" t="n">
         <v>1770.03796411774</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>250.1301657702883</v>
+        <v>250.13016577029</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>231.3018117134542</v>
+        <v>231.3018117134563</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>245.0000227696949</v>
+        <v>245.0000227696965</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>260.960813134297</v>
+        <v>260.9608131342982</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>239.4551276586439</v>
+        <v>239.4551276586454</v>
       </c>
     </row>
     <row r="370">
@@ -71503,13 +71503,13 @@
         <v>56496.75148806424</v>
       </c>
       <c r="AM370" s="368" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="AN370" s="368" t="n">
         <v>52431.33015542696</v>
       </c>
       <c r="AO370" s="380" t="n">
-        <v>56018.87435173048</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="AP370" s="381" t="n">
         <v>538.3261867538652</v>
@@ -71521,10 +71521,10 @@
         <v>588.8613564801755</v>
       </c>
       <c r="AS370" s="372" t="n">
-        <v>614.8282788519615</v>
+        <v>614.8282788519614</v>
       </c>
       <c r="AT370" s="382" t="n">
-        <v>659.9824391699888</v>
+        <v>659.9824391699885</v>
       </c>
       <c r="BA370" s="111" t="inlineStr">
         <is>
@@ -71538,13 +71538,13 @@
         <v>56496.75148806424</v>
       </c>
       <c r="BD370" s="375" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="BE370" s="375" t="n">
         <v>52431.33015542696</v>
       </c>
       <c r="BF370" s="392" t="n">
-        <v>56018.87435173048</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="BG370" s="386" t="n">
         <v>538.3261867538652</v>
@@ -71556,10 +71556,10 @@
         <v>588.8613564801755</v>
       </c>
       <c r="BJ370" s="372" t="n">
-        <v>614.8282788519615</v>
+        <v>614.8282788519614</v>
       </c>
       <c r="BK370" s="387" t="n">
-        <v>659.9824391699888</v>
+        <v>659.9824391699885</v>
       </c>
       <c r="BR370" s="111" t="inlineStr">
         <is>
@@ -71567,49 +71567,49 @@
         </is>
       </c>
       <c r="BS370" s="391" t="n">
-        <v>55227.55342929586</v>
+        <v>55227.55342929587</v>
       </c>
       <c r="BT370" s="375" t="n">
-        <v>56905.08867324544</v>
+        <v>56905.08867324546</v>
       </c>
       <c r="BU370" s="375" t="n">
-        <v>56485.98781551626</v>
+        <v>56485.98781551625</v>
       </c>
       <c r="BV370" s="375" t="n">
         <v>53080.79535081491</v>
       </c>
       <c r="BW370" s="392" t="n">
-        <v>56852.9115608031</v>
+        <v>56852.91156080308</v>
       </c>
       <c r="BX370" s="386" t="n">
         <v>539.6612028096363</v>
       </c>
       <c r="BY370" s="372" t="n">
-        <v>565.9105666048658</v>
+        <v>565.9105666048659</v>
       </c>
       <c r="BZ370" s="372" t="n">
-        <v>590.4642594520905</v>
+        <v>590.4642594520906</v>
       </c>
       <c r="CA370" s="372" t="n">
         <v>616.7228680400991</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>662.0232146523805</v>
+        <v>662.0232146523803</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>178.9675421950328</v>
+        <v>178.9675421950389</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>190.4056745744036</v>
+        <v>190.4056745744106</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>199.9229219469736</v>
+        <v>199.9229219469816</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>211.8809362706868</v>
+        <v>211.8809362706961</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>227.4091424758149</v>
+        <v>227.4091424758251</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71689,7 +71689,7 @@
         </is>
       </c>
       <c r="AK371" s="435" t="n">
-        <v>590580.957886965</v>
+        <v>590580.9578869651</v>
       </c>
       <c r="AL371" s="408" t="n">
         <v>546108.3143469056</v>
@@ -71701,7 +71701,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="AO371" s="409" t="n">
-        <v>417885.453398537</v>
+        <v>417885.4533985371</v>
       </c>
       <c r="AP371" s="410" t="n">
         <v>25268.66956059994</v>
@@ -71724,7 +71724,7 @@
         </is>
       </c>
       <c r="BB371" s="419" t="n">
-        <v>590580.957886965</v>
+        <v>590580.9578869651</v>
       </c>
       <c r="BC371" s="420" t="n">
         <v>546108.3143469056</v>
@@ -71736,7 +71736,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="BF371" s="421" t="n">
-        <v>417885.453398537</v>
+        <v>417885.4533985371</v>
       </c>
       <c r="BG371" s="416" t="n">
         <v>25268.66956059994</v>
@@ -71759,7 +71759,7 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>592068.2898746472</v>
+        <v>592068.2898746473</v>
       </c>
       <c r="BT371" s="420" t="n">
         <v>548288.8330684749</v>
@@ -71771,7 +71771,7 @@
         <v>402245.7525736701</v>
       </c>
       <c r="BW371" s="421" t="n">
-        <v>423521.3656159501</v>
+        <v>423521.3656159502</v>
       </c>
       <c r="BX371" s="416" t="n">
         <v>25256.546832515</v>
@@ -71786,22 +71786,22 @@
         <v>27780.45073578561</v>
       </c>
       <c r="CB371" s="418" t="n">
-        <v>28770.8182458609</v>
+        <v>28770.81824586091</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>30.87585763408107</v>
+        <v>30.87585763408048</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>33.42901440362412</v>
+        <v>33.42901440362353</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>36.32946946924582</v>
+        <v>36.32946946924555</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>39.07531211650949</v>
+        <v>39.07531211650959</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>42.0306350805082</v>
+        <v>42.03063508050789</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71811,22 +71811,22 @@
         </is>
       </c>
       <c r="C372" s="425" t="n">
-        <v>857961.4933376428</v>
+        <v>857961.4933376429</v>
       </c>
       <c r="D372" s="425" t="n">
-        <v>845360.4604822556</v>
+        <v>845360.4604822557</v>
       </c>
       <c r="E372" s="425" t="n">
         <v>756823.2926902301</v>
       </c>
       <c r="F372" s="425" t="n">
-        <v>727992.0158194148</v>
+        <v>727992.0158194149</v>
       </c>
       <c r="G372" s="426" t="n">
         <v>772786.3925708712</v>
       </c>
       <c r="H372" s="427" t="n">
-        <v>1850.302136523233</v>
+        <v>1850.302136523234</v>
       </c>
       <c r="I372" s="427" t="n">
         <v>2023.284531473399</v>
@@ -71846,22 +71846,22 @@
         </is>
       </c>
       <c r="T372" s="429" t="n">
-        <v>857961.4933376428</v>
+        <v>857961.4933376429</v>
       </c>
       <c r="U372" s="430" t="n">
-        <v>845360.4604822556</v>
+        <v>845360.4604822557</v>
       </c>
       <c r="V372" s="430" t="n">
         <v>756823.2926902301</v>
       </c>
       <c r="W372" s="430" t="n">
-        <v>727992.0158194148</v>
+        <v>727992.0158194149</v>
       </c>
       <c r="X372" s="431" t="n">
         <v>772786.3925708712</v>
       </c>
       <c r="Y372" s="432" t="n">
-        <v>1850.302136523233</v>
+        <v>1850.302136523234</v>
       </c>
       <c r="Z372" s="433" t="n">
         <v>2023.284531473399</v>
@@ -71881,13 +71881,13 @@
         </is>
       </c>
       <c r="AK372" s="435" t="n">
-        <v>798622.624669048</v>
+        <v>798622.6246690482</v>
       </c>
       <c r="AL372" s="408" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="AM372" s="408" t="n">
-        <v>666853.7543426913</v>
+        <v>666853.7543426912</v>
       </c>
       <c r="AN372" s="408" t="n">
         <v>620602.53611857</v>
@@ -71896,13 +71896,13 @@
         <v>644475.8154870603</v>
       </c>
       <c r="AP372" s="436" t="n">
-        <v>2670.705402387384</v>
+        <v>2670.705402387385</v>
       </c>
       <c r="AQ372" s="437" t="n">
-        <v>2568.653893492042</v>
+        <v>2568.653893492041</v>
       </c>
       <c r="AR372" s="437" t="n">
-        <v>2360.418532840139</v>
+        <v>2360.418532840138</v>
       </c>
       <c r="AS372" s="437" t="n">
         <v>2326.994788066118</v>
@@ -71916,13 +71916,13 @@
         </is>
       </c>
       <c r="BB372" s="439" t="n">
-        <v>798622.624669048</v>
+        <v>798622.6246690482</v>
       </c>
       <c r="BC372" s="440" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="BD372" s="440" t="n">
-        <v>666853.7543426913</v>
+        <v>666853.7543426912</v>
       </c>
       <c r="BE372" s="440" t="n">
         <v>620602.53611857</v>
@@ -71931,13 +71931,13 @@
         <v>644475.8154870603</v>
       </c>
       <c r="BG372" s="442" t="n">
-        <v>2670.705402387384</v>
+        <v>2670.705402387385</v>
       </c>
       <c r="BH372" s="443" t="n">
-        <v>2568.653893492042</v>
+        <v>2568.653893492041</v>
       </c>
       <c r="BI372" s="443" t="n">
-        <v>2360.418532840139</v>
+        <v>2360.418532840138</v>
       </c>
       <c r="BJ372" s="443" t="n">
         <v>2326.994788066118</v>
@@ -71951,49 +71951,49 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>801676.5659446714</v>
+        <v>801676.5659446715</v>
       </c>
       <c r="BT372" s="440" t="n">
         <v>768586.2921028842</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>672857.3486787787</v>
+        <v>672857.3486787786</v>
       </c>
       <c r="BV372" s="440" t="n">
-        <v>628425.1925887222</v>
+        <v>628425.1925887223</v>
       </c>
       <c r="BW372" s="441" t="n">
-        <v>654199.8587620904</v>
+        <v>654199.8587620906</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>2666.932537370535</v>
+        <v>2666.932537370536</v>
       </c>
       <c r="BY372" s="443" t="n">
         <v>2565.084368566222</v>
       </c>
       <c r="BZ372" s="443" t="n">
-        <v>2358.55611263262</v>
+        <v>2358.556112632619</v>
       </c>
       <c r="CA372" s="443" t="n">
-        <v>2326.870691061409</v>
+        <v>2326.87069106141</v>
       </c>
       <c r="CB372" s="444" t="n">
         <v>2516.171986431975</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>1068.402165215639</v>
+        <v>1068.402165215649</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>1070.38664807301</v>
+        <v>1070.386648073021</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>1156.267714213629</v>
+        <v>1156.267714213642</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>1214.473982957794</v>
+        <v>1214.473982957807</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>1203.937350667075</v>
+        <v>1203.937350667087</v>
       </c>
     </row>
     <row r="375">
